--- a/research/traditional_assets/database/data/japan/japan_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ45"/>
+  <dimension ref="A1:AQ48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,106 +588,106 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.01245</v>
+        <v>0.01675</v>
       </c>
       <c r="E2">
-        <v>-0.0157</v>
+        <v>0.00363</v>
       </c>
       <c r="F2">
-        <v>0.1345</v>
+        <v>0.124</v>
       </c>
       <c r="G2">
-        <v>0.001487440612352631</v>
+        <v>0.0008860467951931285</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001280751237425617</v>
+        <v>0.0006099185063543841</v>
       </c>
       <c r="J2">
-        <v>0.0009073437944644367</v>
+        <v>0.0004511388845228548</v>
       </c>
       <c r="K2">
-        <v>5403.44</v>
+        <v>6622.149</v>
       </c>
       <c r="L2">
-        <v>0.1485636987506599</v>
+        <v>0.1794352874232838</v>
       </c>
       <c r="M2">
-        <v>2559.01101</v>
+        <v>2892.81927</v>
       </c>
       <c r="N2">
-        <v>0.03934173988441973</v>
+        <v>0.03957280140408092</v>
       </c>
       <c r="O2">
-        <v>0.4735892338954444</v>
+        <v>0.4368399548243327</v>
       </c>
       <c r="P2">
-        <v>1653.36701</v>
+        <v>1968.07927</v>
       </c>
       <c r="Q2">
-        <v>0.0254185443465133</v>
+        <v>0.02692266706976083</v>
       </c>
       <c r="R2">
-        <v>0.3059841526879173</v>
+        <v>0.2971964644709746</v>
       </c>
       <c r="S2">
-        <v>905.644</v>
+        <v>924.7399999999999</v>
       </c>
       <c r="T2">
-        <v>0.3539039091512154</v>
+        <v>0.3196673949147193</v>
       </c>
       <c r="U2">
-        <v>529787.3</v>
+        <v>553989.2</v>
       </c>
       <c r="V2">
-        <v>8.144847391910611</v>
+        <v>7.578387222097585</v>
       </c>
       <c r="W2">
-        <v>0.0287622856656597</v>
+        <v>0.03538987906061746</v>
       </c>
       <c r="X2">
-        <v>0.1502495257700956</v>
+        <v>0.1055416727267129</v>
       </c>
       <c r="Y2">
-        <v>-0.1214872401044359</v>
+        <v>-0.07015179366609545</v>
       </c>
       <c r="Z2">
-        <v>0.4859411249350646</v>
+        <v>0.7285317865450093</v>
       </c>
       <c r="AA2">
-        <v>0.0001922562276679438</v>
+        <v>0.0002344296202351785</v>
       </c>
       <c r="AB2">
-        <v>0.06313932733499378</v>
+        <v>0.04948080224828148</v>
       </c>
       <c r="AC2">
-        <v>-0.06289677135603042</v>
+        <v>-0.04878559490396137</v>
       </c>
       <c r="AD2">
-        <v>325310.4</v>
+        <v>381726.5</v>
       </c>
       <c r="AE2">
-        <v>318.1077029667269</v>
+        <v>229.8732628186914</v>
       </c>
       <c r="AF2">
-        <v>325628.5077029667</v>
+        <v>381956.3732628187</v>
       </c>
       <c r="AG2">
-        <v>-204158.7922970333</v>
+        <v>-172032.8267371813</v>
       </c>
       <c r="AH2">
-        <v>0.8335039817897196</v>
+        <v>0.8393583487121081</v>
       </c>
       <c r="AI2">
-        <v>0.7090882573000377</v>
+        <v>0.7317193302795527</v>
       </c>
       <c r="AJ2">
-        <v>1.467574251466677</v>
+        <v>1.738906277101845</v>
       </c>
       <c r="AK2">
-        <v>2.893165318985365</v>
+        <v>5.377584202775732</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>2951.892853253965</v>
+        <v>5573.951579931079</v>
       </c>
       <c r="AP2">
-        <v>-1852.553376438544</v>
+        <v>-2512.01487555022</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Seven Bank, Ltd. (TSE:8410)</t>
+          <t>The Chiba Bank, Ltd. (TSE:8331)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0303</v>
+        <v>0.0269</v>
       </c>
       <c r="E3">
-        <v>-0.052</v>
+        <v>0.0301</v>
       </c>
       <c r="F3">
-        <v>0.0206</v>
+        <v>0.0864</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,82 +734,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.004911725719515757</v>
+        <v>0.0005388541229063475</v>
       </c>
       <c r="J3">
-        <v>0.003663486713618974</v>
+        <v>0.0003749038936780218</v>
       </c>
       <c r="K3">
-        <v>136.1</v>
+        <v>400.4</v>
       </c>
       <c r="L3">
-        <v>0.1393467799733797</v>
+        <v>0.2524908563501072</v>
       </c>
       <c r="M3">
-        <v>90.0612</v>
+        <v>179.8848</v>
       </c>
       <c r="N3">
-        <v>0.03854039712427251</v>
+        <v>0.03434948156352041</v>
       </c>
       <c r="O3">
-        <v>0.6617281410727407</v>
+        <v>0.4492627372627372</v>
       </c>
       <c r="P3">
-        <v>89.3912</v>
+        <v>145.6848</v>
       </c>
       <c r="Q3">
-        <v>0.03825368024649092</v>
+        <v>0.0278189004945674</v>
       </c>
       <c r="R3">
-        <v>0.6568052902277737</v>
+        <v>0.3638481518481518</v>
       </c>
       <c r="S3">
-        <v>0.6700000000000017</v>
+        <v>34.19999999999999</v>
       </c>
       <c r="T3">
-        <v>0.007439385662194172</v>
+        <v>0.1901216778738392</v>
       </c>
       <c r="U3">
-        <v>6833.4</v>
+        <v>26898.6</v>
       </c>
       <c r="V3">
-        <v>2.924255391989044</v>
+        <v>5.13635929653039</v>
       </c>
       <c r="W3">
-        <v>0.06370231687339106</v>
+        <v>0.05560647723800794</v>
       </c>
       <c r="X3">
-        <v>0.07533699358562532</v>
+        <v>0.09877210792575147</v>
       </c>
       <c r="Y3">
-        <v>-0.01163467671223425</v>
+        <v>-0.04316563068774353</v>
       </c>
       <c r="AB3">
-        <v>0.06549114256500985</v>
+        <v>0.05272175935504415</v>
       </c>
       <c r="AD3">
-        <v>1258.6</v>
+        <v>19912.9</v>
       </c>
       <c r="AE3">
-        <v>8.313587448744794</v>
+        <v>4.077425659475571</v>
       </c>
       <c r="AF3">
-        <v>1266.913587448745</v>
+        <v>19916.97742565948</v>
       </c>
       <c r="AG3">
-        <v>-5566.486412551255</v>
+        <v>-6981.622574340523</v>
       </c>
       <c r="AH3">
-        <v>0.3515577907914869</v>
+        <v>0.7918054576087805</v>
       </c>
       <c r="AI3">
-        <v>0.4219088366804487</v>
+        <v>0.7283196704147048</v>
       </c>
       <c r="AJ3">
-        <v>1.723537737570649</v>
+        <v>4.001566023744183</v>
       </c>
       <c r="AK3">
-        <v>1.453168213178058</v>
+        <v>-15.58824395773115</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>194.8297213622291</v>
+        <v>11923.89221556886</v>
       </c>
       <c r="AP3">
-        <v>-861.6852031813088</v>
+        <v>-4180.612319964385</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Concordia Financial Group, Ltd. (TSE:7186)</t>
+          <t>Juroku Financial Group,Inc. (TSE:7380)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.03240000000000001</v>
+        <v>0.0159</v>
       </c>
       <c r="E4">
-        <v>-0.0712</v>
-      </c>
-      <c r="F4">
-        <v>0.286</v>
+        <v>0.114</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,82 +853,82 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.00146238449736472</v>
+        <v>0.0002874539738931543</v>
       </c>
       <c r="J4">
-        <v>0.0009975627195376172</v>
+        <v>0.0002017398129607492</v>
       </c>
       <c r="K4">
-        <v>327.3</v>
+        <v>119.3</v>
       </c>
       <c r="L4">
-        <v>0.1805892738909733</v>
+        <v>0.1617846487659344</v>
       </c>
       <c r="M4">
-        <v>231.8075</v>
+        <v>51.20050000000001</v>
       </c>
       <c r="N4">
-        <v>0.04692174564297714</v>
+        <v>0.05309052260472834</v>
       </c>
       <c r="O4">
-        <v>0.708241674304919</v>
+        <v>0.4291743503772004</v>
       </c>
       <c r="P4">
-        <v>159.9075</v>
+        <v>34.20050000000001</v>
       </c>
       <c r="Q4">
-        <v>0.03236797360484181</v>
+        <v>0.03546298216507674</v>
       </c>
       <c r="R4">
-        <v>0.4885655362053162</v>
+        <v>0.2866764459346187</v>
       </c>
       <c r="S4">
-        <v>71.90000000000001</v>
+        <v>17</v>
       </c>
       <c r="T4">
-        <v>0.3101711549453749</v>
+        <v>0.3320280075389889</v>
       </c>
       <c r="U4">
-        <v>35311</v>
+        <v>6159.7</v>
       </c>
       <c r="V4">
-        <v>7.147541647268384</v>
+        <v>6.387080049771879</v>
       </c>
       <c r="W4">
-        <v>0.03081079554547252</v>
+        <v>0.04553435114503817</v>
       </c>
       <c r="X4">
-        <v>0.1502495257700956</v>
+        <v>0.101514508450385</v>
       </c>
       <c r="Y4">
-        <v>-0.119438730224623</v>
+        <v>-0.05598015730534681</v>
       </c>
       <c r="AB4">
-        <v>0.06310851573619219</v>
+        <v>0.04945697465186523</v>
       </c>
       <c r="AD4">
-        <v>21349.3</v>
+        <v>3891.2</v>
       </c>
       <c r="AE4">
-        <v>9.797871684880912</v>
+        <v>7.89015719825594</v>
       </c>
       <c r="AF4">
-        <v>21359.09787168488</v>
+        <v>3899.090157198256</v>
       </c>
       <c r="AG4">
-        <v>-13951.90212831512</v>
+        <v>-2260.609842801744</v>
       </c>
       <c r="AH4">
-        <v>0.812151592819585</v>
+        <v>0.8017061885953177</v>
       </c>
       <c r="AI4">
-        <v>0.73051033313637</v>
+        <v>0.5845721006035304</v>
       </c>
       <c r="AJ4">
-        <v>1.54821550370907</v>
+        <v>1.744015334674099</v>
       </c>
       <c r="AK4">
-        <v>2.297591930425446</v>
+        <v>-4.430047906888119</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -940,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>4631.084598698481</v>
+        <v>2173.854748603352</v>
       </c>
       <c r="AP4">
-        <v>-3026.442977942542</v>
+        <v>-1262.910526704885</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hokuhoku Financial Group, Inc. (TSE:8377)</t>
+          <t>Mebuki Financial Group,Inc. (TSE:7167)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="E5">
-        <v>-0.0578</v>
+        <v>-0.08689999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,82 +972,82 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>1.376018466623857e-05</v>
+        <v>0.0002907629859179205</v>
       </c>
       <c r="J5">
-        <v>8.092183309524447e-06</v>
+        <v>0.0002044576527484173</v>
       </c>
       <c r="K5">
-        <v>115.5</v>
+        <v>192.6</v>
       </c>
       <c r="L5">
-        <v>0.1072921504876916</v>
+        <v>0.1065442274713725</v>
       </c>
       <c r="M5">
-        <v>90.50019999999999</v>
+        <v>178.6474</v>
       </c>
       <c r="N5">
-        <v>0.09535370350858707</v>
+        <v>0.05777916491477732</v>
       </c>
       <c r="O5">
-        <v>0.7835515151515151</v>
+        <v>0.9275565939771547</v>
       </c>
       <c r="P5">
-        <v>31.0002</v>
+        <v>78.2474</v>
       </c>
       <c r="Q5">
-        <v>0.03266273311558318</v>
+        <v>0.02530722209644555</v>
       </c>
       <c r="R5">
-        <v>0.2684</v>
+        <v>0.4062689511941848</v>
       </c>
       <c r="S5">
-        <v>59.5</v>
+        <v>100.4</v>
       </c>
       <c r="T5">
-        <v>0.6574571105920208</v>
+        <v>0.5620009023361101</v>
       </c>
       <c r="U5">
-        <v>27415.9</v>
+        <v>29050.7</v>
       </c>
       <c r="V5">
-        <v>28.88620798651354</v>
+        <v>9.395743717455286</v>
       </c>
       <c r="W5">
-        <v>0.01973954060705497</v>
+        <v>0.03154274484113986</v>
       </c>
       <c r="X5">
-        <v>0.3184047670517111</v>
+        <v>0.1164383442986085</v>
       </c>
       <c r="Y5">
-        <v>-0.2986652264446562</v>
+        <v>-0.08489559945746866</v>
       </c>
       <c r="AB5">
-        <v>0.06289706321083931</v>
+        <v>0.04916077805203826</v>
       </c>
       <c r="AD5">
-        <v>12159.1</v>
+        <v>16534.9</v>
       </c>
       <c r="AE5">
-        <v>0.05093580603397092</v>
+        <v>0.9069387517808749</v>
       </c>
       <c r="AF5">
-        <v>12159.15093580603</v>
+        <v>16535.80693875178</v>
       </c>
       <c r="AG5">
-        <v>-15256.74906419397</v>
+        <v>-12514.89306124822</v>
       </c>
       <c r="AH5">
-        <v>0.92759522192183</v>
+        <v>0.8424726836584493</v>
       </c>
       <c r="AI5">
-        <v>0.7487968367944474</v>
+        <v>0.7308383291484069</v>
       </c>
       <c r="AJ5">
-        <v>1.066335146727578</v>
+        <v>1.328122920170168</v>
       </c>
       <c r="AK5">
-        <v>1.364933625718026</v>
+        <v>1.947875698777287</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1059,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>486364</v>
+        <v>23387.41159830269</v>
       </c>
       <c r="AP5">
-        <v>-610269.9625677586</v>
+        <v>-17701.40461279805</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Chiba Bank, Ltd. (TSE:8331)</t>
+          <t>Hokkoku Financial Holdings, Inc. (TSE:7381)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,13 +1079,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0186</v>
+        <v>0.0176</v>
       </c>
       <c r="E6">
-        <v>0.0134</v>
-      </c>
-      <c r="F6">
-        <v>0.08800000000000001</v>
+        <v>-0.212</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,82 +1091,82 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.0006812870876929253</v>
+        <v>0.001594785136962902</v>
       </c>
       <c r="J6">
-        <v>0.0004718871603067882</v>
+        <v>0.0009806442767660078</v>
       </c>
       <c r="K6">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>0.255069506440505</v>
+        <v>0.04029550033579584</v>
       </c>
       <c r="M6">
-        <v>133.714</v>
+        <v>104.56</v>
       </c>
       <c r="N6">
-        <v>0.02529731161435572</v>
+        <v>0.1331465681905005</v>
       </c>
       <c r="O6">
-        <v>0.334285</v>
+        <v>5.808888888888889</v>
       </c>
       <c r="P6">
-        <v>65.214</v>
+        <v>24.96</v>
       </c>
       <c r="Q6">
-        <v>0.01233781712923548</v>
+        <v>0.03178403158028779</v>
       </c>
       <c r="R6">
-        <v>0.163035</v>
+        <v>1.386666666666667</v>
       </c>
       <c r="S6">
-        <v>68.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="T6">
-        <v>0.5122874194175628</v>
+        <v>0.7612853863810252</v>
       </c>
       <c r="U6">
-        <v>23999</v>
+        <v>8099</v>
       </c>
       <c r="V6">
-        <v>4.540363622604386</v>
+        <v>10.3132560804788</v>
       </c>
       <c r="W6">
-        <v>0.0413393964448119</v>
+        <v>0.01164671627305079</v>
       </c>
       <c r="X6">
-        <v>0.1193266323654678</v>
+        <v>0.133374417485224</v>
       </c>
       <c r="Y6">
-        <v>-0.0779872359206559</v>
+        <v>-0.1217277012121732</v>
       </c>
       <c r="AB6">
-        <v>0.06759316214604376</v>
+        <v>0.05246158401818372</v>
       </c>
       <c r="AD6">
-        <v>14598.3</v>
+        <v>5360.7</v>
       </c>
       <c r="AE6">
-        <v>3.858027945399772</v>
+        <v>2.238047396593359</v>
       </c>
       <c r="AF6">
-        <v>14602.1580279454</v>
+        <v>5362.938047396593</v>
       </c>
       <c r="AG6">
-        <v>-9396.841972054601</v>
+        <v>-2736.061952603407</v>
       </c>
       <c r="AH6">
-        <v>0.7342247720909509</v>
+        <v>0.8722723495827349</v>
       </c>
       <c r="AI6">
-        <v>0.669739030687277</v>
+        <v>0.7802750374594857</v>
       </c>
       <c r="AJ6">
-        <v>2.285701159417367</v>
+        <v>1.402560650186954</v>
       </c>
       <c r="AK6">
-        <v>4.278600487387911</v>
+        <v>2.231949484028552</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1181,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>7933.858695652173</v>
+        <v>4621.293103448276</v>
       </c>
       <c r="AP6">
-        <v>-5106.97933263837</v>
+        <v>-2358.674097071903</v>
       </c>
     </row>
     <row r="7">
@@ -1195,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Senshu Ikeda Holdings, Inc. (TSE:8714)</t>
+          <t>Concordia Financial Group, Ltd. (TSE:7186)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,10 +1198,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0278</v>
+        <v>-0.0134</v>
       </c>
       <c r="E7">
-        <v>0.117</v>
+        <v>0.00501</v>
+      </c>
+      <c r="F7">
+        <v>0.124</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,82 +1213,82 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.0004715451108894873</v>
+        <v>0.001365288241549415</v>
       </c>
       <c r="J7">
-        <v>0.0003941015707799</v>
+        <v>0.001029250172008204</v>
       </c>
       <c r="K7">
-        <v>91.40000000000001</v>
+        <v>432.8</v>
       </c>
       <c r="L7">
-        <v>0.1518524671872404</v>
+        <v>0.2317040526794796</v>
       </c>
       <c r="M7">
-        <v>186.3529</v>
+        <v>201.0791</v>
       </c>
       <c r="N7">
-        <v>0.3465096690219413</v>
+        <v>0.03744629222689858</v>
       </c>
       <c r="O7">
-        <v>2.038871991247265</v>
+        <v>0.4646005083179297</v>
       </c>
       <c r="P7">
-        <v>12.0529</v>
+        <v>160.8791</v>
       </c>
       <c r="Q7">
-        <v>0.02241149126069171</v>
+        <v>0.02995997988751909</v>
       </c>
       <c r="R7">
-        <v>0.1318698030634573</v>
+        <v>0.3717169593345656</v>
       </c>
       <c r="S7">
-        <v>174.3</v>
+        <v>40.19999999999999</v>
       </c>
       <c r="T7">
-        <v>0.93532217636538</v>
+        <v>0.1999213244936942</v>
       </c>
       <c r="U7">
-        <v>5690.1</v>
+        <v>26011.4</v>
       </c>
       <c r="V7">
-        <v>10.58032725920417</v>
+        <v>4.844016536928749</v>
       </c>
       <c r="W7">
-        <v>0.04089485458612976</v>
+        <v>0.05521041956347029</v>
       </c>
       <c r="X7">
-        <v>0.1312848088451343</v>
+        <v>0.09046933440926649</v>
       </c>
       <c r="Y7">
-        <v>-0.09038995425900451</v>
+        <v>-0.0352589148457962</v>
       </c>
       <c r="AB7">
-        <v>0.06318395198819179</v>
+        <v>0.04979829502129457</v>
       </c>
       <c r="AD7">
-        <v>1777.6</v>
+        <v>16516.2</v>
       </c>
       <c r="AE7">
-        <v>32.73088498877809</v>
+        <v>7.348890468049239</v>
       </c>
       <c r="AF7">
-        <v>1810.330884988778</v>
+        <v>16523.54889046805</v>
       </c>
       <c r="AG7">
-        <v>-3879.769115011222</v>
+        <v>-9487.851109531952</v>
       </c>
       <c r="AH7">
-        <v>0.7709667704479044</v>
+        <v>0.7547291633242136</v>
       </c>
       <c r="AI7">
-        <v>0.5389604451461723</v>
+        <v>0.6693856154805831</v>
       </c>
       <c r="AJ7">
-        <v>1.160923090995769</v>
+        <v>2.303966331930815</v>
       </c>
       <c r="AK7">
-        <v>1.664301868975535</v>
+        <v>7.151191388774536</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1300,10 +1297,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>260.2635431918009</v>
+        <v>4108.507462686568</v>
       </c>
       <c r="AP7">
-        <v>-568.0481866780706</v>
+        <v>-2360.161967545262</v>
       </c>
     </row>
     <row r="8">
@@ -1314,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mebuki Financial Group,Inc. (TSE:7167)</t>
+          <t>Yamaguchi Financial Group, Inc. (TSE:8418)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1323,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0107</v>
+        <v>-0.0204</v>
       </c>
       <c r="E8">
-        <v>-0.234</v>
+        <v>-0.0669</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1335,82 +1332,82 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0002593963264870833</v>
+        <v>0.0003234347691676979</v>
       </c>
       <c r="J8">
-        <v>0.000182207541074935</v>
+        <v>0.0002075198693166564</v>
       </c>
       <c r="K8">
-        <v>312.4</v>
+        <v>128.6</v>
       </c>
       <c r="L8">
-        <v>0.1660642143312779</v>
+        <v>0.1437192668752794</v>
       </c>
       <c r="M8">
-        <v>116.3912</v>
+        <v>125.7328</v>
       </c>
       <c r="N8">
-        <v>0.04269983124220412</v>
+        <v>0.06345334342669695</v>
       </c>
       <c r="O8">
-        <v>0.3725710627400768</v>
+        <v>0.9777045101088647</v>
       </c>
       <c r="P8">
-        <v>81.7912</v>
+        <v>54.8328</v>
       </c>
       <c r="Q8">
-        <v>0.03000631007410668</v>
+        <v>0.02767236941710825</v>
       </c>
       <c r="R8">
-        <v>0.2618156209987196</v>
+        <v>0.4263825816485226</v>
       </c>
       <c r="S8">
-        <v>34.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="T8">
-        <v>0.2972733333791558</v>
+        <v>0.5638942264866448</v>
       </c>
       <c r="U8">
-        <v>31438.7</v>
+        <v>11900.8</v>
       </c>
       <c r="V8">
-        <v>11.53375155917529</v>
+        <v>6.00595508453192</v>
       </c>
       <c r="W8">
-        <v>0.03407578699360806</v>
+        <v>0.03065408085430969</v>
       </c>
       <c r="X8">
-        <v>0.2226536493594215</v>
+        <v>0.107790689171219</v>
       </c>
       <c r="Y8">
-        <v>-0.1885778623658134</v>
+        <v>-0.07713660831690936</v>
       </c>
       <c r="AB8">
-        <v>0.06296845591460583</v>
+        <v>0.04931556403877048</v>
       </c>
       <c r="AD8">
-        <v>21745.8</v>
+        <v>9095.799999999999</v>
       </c>
       <c r="AE8">
-        <v>0.9351181530624945</v>
+        <v>2.99295284274372</v>
       </c>
       <c r="AF8">
-        <v>21746.73511815306</v>
+        <v>9098.792952842743</v>
       </c>
       <c r="AG8">
-        <v>-9691.96488184694</v>
+        <v>-2802.007047157256</v>
       </c>
       <c r="AH8">
-        <v>0.8886179961806214</v>
+        <v>0.8211689881817043</v>
       </c>
       <c r="AI8">
-        <v>0.7807699628747455</v>
+        <v>0.6867120856322964</v>
       </c>
       <c r="AJ8">
-        <v>1.391291341251933</v>
+        <v>3.41497011739892</v>
       </c>
       <c r="AK8">
-        <v>2.702900274056688</v>
+        <v>-2.077110218591256</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1419,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>32216</v>
+        <v>10243.01801801802</v>
       </c>
       <c r="AP8">
-        <v>-14358.46649162509</v>
+        <v>-3155.413341393306</v>
       </c>
     </row>
     <row r="9">
@@ -1433,7 +1430,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daishi Hokuetsu Financial Group, Inc. (TSE:7327)</t>
+          <t>Hokuhoku Financial Group, Inc. (TSE:8377)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1441,6 +1438,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.00494</v>
+      </c>
+      <c r="E9">
+        <v>0.0325</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1448,82 +1451,82 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.0002840046462049999</v>
+        <v>1.408899718606629e-05</v>
       </c>
       <c r="J9">
-        <v>0.0001930344079674609</v>
+        <v>1.396038088415906e-05</v>
       </c>
       <c r="K9">
-        <v>137.6</v>
+        <v>188.9</v>
       </c>
       <c r="L9">
-        <v>0.1515919356615622</v>
+        <v>0.1604246284501062</v>
       </c>
       <c r="M9">
-        <v>37.66459999999999</v>
+        <v>93.70079999999999</v>
       </c>
       <c r="N9">
-        <v>0.03814522989669839</v>
+        <v>0.06959875213548243</v>
       </c>
       <c r="O9">
-        <v>0.2737252906976744</v>
+        <v>0.4960338803599788</v>
       </c>
       <c r="P9">
-        <v>37.63659999999999</v>
+        <v>30.9008</v>
       </c>
       <c r="Q9">
-        <v>0.03811687259469313</v>
+        <v>0.02295238802644284</v>
       </c>
       <c r="R9">
-        <v>0.2735218023255814</v>
+        <v>0.1635828480677607</v>
       </c>
       <c r="S9">
-        <v>0.02799999999999869</v>
+        <v>62.79999999999999</v>
       </c>
       <c r="T9">
-        <v>0.0007434036203755966</v>
+        <v>0.67021839728156</v>
       </c>
       <c r="U9">
-        <v>13575.7</v>
+        <v>29134.7</v>
       </c>
       <c r="V9">
-        <v>13.7489366011748</v>
+        <v>21.64057045235089</v>
       </c>
       <c r="W9">
-        <v>0.03492119889348527</v>
+        <v>0.04658676136924139</v>
       </c>
       <c r="X9">
-        <v>0.2123396260563616</v>
+        <v>0.1595593057144615</v>
       </c>
       <c r="Y9">
-        <v>-0.1774184271628764</v>
+        <v>-0.1129725443452201</v>
       </c>
       <c r="AB9">
-        <v>0.06298101415592952</v>
+        <v>0.04873425690187878</v>
       </c>
       <c r="AD9">
-        <v>7362.6</v>
+        <v>12276.9</v>
       </c>
       <c r="AE9">
-        <v>0.9360449131986079</v>
+        <v>0.03205102906703473</v>
       </c>
       <c r="AF9">
-        <v>7363.536044913199</v>
+        <v>12276.93205102907</v>
       </c>
       <c r="AG9">
-        <v>-6212.163955086802</v>
+        <v>-16857.76794897093</v>
       </c>
       <c r="AH9">
-        <v>0.881761757641354</v>
+        <v>0.9011761676702628</v>
       </c>
       <c r="AI9">
-        <v>0.7253046010629918</v>
+        <v>0.7480491640385066</v>
       </c>
       <c r="AJ9">
-        <v>1.18898461413528</v>
+        <v>1.086793848553149</v>
       </c>
       <c r="AK9">
-        <v>1.814637308970932</v>
+        <v>1.325007892668077</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1532,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>16545.16853932584</v>
+        <v>533778.2608695652</v>
       </c>
       <c r="AP9">
-        <v>-13959.91900019506</v>
+        <v>-732946.4325639537</v>
       </c>
     </row>
     <row r="10">
@@ -1546,7 +1549,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Nanto Bank, Ltd. (TSE:8367)</t>
+          <t>Daishi Hokuetsu Financial Group, Inc. (TSE:7327)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1554,12 +1557,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.00046</v>
-      </c>
-      <c r="E10">
-        <v>0.009010000000000001</v>
-      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1567,82 +1564,82 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.001078596855597833</v>
+        <v>0.0001982636766208533</v>
       </c>
       <c r="J10">
-        <v>0.0007374873616337464</v>
+        <v>0.0001445391656090802</v>
       </c>
       <c r="K10">
-        <v>85.40000000000001</v>
+        <v>128.6</v>
       </c>
       <c r="L10">
-        <v>0.16991643454039</v>
+        <v>0.1454093170511081</v>
       </c>
       <c r="M10">
-        <v>28.7854</v>
+        <v>47.765</v>
       </c>
       <c r="N10">
-        <v>0.04664624858207746</v>
+        <v>0.03904602305239925</v>
       </c>
       <c r="O10">
-        <v>0.3370655737704918</v>
+        <v>0.3714230171073095</v>
       </c>
       <c r="P10">
-        <v>17.5854</v>
+        <v>37.665</v>
       </c>
       <c r="Q10">
-        <v>0.02849684005833739</v>
+        <v>0.03078966729338674</v>
       </c>
       <c r="R10">
-        <v>0.2059180327868853</v>
+        <v>0.2928849144634526</v>
       </c>
       <c r="S10">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="T10">
-        <v>0.3890861339429015</v>
+        <v>0.2114518999267246</v>
       </c>
       <c r="U10">
-        <v>8367</v>
+        <v>15623.1</v>
       </c>
       <c r="V10">
-        <v>13.55858045697618</v>
+        <v>12.77127442164637</v>
       </c>
       <c r="W10">
-        <v>0.03179685754709956</v>
+        <v>0.04671098034942429</v>
       </c>
       <c r="X10">
-        <v>0.213995099427894</v>
+        <v>0.156399379835036</v>
       </c>
       <c r="Y10">
-        <v>-0.1821982418807945</v>
+        <v>-0.1096883994856117</v>
       </c>
       <c r="AB10">
-        <v>0.0629788953264636</v>
+        <v>0.04875441547042751</v>
       </c>
       <c r="AD10">
-        <v>4647.6</v>
+        <v>10816.7</v>
       </c>
       <c r="AE10">
-        <v>5.989486101882646</v>
+        <v>0.5532780219825866</v>
       </c>
       <c r="AF10">
-        <v>4653.589486101883</v>
+        <v>10817.25327802198</v>
       </c>
       <c r="AG10">
-        <v>-3713.410513898117</v>
+        <v>-4805.846721978018</v>
       </c>
       <c r="AH10">
-        <v>0.8829185438400019</v>
+        <v>0.8984016787473604</v>
       </c>
       <c r="AI10">
-        <v>0.7227204666425278</v>
+        <v>0.786929481960392</v>
       </c>
       <c r="AJ10">
-        <v>1.199301716423492</v>
+        <v>1.341461003842703</v>
       </c>
       <c r="AK10">
-        <v>1.926032294497305</v>
+        <v>2.560459849874366</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1651,10 +1648,10 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>2671.034482758621</v>
+        <v>37820.62937062937</v>
       </c>
       <c r="AP10">
-        <v>-2134.143973504665</v>
+        <v>-16803.65986705601</v>
       </c>
     </row>
     <row r="11">
@@ -1665,7 +1662,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yamaguchi Financial Group, Inc. (TSE:8418)</t>
+          <t>Resona Holdings, Inc. (TSE:8308)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1674,7 +1671,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0571</v>
+        <v>0.0115</v>
+      </c>
+      <c r="E11">
+        <v>-0.09519999999999999</v>
+      </c>
+      <c r="F11">
+        <v>0.066</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1683,82 +1686,82 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.000377687520382092</v>
+        <v>0.001237292918477332</v>
       </c>
       <c r="J11">
-        <v>0.000377687520382092</v>
+        <v>0.0008925818891271526</v>
       </c>
       <c r="K11">
-        <v>-89.09999999999999</v>
+        <v>1072.8</v>
       </c>
       <c r="L11">
-        <v>-0.1138658146964856</v>
+        <v>0.2058603419492257</v>
       </c>
       <c r="M11">
-        <v>121.74</v>
+        <v>510.0472</v>
       </c>
       <c r="N11">
-        <v>0.08134981623788841</v>
+        <v>0.0430903207819747</v>
       </c>
       <c r="O11">
-        <v>-1.366329966329967</v>
+        <v>0.4754354958985831</v>
       </c>
       <c r="P11">
-        <v>45.84</v>
+        <v>335.3472</v>
       </c>
       <c r="Q11">
-        <v>0.03063147343802206</v>
+        <v>0.02833113959127121</v>
       </c>
       <c r="R11">
-        <v>-0.5144781144781145</v>
+        <v>0.3125906040268456</v>
       </c>
       <c r="S11">
-        <v>75.90000000000001</v>
+        <v>174.7</v>
       </c>
       <c r="T11">
-        <v>0.6234598324297683</v>
+        <v>0.3425173199656816</v>
       </c>
       <c r="U11">
-        <v>13056.8</v>
+        <v>134455.4</v>
       </c>
       <c r="V11">
-        <v>8.724891413297694</v>
+        <v>11.35919639764461</v>
       </c>
       <c r="W11">
-        <v>-0.01471511147811726</v>
+        <v>0.06397786299147797</v>
       </c>
       <c r="X11">
-        <v>0.1492770546664323</v>
+        <v>0.09785976903596069</v>
       </c>
       <c r="Y11">
-        <v>-0.1639921661445495</v>
+        <v>-0.03388190604448273</v>
       </c>
       <c r="AB11">
-        <v>0.06311171789293736</v>
+        <v>0.04955446102953727</v>
       </c>
       <c r="AD11">
-        <v>6392.7</v>
+        <v>43973.7</v>
       </c>
       <c r="AE11">
-        <v>3.872297576505066</v>
+        <v>99.26047706969541</v>
       </c>
       <c r="AF11">
-        <v>6396.572297576505</v>
+        <v>44072.96047706969</v>
       </c>
       <c r="AG11">
-        <v>-6660.227702423495</v>
+        <v>-90382.4395229303</v>
       </c>
       <c r="AH11">
-        <v>0.8104033583400109</v>
+        <v>0.7882888234519936</v>
       </c>
       <c r="AI11">
-        <v>0.6014771279150172</v>
+        <v>0.7161227803298204</v>
       </c>
       <c r="AJ11">
-        <v>1.289810014439307</v>
+        <v>1.150698180090907</v>
       </c>
       <c r="AK11">
-        <v>2.749856120868986</v>
+        <v>1.239617763036062</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1767,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>5974.48598130841</v>
+        <v>1672.003802281369</v>
       </c>
       <c r="AP11">
-        <v>-6224.511871423826</v>
+        <v>-3436.594658666551</v>
       </c>
     </row>
     <row r="12">
@@ -1781,7 +1784,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Shikoku Bank, Ltd. (TSE:8387)</t>
+          <t>The Nanto Bank, Ltd. (TSE:8367)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1790,10 +1793,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0133</v>
+        <v>-0.0268</v>
       </c>
       <c r="E12">
-        <v>-0.05980000000000001</v>
+        <v>-0.211</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1802,82 +1805,82 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.001766696761292689</v>
+        <v>0.001739842534881521</v>
       </c>
       <c r="J12">
-        <v>0.001357942386397331</v>
+        <v>0.001349827833312247</v>
       </c>
       <c r="K12">
-        <v>49.4</v>
+        <v>28</v>
       </c>
       <c r="L12">
-        <v>0.1400623759569039</v>
+        <v>0.06977323697981559</v>
       </c>
       <c r="M12">
-        <v>12.2668</v>
+        <v>17.0648</v>
       </c>
       <c r="N12">
-        <v>0.03962144702842377</v>
+        <v>0.03103255137297691</v>
       </c>
       <c r="O12">
-        <v>0.2483157894736842</v>
+        <v>0.6094571428571429</v>
       </c>
       <c r="P12">
-        <v>12.2598</v>
+        <v>17.0448</v>
       </c>
       <c r="Q12">
-        <v>0.03959883720930232</v>
+        <v>0.0309961811238407</v>
       </c>
       <c r="R12">
-        <v>0.2481740890688259</v>
+        <v>0.6087428571428573</v>
       </c>
       <c r="S12">
-        <v>0.006999999999999673</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="T12">
-        <v>0.0005706459712394164</v>
+        <v>0.001172003187848646</v>
       </c>
       <c r="U12">
-        <v>3704.1</v>
+        <v>7523.3</v>
       </c>
       <c r="V12">
-        <v>11.9641472868217</v>
+        <v>13.68121476632115</v>
       </c>
       <c r="W12">
-        <v>0.03382634894549438</v>
+        <v>0.01568276016578918</v>
       </c>
       <c r="X12">
-        <v>0.09542243123372345</v>
+        <v>0.1311130644403375</v>
       </c>
       <c r="Y12">
-        <v>-0.06159608228822906</v>
+        <v>-0.1154303042745483</v>
       </c>
       <c r="AB12">
-        <v>0.06348105440889307</v>
+        <v>0.04896831124890938</v>
       </c>
       <c r="AD12">
-        <v>478.8</v>
+        <v>3642.7</v>
       </c>
       <c r="AE12">
-        <v>2.934430261460342</v>
+        <v>3.909005953760228</v>
       </c>
       <c r="AF12">
-        <v>481.7344302614604</v>
+        <v>3646.60900595376</v>
       </c>
       <c r="AG12">
-        <v>-3222.365569738539</v>
+        <v>-3876.69099404624</v>
       </c>
       <c r="AH12">
-        <v>0.6087621261497408</v>
+        <v>0.8689625116448376</v>
       </c>
       <c r="AI12">
-        <v>0.3238911306428747</v>
+        <v>0.6681329794937688</v>
       </c>
       <c r="AJ12">
-        <v>1.106290737303583</v>
+        <v>1.165294423660556</v>
       </c>
       <c r="AK12">
-        <v>1.453633895134255</v>
+        <v>1.876976807404172</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1886,10 +1889,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>395.702479338843</v>
+        <v>2461.283783783784</v>
       </c>
       <c r="AP12">
-        <v>-2663.112041106231</v>
+        <v>-2619.385806788</v>
       </c>
     </row>
     <row r="13">
@@ -1900,7 +1903,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Minami-Nippon Bank,Ltd. (FKSE:8554)</t>
+          <t>Senshu Ikeda Holdings, Inc. (TSE:8714)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1909,10 +1912,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0313</v>
+        <v>-0.009679999999999999</v>
       </c>
       <c r="E13">
-        <v>-0.0191</v>
+        <v>0.0442</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1921,82 +1924,82 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.001473066223353013</v>
+        <v>0.0005386761619789051</v>
       </c>
       <c r="J13">
-        <v>0.001158956513961562</v>
+        <v>0.0003911027171124484</v>
       </c>
       <c r="K13">
-        <v>10.7</v>
+        <v>59.6</v>
       </c>
       <c r="L13">
-        <v>0.1095189355168884</v>
+        <v>0.103239217044864</v>
       </c>
       <c r="M13">
-        <v>105.69265</v>
+        <v>30.5706</v>
       </c>
       <c r="N13">
-        <v>2.655594221105528</v>
+        <v>0.04758070038910506</v>
       </c>
       <c r="O13">
-        <v>9.877817757009346</v>
+        <v>0.5129295302013422</v>
       </c>
       <c r="P13">
-        <v>1.39265</v>
+        <v>30.5636</v>
       </c>
       <c r="Q13">
-        <v>0.03499120603015075</v>
+        <v>0.04756980544747081</v>
       </c>
       <c r="R13">
-        <v>0.1301542056074766</v>
+        <v>0.5128120805369127</v>
       </c>
       <c r="S13">
-        <v>104.3</v>
+        <v>0.00700000000000145</v>
       </c>
       <c r="T13">
-        <v>0.9868235870706241</v>
+        <v>0.0002289781685672329</v>
       </c>
       <c r="U13">
-        <v>1201</v>
+        <v>6287.8</v>
       </c>
       <c r="V13">
-        <v>30.17587939698493</v>
+        <v>9.786459143968871</v>
       </c>
       <c r="W13">
-        <v>0.02273210112598258</v>
+        <v>0.03888562667188621</v>
       </c>
       <c r="X13">
-        <v>0.146081882461383</v>
+        <v>0.1046283176509774</v>
       </c>
       <c r="Y13">
-        <v>-0.1233497813354004</v>
+        <v>-0.06574269097909119</v>
       </c>
       <c r="AB13">
-        <v>0.06312267183459894</v>
+        <v>0.04938316620662751</v>
       </c>
       <c r="AD13">
-        <v>163.1</v>
+        <v>2742</v>
       </c>
       <c r="AE13">
-        <v>0.6004071498920531</v>
+        <v>30.59511125844789</v>
       </c>
       <c r="AF13">
-        <v>163.700407149892</v>
+        <v>2772.595111258448</v>
       </c>
       <c r="AG13">
-        <v>-1037.299592850108</v>
+        <v>-3515.204888741552</v>
       </c>
       <c r="AH13">
-        <v>0.8044229957206691</v>
+        <v>0.8118646833928905</v>
       </c>
       <c r="AI13">
-        <v>0.3877315236500333</v>
+        <v>0.6384356250357411</v>
       </c>
       <c r="AJ13">
-        <v>1.039899765659334</v>
+        <v>1.223656806001211</v>
       </c>
       <c r="AK13">
-        <v>1.331921077480266</v>
+        <v>1.807298742069458</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2005,10 +2008,10 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>617.8030303030303</v>
+        <v>426.4385692068429</v>
       </c>
       <c r="AP13">
-        <v>-3929.165124432227</v>
+        <v>-546.68816310133</v>
       </c>
     </row>
     <row r="14">
@@ -2019,7 +2022,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Chikuho Bank, Ltd. (FKSE:8398)</t>
+          <t>Seven Bank, Ltd. (TSE:8410)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2028,10 +2031,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.00257</v>
+        <v>0.0426</v>
       </c>
       <c r="E14">
-        <v>-0.0926</v>
+        <v>0.295</v>
+      </c>
+      <c r="F14">
+        <v>0.159</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2040,82 +2046,82 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.0001107587089851055</v>
+        <v>0.0005689802520587298</v>
       </c>
       <c r="J14">
-        <v>7.160557105205519e-05</v>
+        <v>0.0004620678318150818</v>
       </c>
       <c r="K14">
-        <v>4.64</v>
+        <v>279.2</v>
       </c>
       <c r="L14">
-        <v>0.04059492563429571</v>
+        <v>0.2453211492838942</v>
       </c>
       <c r="M14">
-        <v>2.11068</v>
+        <v>91.37260000000001</v>
       </c>
       <c r="N14">
-        <v>0.03308275862068966</v>
+        <v>0.03673565713826237</v>
       </c>
       <c r="O14">
-        <v>0.4548879310344828</v>
+        <v>0.3272657593123209</v>
       </c>
       <c r="P14">
-        <v>2.10368</v>
+        <v>86.57260000000001</v>
       </c>
       <c r="Q14">
-        <v>0.03297304075235109</v>
+        <v>0.03480585373698388</v>
       </c>
       <c r="R14">
-        <v>0.4533793103448276</v>
+        <v>0.3100737822349571</v>
       </c>
       <c r="S14">
-        <v>0.007000000000000117</v>
+        <v>4.799999999999997</v>
       </c>
       <c r="T14">
-        <v>0.003316466731100933</v>
+        <v>0.0525321595314131</v>
       </c>
       <c r="U14">
-        <v>484.8</v>
+        <v>7388.8</v>
       </c>
       <c r="V14">
-        <v>7.598746081504703</v>
+        <v>2.970610702368029</v>
       </c>
       <c r="W14">
-        <v>0.01318556408070475</v>
+        <v>0.1619113894688007</v>
       </c>
       <c r="X14">
-        <v>0.09478261447021261</v>
+        <v>0.06492781905407558</v>
       </c>
       <c r="Y14">
-        <v>-0.08159705038950786</v>
+        <v>0.09698357041472516</v>
       </c>
       <c r="AB14">
-        <v>0.06882259342890194</v>
+        <v>0.05337866982278527</v>
       </c>
       <c r="AD14">
-        <v>96.7</v>
+        <v>2097.1</v>
       </c>
       <c r="AE14">
-        <v>0.5117013978150122</v>
+        <v>1.012217875659799</v>
       </c>
       <c r="AF14">
-        <v>97.21170139781502</v>
+        <v>2098.11221787566</v>
       </c>
       <c r="AG14">
-        <v>-387.588298602185</v>
+        <v>-5290.687782124341</v>
       </c>
       <c r="AH14">
-        <v>0.6037555069220218</v>
+        <v>0.4575623996674563</v>
       </c>
       <c r="AI14">
-        <v>0.3069406686547063</v>
+        <v>0.5243691420570534</v>
       </c>
       <c r="AJ14">
-        <v>1.197042327580795</v>
+        <v>1.887247927618199</v>
       </c>
       <c r="AK14">
-        <v>2.305861275444826</v>
+        <v>1.561786180137471</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2124,10 +2130,10 @@
         <v>0</v>
       </c>
       <c r="AN14">
-        <v>840.8695652173913</v>
+        <v>2467.176470588235</v>
       </c>
       <c r="AP14">
-        <v>-3370.333031323347</v>
+        <v>-6224.338567205107</v>
       </c>
     </row>
     <row r="15">
@@ -2138,7 +2144,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Resona Holdings, Inc. (TSE:8308)</t>
+          <t>TOMONY Holdings, Inc. (TSE:8600)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2147,13 +2153,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0209</v>
+        <v>0.0334</v>
       </c>
       <c r="E15">
-        <v>-0.06759999999999999</v>
-      </c>
-      <c r="F15">
-        <v>0.193</v>
+        <v>0.0384</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2162,34 +2165,34 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.000854751735519008</v>
+        <v>0.0001653657859427909</v>
       </c>
       <c r="J15">
-        <v>0.0006231147355572129</v>
+        <v>0.0001116219055113839</v>
       </c>
       <c r="K15">
-        <v>772.8</v>
+        <v>96</v>
       </c>
       <c r="L15">
-        <v>0.1463774978691164</v>
+        <v>0.1797416214192099</v>
       </c>
       <c r="M15">
-        <v>342.287</v>
+        <v>13.328</v>
       </c>
       <c r="N15">
-        <v>0.02644041218637993</v>
+        <v>0.02524242424242424</v>
       </c>
       <c r="O15">
-        <v>0.4429179606625259</v>
+        <v>0.1388333333333333</v>
       </c>
       <c r="P15">
-        <v>342.287</v>
+        <v>13.328</v>
       </c>
       <c r="Q15">
-        <v>0.02644041218637993</v>
+        <v>0.02524242424242424</v>
       </c>
       <c r="R15">
-        <v>0.4429179606625259</v>
+        <v>0.1388333333333333</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2198,46 +2201,46 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>144908.6</v>
+        <v>2817.2</v>
       </c>
       <c r="V15">
-        <v>11.19365653194908</v>
+        <v>5.33560606060606</v>
       </c>
       <c r="W15">
-        <v>0.03372316285564671</v>
+        <v>0.05879830954860048</v>
       </c>
       <c r="X15">
-        <v>0.1415814149009501</v>
+        <v>0.07533910787166623</v>
       </c>
       <c r="Y15">
-        <v>-0.1078582520453034</v>
+        <v>-0.01654079832306575</v>
       </c>
       <c r="AB15">
-        <v>0.06313932733499378</v>
+        <v>0.05065447103311479</v>
       </c>
       <c r="AD15">
-        <v>50180</v>
+        <v>921</v>
       </c>
       <c r="AE15">
-        <v>125.436691061637</v>
+        <v>5.108390668639777</v>
       </c>
       <c r="AF15">
-        <v>50305.43669106164</v>
+        <v>926.1083906686398</v>
       </c>
       <c r="AG15">
-        <v>-94603.16330893837</v>
+        <v>-1891.09160933136</v>
       </c>
       <c r="AH15">
-        <v>0.795329836833656</v>
+        <v>0.6368908924614548</v>
       </c>
       <c r="AI15">
-        <v>0.7486046531113183</v>
+        <v>0.3539617110125408</v>
       </c>
       <c r="AJ15">
-        <v>1.158535222891998</v>
+        <v>1.387354742986791</v>
       </c>
       <c r="AK15">
-        <v>1.217392525982761</v>
+        <v>9.418180449017429</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2246,10 +2249,10 @@
         <v>0</v>
       </c>
       <c r="AN15">
-        <v>1695.27027027027</v>
+        <v>829.7297297297297</v>
       </c>
       <c r="AP15">
-        <v>-3196.052814491161</v>
+        <v>-1703.686134532757</v>
       </c>
     </row>
     <row r="16">
@@ -2260,7 +2263,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Bank of Nagoya, Ltd. (TSE:8522)</t>
+          <t>The Shikoku Bank, Ltd. (TSE:8387)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2269,10 +2272,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0393</v>
+        <v>0.0516</v>
       </c>
       <c r="E16">
-        <v>0.096</v>
+        <v>-0.0049</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2281,91 +2284,82 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0.003335402506574764</v>
+        <v>0.0009112428967243175</v>
       </c>
       <c r="J16">
-        <v>0.002399646649257296</v>
+        <v>0.000736713870464043</v>
       </c>
       <c r="K16">
-        <v>67.59999999999999</v>
+        <v>43.9</v>
       </c>
       <c r="L16">
-        <v>0.1312876286657603</v>
+        <v>0.1215393133997785</v>
       </c>
       <c r="M16">
-        <v>25.6669</v>
+        <v>9.764800000000001</v>
       </c>
       <c r="N16">
-        <v>0.05892309458218549</v>
+        <v>0.0343830985915493</v>
       </c>
       <c r="O16">
-        <v>0.3796878698224853</v>
+        <v>0.2224328018223235</v>
       </c>
       <c r="P16">
-        <v>9.5669</v>
+        <v>9.757800000000001</v>
       </c>
       <c r="Q16">
-        <v>0.02196258034894398</v>
+        <v>0.03435845070422536</v>
       </c>
       <c r="R16">
-        <v>0.1415221893491125</v>
+        <v>0.2222733485193622</v>
       </c>
       <c r="S16">
-        <v>16.1</v>
+        <v>0.006999999999999673</v>
       </c>
       <c r="T16">
-        <v>0.6272670248452287</v>
+        <v>0.0007168605603801074</v>
       </c>
       <c r="U16">
-        <v>1640.6</v>
+        <v>1728.1</v>
       </c>
       <c r="V16">
-        <v>3.766299357208448</v>
+        <v>6.084859154929577</v>
       </c>
       <c r="W16">
-        <v>0.0287622856656597</v>
+        <v>0.04369898467051563</v>
       </c>
       <c r="X16">
-        <v>0.1266710438357573</v>
+        <v>0.05716909615914174</v>
       </c>
       <c r="Y16">
-        <v>-0.09790875817009764</v>
-      </c>
-      <c r="Z16">
-        <v>2.503610199016776</v>
-      </c>
-      <c r="AA16">
-        <v>0.006007779825116998</v>
+        <v>-0.01347011148862612</v>
       </c>
       <c r="AB16">
-        <v>0.06320758860751499</v>
-      </c>
-      <c r="AC16">
-        <v>-0.05719980878239799</v>
+        <v>0.05425269998286184</v>
       </c>
       <c r="AD16">
-        <v>1361.7</v>
+        <v>44.3</v>
       </c>
       <c r="AE16">
-        <v>3.163006246823271</v>
+        <v>2.569295328515882</v>
       </c>
       <c r="AF16">
-        <v>1364.863006246823</v>
+        <v>46.86929532851588</v>
       </c>
       <c r="AG16">
-        <v>-275.7369937531766</v>
+        <v>-1681.230704671484</v>
       </c>
       <c r="AH16">
-        <v>0.7580622326098023</v>
+        <v>0.141655016014647</v>
       </c>
       <c r="AI16">
-        <v>0.4528015648993641</v>
+        <v>0.04326252878922829</v>
       </c>
       <c r="AJ16">
-        <v>-1.724833031898872</v>
+        <v>1.203259203401756</v>
       </c>
       <c r="AK16">
-        <v>-0.2007311782433133</v>
+        <v>2.607647956720377</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2374,10 +2368,10 @@
         <v>0</v>
       </c>
       <c r="AN16">
-        <v>579.4468085106383</v>
+        <v>52.55041518386714</v>
       </c>
       <c r="AP16">
-        <v>-117.3348909587986</v>
+        <v>-1994.34247291991</v>
       </c>
     </row>
     <row r="17">
@@ -2388,7 +2382,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Taiko Bank,Ltd. (TSE:8537)</t>
+          <t>The Towa Bank, Ltd. (TSE:8558)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2397,10 +2391,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.0107</v>
+        <v>-0.0518</v>
       </c>
       <c r="E17">
-        <v>-0.141</v>
+        <v>-0.211</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2409,91 +2403,82 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0.0005134116687152076</v>
+        <v>0.0008855232144231277</v>
       </c>
       <c r="J17">
-        <v>0.0003756353728068228</v>
+        <v>0.0006908641465829777</v>
       </c>
       <c r="K17">
-        <v>11.3</v>
+        <v>17.7</v>
       </c>
       <c r="L17">
-        <v>0.08176555716353112</v>
+        <v>0.08596406022340941</v>
       </c>
       <c r="M17">
-        <v>3.27316</v>
+        <v>6.186</v>
       </c>
       <c r="N17">
-        <v>0.03669461883408071</v>
+        <v>0.03888120678818353</v>
       </c>
       <c r="O17">
-        <v>0.2896601769911504</v>
+        <v>0.3494915254237288</v>
       </c>
       <c r="P17">
-        <v>3.27316</v>
+        <v>6.179</v>
       </c>
       <c r="Q17">
-        <v>0.03669461883408071</v>
+        <v>0.03883720930232559</v>
       </c>
       <c r="R17">
-        <v>0.2896601769911504</v>
+        <v>0.3490960451977401</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>0.006999999999999673</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.001131587455544726</v>
       </c>
       <c r="U17">
-        <v>1055</v>
+        <v>1483.1</v>
       </c>
       <c r="V17">
-        <v>11.82735426008969</v>
+        <v>9.321810182275298</v>
       </c>
       <c r="W17">
-        <v>0.01551771491348531</v>
+        <v>0.02166727873668748</v>
       </c>
       <c r="X17">
-        <v>0.2383123686285846</v>
+        <v>0.1064550278024484</v>
       </c>
       <c r="Y17">
-        <v>-0.2227946537150993</v>
-      </c>
-      <c r="Z17">
-        <v>2.245320517954315</v>
-      </c>
-      <c r="AA17">
-        <v>0.0008434218098325776</v>
+        <v>-0.08478774906576096</v>
       </c>
       <c r="AB17">
-        <v>0.06295194880283558</v>
-      </c>
-      <c r="AC17">
-        <v>-0.062108526993003</v>
+        <v>0.04934328346486996</v>
       </c>
       <c r="AD17">
-        <v>779.5</v>
+        <v>710.3</v>
       </c>
       <c r="AE17">
-        <v>2.650232536917791</v>
+        <v>1.68335385075139</v>
       </c>
       <c r="AF17">
-        <v>782.1502325369178</v>
+        <v>711.9833538507513</v>
       </c>
       <c r="AG17">
-        <v>-272.8497674630822</v>
+        <v>-771.1166461492486</v>
       </c>
       <c r="AH17">
-        <v>0.8976301415100377</v>
+        <v>0.8173538740045081</v>
       </c>
       <c r="AI17">
-        <v>0.6032083386177534</v>
+        <v>0.4890723279445774</v>
       </c>
       <c r="AJ17">
-        <v>1.485707121943028</v>
+        <v>1.259960249449165</v>
       </c>
       <c r="AK17">
-        <v>-1.129110303758545</v>
+        <v>28.22881849902568</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2502,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="AN17">
-        <v>1297.004991680532</v>
+        <v>1368.59344894027</v>
       </c>
       <c r="AP17">
-        <v>-453.9929575092883</v>
+        <v>-1485.773884680633</v>
       </c>
     </row>
     <row r="18">
@@ -2516,7 +2501,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Towa Bank, Ltd. (TSE:8558)</t>
+          <t>The Chikuho Bank, Ltd. (FKSE:8398)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2525,10 +2510,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.0742</v>
+        <v>-0.0206</v>
       </c>
       <c r="E18">
-        <v>-0.233</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2537,91 +2522,82 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0.0006292368813031812</v>
+        <v>7.693823683002852e-05</v>
       </c>
       <c r="J18">
-        <v>0.0004557509233406442</v>
+        <v>5.704756159928506e-05</v>
       </c>
       <c r="K18">
-        <v>17.6</v>
+        <v>3.84</v>
       </c>
       <c r="L18">
-        <v>0.0856447688564477</v>
+        <v>0.03484573502722323</v>
       </c>
       <c r="M18">
-        <v>6.383699999999999</v>
+        <v>2.0438</v>
       </c>
       <c r="N18">
-        <v>0.0405571791613723</v>
+        <v>0.03307119741100324</v>
       </c>
       <c r="O18">
-        <v>0.3627102272727272</v>
+        <v>0.5322395833333333</v>
       </c>
       <c r="P18">
-        <v>6.383699999999999</v>
+        <v>2.0368</v>
       </c>
       <c r="Q18">
-        <v>0.0405571791613723</v>
+        <v>0.032957928802589</v>
       </c>
       <c r="R18">
-        <v>0.3627102272727272</v>
+        <v>0.5304166666666666</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>0.007000000000000117</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>0.00342499266073007</v>
       </c>
       <c r="U18">
-        <v>2781.5</v>
+        <v>590.5</v>
       </c>
       <c r="V18">
-        <v>17.6715374841169</v>
+        <v>9.555016181229774</v>
       </c>
       <c r="W18">
-        <v>0.01468379776405807</v>
+        <v>0.01783557826288899</v>
       </c>
       <c r="X18">
-        <v>0.3063598101474917</v>
+        <v>0.07221402190033779</v>
       </c>
       <c r="Y18">
-        <v>-0.2916760123834336</v>
-      </c>
-      <c r="Z18">
-        <v>1.624589931012118</v>
-      </c>
-      <c r="AA18">
-        <v>0.0007404083611086863</v>
+        <v>-0.0543784436374488</v>
       </c>
       <c r="AB18">
-        <v>0.06290317008478591</v>
-      </c>
-      <c r="AC18">
-        <v>-0.06216276172367722</v>
+        <v>0.0544572776143584</v>
       </c>
       <c r="AD18">
-        <v>1918.6</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AE18">
-        <v>2.193459104460981</v>
+        <v>0.4076070315066543</v>
       </c>
       <c r="AF18">
-        <v>1920.793459104461</v>
+        <v>91.50760703150665</v>
       </c>
       <c r="AG18">
-        <v>-860.7065408955391</v>
+        <v>-498.9923929684933</v>
       </c>
       <c r="AH18">
-        <v>0.9242611416610718</v>
+        <v>0.5968888876642676</v>
       </c>
       <c r="AI18">
-        <v>0.7006631801521597</v>
+        <v>0.2825114478481688</v>
       </c>
       <c r="AJ18">
-        <v>1.223799994522415</v>
+        <v>1.141356530886515</v>
       </c>
       <c r="AK18">
-        <v>21.46050299220078</v>
+        <v>1.87174280335698</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2630,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="AN18">
-        <v>3377.816901408451</v>
+        <v>1012.222222222222</v>
       </c>
       <c r="AP18">
-        <v>-1515.328417069611</v>
+        <v>-5544.359921872148</v>
       </c>
     </row>
     <row r="19">
@@ -2644,7 +2620,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Hyakugo Bank, Ltd. (TSE:8368)</t>
+          <t>The Minami-Nippon Bank,Ltd. (FKSE:8554)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2653,10 +2629,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0358</v>
+        <v>-0.0219</v>
       </c>
       <c r="E19">
-        <v>0.04940000000000001</v>
+        <v>0.428</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2665,91 +2641,82 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.001825374268045771</v>
+        <v>0.001240887071892579</v>
       </c>
       <c r="J19">
-        <v>0.001300009574158882</v>
+        <v>0.001057235785252477</v>
       </c>
       <c r="K19">
-        <v>97.09999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="L19">
-        <v>0.1469653397911306</v>
+        <v>0.1371918542336549</v>
       </c>
       <c r="M19">
-        <v>20.0344</v>
+        <v>1.96997</v>
       </c>
       <c r="N19">
-        <v>0.02831317128321085</v>
+        <v>0.05197810026385225</v>
       </c>
       <c r="O19">
-        <v>0.2063274974253347</v>
+        <v>0.15390390625</v>
       </c>
       <c r="P19">
-        <v>20.0344</v>
+        <v>1.32097</v>
       </c>
       <c r="Q19">
-        <v>0.02831317128321085</v>
+        <v>0.03485408970976254</v>
       </c>
       <c r="R19">
-        <v>0.2063274974253347</v>
+        <v>0.10320078125</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>0.649</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.3294466413194109</v>
       </c>
       <c r="U19">
-        <v>9905.4</v>
+        <v>999.5</v>
       </c>
       <c r="V19">
-        <v>13.99858677218768</v>
+        <v>26.37203166226913</v>
       </c>
       <c r="W19">
-        <v>0.02656198708830288</v>
+        <v>0.04951644100580271</v>
       </c>
       <c r="X19">
-        <v>0.2773942206821273</v>
+        <v>0.05540294847527822</v>
       </c>
       <c r="Y19">
-        <v>-0.2508322335938244</v>
-      </c>
-      <c r="Z19">
-        <v>0.2731215028247424</v>
-      </c>
-      <c r="AA19">
-        <v>0.0003550605685808273</v>
+        <v>-0.005886507469475506</v>
       </c>
       <c r="AB19">
-        <v>0.0629204450242119</v>
-      </c>
-      <c r="AC19">
-        <v>-0.06256538445563108</v>
+        <v>0.05520582775964285</v>
       </c>
       <c r="AD19">
-        <v>7594</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>6.469876105510796</v>
+        <v>0.4011261809621121</v>
       </c>
       <c r="AF19">
-        <v>7600.469876105511</v>
+        <v>0.4011261809621121</v>
       </c>
       <c r="AG19">
-        <v>-2304.930123894489</v>
+        <v>-999.0988738190379</v>
       </c>
       <c r="AH19">
-        <v>0.9148297967455596</v>
+        <v>0.01047296048337856</v>
       </c>
       <c r="AI19">
-        <v>0.7408536999838389</v>
+        <v>0.001509689427093039</v>
       </c>
       <c r="AJ19">
-        <v>1.44298920393161</v>
+        <v>1.039429925515222</v>
       </c>
       <c r="AK19">
-        <v>-6.517179662784895</v>
+        <v>1.361543209543581</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2758,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="AN19">
-        <v>3037.6</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>-921.9720495577956</v>
+        <v>-5097.443233770601</v>
       </c>
     </row>
     <row r="20">
@@ -2772,7 +2739,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nishi-Nippon Financial Holdings, Inc. (TSE:7189)</t>
+          <t>The Hyakugo Bank, Ltd. (TSE:8368)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2781,10 +2748,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.004699999999999999</v>
+        <v>0.0344</v>
       </c>
       <c r="E20">
-        <v>0.036</v>
+        <v>0.0539</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2793,91 +2760,91 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0.001658177579771943</v>
+        <v>0.004643789127052766</v>
       </c>
       <c r="J20">
-        <v>0.001131599066703761</v>
+        <v>0.00330139365325743</v>
       </c>
       <c r="K20">
-        <v>152.6</v>
+        <v>102.7</v>
       </c>
       <c r="L20">
-        <v>0.1688053097345133</v>
+        <v>0.1548085619535725</v>
       </c>
       <c r="M20">
-        <v>58.5665</v>
+        <v>23.8384</v>
       </c>
       <c r="N20">
-        <v>0.05588406488549618</v>
+        <v>0.02481099084096586</v>
       </c>
       <c r="O20">
-        <v>0.3837909567496723</v>
+        <v>0.2321168451801363</v>
       </c>
       <c r="P20">
-        <v>37.1665</v>
+        <v>23.8384</v>
       </c>
       <c r="Q20">
-        <v>0.03546421755725191</v>
+        <v>0.02481099084096586</v>
       </c>
       <c r="R20">
-        <v>0.2435550458715596</v>
+        <v>0.2321168451801363</v>
       </c>
       <c r="S20">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>0.3653966004456473</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>16905.1</v>
+        <v>7891.3</v>
       </c>
       <c r="V20">
-        <v>16.13082061068702</v>
+        <v>8.21325978351374</v>
       </c>
       <c r="W20">
-        <v>0.0306974311520589</v>
+        <v>0.03862935379523057</v>
       </c>
       <c r="X20">
-        <v>0.3394396757344345</v>
+        <v>0.1371245397235903</v>
       </c>
       <c r="Y20">
-        <v>-0.3087422445823755</v>
+        <v>-0.09849518592835968</v>
       </c>
       <c r="Z20">
-        <v>0.2532564012499071</v>
+        <v>1.867435439593006</v>
       </c>
       <c r="AA20">
-        <v>0.0002865847072911481</v>
+        <v>0.006165139508140348</v>
       </c>
       <c r="AB20">
-        <v>0.06288759567462625</v>
+        <v>0.04890695269154664</v>
       </c>
       <c r="AC20">
-        <v>-0.0626010109673351</v>
+        <v>-0.04274181318340629</v>
       </c>
       <c r="AD20">
-        <v>14535.3</v>
+        <v>6868.5</v>
       </c>
       <c r="AE20">
-        <v>3.605037339430821</v>
+        <v>8.04655146556598</v>
       </c>
       <c r="AF20">
-        <v>14538.90503733943</v>
+        <v>6876.546551465566</v>
       </c>
       <c r="AG20">
-        <v>-2366.194962660569</v>
+        <v>-1014.753448534434</v>
       </c>
       <c r="AH20">
-        <v>0.9327640735932214</v>
+        <v>0.8774074881478435</v>
       </c>
       <c r="AI20">
-        <v>0.8051046040487676</v>
+        <v>0.7073365382508267</v>
       </c>
       <c r="AJ20">
-        <v>1.795026555013362</v>
+        <v>18.80794418334168</v>
       </c>
       <c r="AK20">
-        <v>-2.051664465213093</v>
+        <v>-0.5543748041820512</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2886,10 +2853,10 @@
         <v>0</v>
       </c>
       <c r="AN20">
-        <v>6547.432432432432</v>
+        <v>1464.498933901919</v>
       </c>
       <c r="AP20">
-        <v>-1065.85358678404</v>
+        <v>-216.3653408388985</v>
       </c>
     </row>
     <row r="21">
@@ -2900,7 +2867,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shizuoka Financial Group,Inc. (TSE:5831)</t>
+          <t>Nishi-Nippon Financial Holdings, Inc. (TSE:7189)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2909,13 +2876,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.0146</v>
+        <v>0.0267</v>
       </c>
       <c r="E21">
-        <v>0.0126</v>
-      </c>
-      <c r="F21">
-        <v>0.0726</v>
+        <v>0.0513</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2924,91 +2888,91 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0.002430374594400147</v>
+        <v>0.001389007780331748</v>
       </c>
       <c r="J21">
-        <v>0.001750825137784087</v>
+        <v>0.001058159249788357</v>
       </c>
       <c r="K21">
-        <v>292.5</v>
+        <v>187.3</v>
       </c>
       <c r="L21">
-        <v>0.1718061674008811</v>
+        <v>0.1842234680830137</v>
       </c>
       <c r="M21">
-        <v>111.1474</v>
+        <v>66.3261</v>
       </c>
       <c r="N21">
-        <v>0.024625</v>
+        <v>0.04063352324940268</v>
       </c>
       <c r="O21">
-        <v>0.3799911111111112</v>
+        <v>0.354116924719701</v>
       </c>
       <c r="P21">
-        <v>111.1474</v>
+        <v>49.52609999999999</v>
       </c>
       <c r="Q21">
-        <v>0.024625</v>
+        <v>0.03034129755559639</v>
       </c>
       <c r="R21">
-        <v>0.3799911111111112</v>
+        <v>0.2644212493326214</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>0.2532939521545818</v>
       </c>
       <c r="U21">
-        <v>7801.4</v>
+        <v>17164.4</v>
       </c>
       <c r="V21">
-        <v>1.728420772775611</v>
+        <v>10.5154689701648</v>
       </c>
       <c r="W21">
-        <v>0.02896412409518057</v>
+        <v>0.05412669055600509</v>
       </c>
       <c r="X21">
-        <v>0.1065325293966759</v>
+        <v>0.1866015507987786</v>
       </c>
       <c r="Y21">
-        <v>-0.07756840530149532</v>
+        <v>-0.1324748602427735</v>
       </c>
       <c r="Z21">
-        <v>0.3964547111377397</v>
+        <v>0.9299462626776552</v>
       </c>
       <c r="AA21">
-        <v>0.0006941228742528833</v>
+        <v>0.0009840312396584743</v>
       </c>
       <c r="AB21">
-        <v>0.06335211669862609</v>
+        <v>0.04859824076010516</v>
       </c>
       <c r="AC21">
-        <v>-0.0626579938243732</v>
+        <v>-0.04761420952044668</v>
       </c>
       <c r="AD21">
-        <v>9544.4</v>
+        <v>18742.4</v>
       </c>
       <c r="AE21">
-        <v>9.911436265168742</v>
+        <v>2.688978948683559</v>
       </c>
       <c r="AF21">
-        <v>9554.311436265169</v>
+        <v>18745.08897894869</v>
       </c>
       <c r="AG21">
-        <v>1752.911436265169</v>
+        <v>1580.688978948685</v>
       </c>
       <c r="AH21">
-        <v>0.6791563537736987</v>
+        <v>0.9198965087388633</v>
       </c>
       <c r="AI21">
-        <v>0.5545768305255646</v>
+        <v>0.8392851552637365</v>
       </c>
       <c r="AJ21">
-        <v>0.2797268391023477</v>
+        <v>0.4919683787604832</v>
       </c>
       <c r="AK21">
-        <v>0.1859515323150346</v>
+        <v>0.3057313737243904</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3017,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="AN21">
-        <v>1559.542483660131</v>
+        <v>9611.48717948718</v>
       </c>
       <c r="AP21">
-        <v>286.4234372982302</v>
+        <v>810.6097327941974</v>
       </c>
     </row>
     <row r="22">
@@ -3031,7 +2995,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Miyazaki Bank, Ltd. (TSE:8393)</t>
+          <t>Fukuoka Financial Group, Inc. (TSE:8354)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3040,10 +3004,13 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0351</v>
+        <v>0.0578</v>
       </c>
       <c r="E22">
-        <v>0.0179</v>
+        <v>-0.0882</v>
+      </c>
+      <c r="F22">
+        <v>0.354</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3052,97 +3019,103 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>0.0001190337335996922</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>8.081908418918844e-05</v>
       </c>
       <c r="K22">
-        <v>65.8</v>
+        <v>205.4</v>
       </c>
       <c r="L22">
-        <v>0.1604095563139932</v>
+        <v>0.1075505288511886</v>
       </c>
       <c r="M22">
-        <v>11.9683</v>
+        <v>126.594</v>
       </c>
       <c r="N22">
-        <v>0.03688228043143297</v>
+        <v>0.02857458862830959</v>
       </c>
       <c r="O22">
-        <v>0.1818890577507599</v>
+        <v>0.6163291139240505</v>
       </c>
       <c r="P22">
-        <v>11.9543</v>
+        <v>126.5</v>
       </c>
       <c r="Q22">
-        <v>0.03683913713405239</v>
+        <v>0.02855337110353701</v>
       </c>
       <c r="R22">
-        <v>0.1816762917933131</v>
+        <v>0.6158714703018501</v>
       </c>
       <c r="S22">
-        <v>0.01399999999999935</v>
+        <v>0.09399999999999409</v>
       </c>
       <c r="T22">
-        <v>0.001169756774144979</v>
+        <v>0.0007425312416069806</v>
       </c>
       <c r="U22">
-        <v>5648.4</v>
+        <v>55648.9</v>
       </c>
       <c r="V22">
-        <v>17.40647149460709</v>
+        <v>12.56097781188633</v>
       </c>
       <c r="W22">
-        <v>0.0453168044077135</v>
+        <v>0.03427846664775287</v>
       </c>
       <c r="X22">
-        <v>0.3293301334129327</v>
+        <v>0.2176192903649311</v>
       </c>
       <c r="Y22">
-        <v>-0.2840133290052192</v>
+        <v>-0.1833408237171782</v>
       </c>
       <c r="Z22">
-        <v>1.954263935207245</v>
+        <v>0.2295448322633919</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.855160312388821e-05</v>
       </c>
       <c r="AB22">
-        <v>0.06289197113911922</v>
+        <v>0.04849435472529225</v>
       </c>
       <c r="AC22">
-        <v>-0.06289197113911922</v>
+        <v>-0.04847580312216836</v>
       </c>
       <c r="AD22">
-        <v>4336.2</v>
+        <v>62893</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.043346877856539</v>
       </c>
       <c r="AF22">
-        <v>4336.2</v>
+        <v>62894.04334687786</v>
       </c>
       <c r="AG22">
-        <v>-1312.2</v>
+        <v>7245.143346877856</v>
       </c>
       <c r="AH22">
-        <v>0.9303752655180553</v>
+        <v>0.9341946793721613</v>
       </c>
       <c r="AI22">
-        <v>0.8020197536344467</v>
+        <v>0.9127838757181667</v>
       </c>
       <c r="AJ22">
-        <v>1.328541054976207</v>
+        <v>0.6205454586711937</v>
       </c>
       <c r="AK22">
-        <v>5.426799007444174</v>
+        <v>0.5466117161563956</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
         <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>144250</v>
+      </c>
+      <c r="AP22">
+        <v>16617.30125430701</v>
       </c>
     </row>
     <row r="23">
@@ -3153,7 +3126,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Bank Of Kochi, Ltd. (TSE:8416)</t>
+          <t>The Bank of Nagoya, Ltd. (TSE:8522)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3162,10 +3135,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.0201</v>
+        <v>0.0667</v>
       </c>
       <c r="E23">
-        <v>-0.114</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3174,97 +3147,103 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.003096305062398487</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>0.002212815110644097</v>
       </c>
       <c r="K23">
-        <v>7.56</v>
+        <v>54.1</v>
       </c>
       <c r="L23">
-        <v>0.05331452750352609</v>
+        <v>0.1071499306793424</v>
       </c>
       <c r="M23">
-        <v>1.8783</v>
+        <v>22.4479</v>
       </c>
       <c r="N23">
-        <v>0.03446422018348624</v>
+        <v>0.03486240099394316</v>
       </c>
       <c r="O23">
-        <v>0.248452380952381</v>
+        <v>0.4149334565619224</v>
       </c>
       <c r="P23">
-        <v>1.7473</v>
+        <v>15.6479</v>
       </c>
       <c r="Q23">
-        <v>0.03206055045871559</v>
+        <v>0.02430175493088989</v>
       </c>
       <c r="R23">
-        <v>0.2311243386243386</v>
+        <v>0.2892402957486137</v>
       </c>
       <c r="S23">
-        <v>0.131</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="T23">
-        <v>0.06974391737209179</v>
+        <v>0.302923658783227</v>
       </c>
       <c r="U23">
-        <v>806.1</v>
+        <v>3621.6</v>
       </c>
       <c r="V23">
-        <v>14.7908256880734</v>
+        <v>5.624475850287312</v>
       </c>
       <c r="W23">
-        <v>0.01129200896191187</v>
+        <v>0.03279980599005699</v>
       </c>
       <c r="X23">
-        <v>0.3206539043897116</v>
+        <v>0.09966811307894913</v>
       </c>
       <c r="Y23">
-        <v>-0.3093618954277998</v>
+        <v>-0.06686830708889213</v>
       </c>
       <c r="Z23">
-        <v>0.7279260780287476</v>
+        <v>0.36761885078331</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>0.000813472547970926</v>
       </c>
       <c r="AB23">
-        <v>0.06289598196891787</v>
+        <v>0.04950462984469772</v>
       </c>
       <c r="AC23">
-        <v>-0.06289598196891787</v>
+        <v>-0.04869115729672679</v>
       </c>
       <c r="AD23">
-        <v>704.4</v>
+        <v>2496.4</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>2.933377869975019</v>
       </c>
       <c r="AF23">
-        <v>704.4</v>
+        <v>2499.333377869975</v>
       </c>
       <c r="AG23">
-        <v>-101.7</v>
+        <v>-1122.266622130025</v>
       </c>
       <c r="AH23">
-        <v>0.9281855316906048</v>
+        <v>0.795147250429002</v>
       </c>
       <c r="AI23">
-        <v>0.5912868295139764</v>
+        <v>0.5882814504620956</v>
       </c>
       <c r="AJ23">
-        <v>2.154661016949151</v>
+        <v>2.346038728899822</v>
       </c>
       <c r="AK23">
-        <v>-0.2640186915887852</v>
+        <v>-1.790089125487238</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>1161.116279069768</v>
+      </c>
+      <c r="AP23">
+        <v>-521.9844754093139</v>
       </c>
     </row>
     <row r="24">
@@ -3275,7 +3254,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fukuoka Financial Group, Inc. (TSE:8354)</t>
+          <t>The Taiko Bank,Ltd. (TSE:8537)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3284,10 +3263,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.0426</v>
-      </c>
-      <c r="F24">
-        <v>0.116</v>
+        <v>-0.0233</v>
+      </c>
+      <c r="E24">
+        <v>-0.111</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3296,91 +3275,91 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0.0001324284176265434</v>
+        <v>0.0007288408452428655</v>
       </c>
       <c r="J24">
-        <v>9.542208585380046e-05</v>
+        <v>0.0005285370325292668</v>
       </c>
       <c r="K24">
-        <v>393.5</v>
+        <v>10.2</v>
       </c>
       <c r="L24">
-        <v>0.2103040991929881</v>
+        <v>0.08717948717948718</v>
       </c>
       <c r="M24">
-        <v>168.4007</v>
+        <v>3.1892</v>
       </c>
       <c r="N24">
-        <v>0.03937079466018282</v>
+        <v>0.03695480880648899</v>
       </c>
       <c r="O24">
-        <v>0.4279560355781448</v>
+        <v>0.3126666666666667</v>
       </c>
       <c r="P24">
-        <v>129.7007</v>
+        <v>3.1892</v>
       </c>
       <c r="Q24">
-        <v>0.03032303088396885</v>
+        <v>0.03695480880648899</v>
       </c>
       <c r="R24">
-        <v>0.329607878017789</v>
+        <v>0.3126666666666667</v>
       </c>
       <c r="S24">
-        <v>38.69999999999999</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>0.2298090209838795</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>46597.3</v>
+        <v>879.3</v>
       </c>
       <c r="V24">
-        <v>10.89409206742571</v>
+        <v>10.18887601390498</v>
       </c>
       <c r="W24">
-        <v>0.04492162973617818</v>
+        <v>0.01995305164319249</v>
       </c>
       <c r="X24">
-        <v>0.2912052348156558</v>
+        <v>0.1286025600809925</v>
       </c>
       <c r="Y24">
-        <v>-0.2462836050794776</v>
+        <v>-0.1086495084378</v>
       </c>
       <c r="Z24">
-        <v>0.1564657709221705</v>
+        <v>0.4910939315790364</v>
       </c>
       <c r="AA24">
-        <v>1.493029022611643e-05</v>
+        <v>0.0002595613292899147</v>
       </c>
       <c r="AB24">
-        <v>0.06291170164625653</v>
+        <v>0.048996512204737</v>
       </c>
       <c r="AC24">
-        <v>-0.06289677135603042</v>
+        <v>-0.04873695087544708</v>
       </c>
       <c r="AD24">
-        <v>48924.1</v>
+        <v>550.8</v>
       </c>
       <c r="AE24">
-        <v>1.026065938894873</v>
+        <v>2.543628105532924</v>
       </c>
       <c r="AF24">
-        <v>48925.12606593889</v>
+        <v>553.3436281055328</v>
       </c>
       <c r="AG24">
-        <v>2327.826065938891</v>
+        <v>-325.9563718944671</v>
       </c>
       <c r="AH24">
-        <v>0.9196032903706547</v>
+        <v>0.8650811229753053</v>
       </c>
       <c r="AI24">
-        <v>0.8907506476510439</v>
+        <v>0.5308139578838834</v>
       </c>
       <c r="AJ24">
-        <v>0.3524271971042237</v>
+        <v>1.360098917119559</v>
       </c>
       <c r="AK24">
-        <v>0.2795037198515932</v>
+        <v>-1.99797182200469</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3389,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="AN24">
-        <v>108000.2207505519</v>
+        <v>927.2727272727273</v>
       </c>
       <c r="AP24">
-        <v>5138.688887282319</v>
+        <v>-548.7481008324362</v>
       </c>
     </row>
     <row r="25">
@@ -3403,7 +3382,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tokyo Kiraboshi Financial Group, Inc. (TSE:7173)</t>
+          <t>The Shimizu Bank, Ltd. (TSE:8364)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3412,10 +3391,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.0645</v>
+        <v>-0.0188</v>
       </c>
       <c r="E25">
-        <v>0.266</v>
+        <v>-0.433</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3424,103 +3403,97 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.000127024580689681</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>8.834722438993838e-05</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>152.3</v>
+        <v>1.14</v>
       </c>
       <c r="L25">
-        <v>0.204347242721052</v>
+        <v>0.006884057971014493</v>
       </c>
       <c r="M25">
-        <v>12.8411</v>
+        <v>7.6045</v>
       </c>
       <c r="N25">
-        <v>0.02154185539339037</v>
+        <v>0.0603531746031746</v>
       </c>
       <c r="O25">
-        <v>0.0843145108338805</v>
+        <v>6.67061403508772</v>
       </c>
       <c r="P25">
-        <v>9.3611</v>
+        <v>6.9345</v>
       </c>
       <c r="Q25">
-        <v>0.01570390874014427</v>
+        <v>0.05503571428571429</v>
       </c>
       <c r="R25">
-        <v>0.06146487196323046</v>
+        <v>6.082894736842106</v>
       </c>
       <c r="S25">
-        <v>3.48</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="T25">
-        <v>0.2710048204593065</v>
+        <v>0.08810572687224669</v>
       </c>
       <c r="U25">
-        <v>5942.4</v>
+        <v>1001</v>
       </c>
       <c r="V25">
-        <v>9.968797181680925</v>
+        <v>7.944444444444445</v>
       </c>
       <c r="W25">
-        <v>0.05290215012678454</v>
+        <v>0.0022265625</v>
       </c>
       <c r="X25">
-        <v>0.2607428083995365</v>
+        <v>0.1549402200751308</v>
       </c>
       <c r="Y25">
-        <v>-0.207840658272752</v>
+        <v>-0.1527136575751308</v>
       </c>
       <c r="Z25">
-        <v>0.3673407066846062</v>
+        <v>0.3303411131059245</v>
       </c>
       <c r="AA25">
-        <v>3.245353184102344e-05</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.0629324735425887</v>
+        <v>0.04876411113525998</v>
       </c>
       <c r="AC25">
-        <v>-0.06290002001074768</v>
+        <v>-0.04876411113525998</v>
       </c>
       <c r="AD25">
-        <v>5901.5</v>
+        <v>1098.1</v>
       </c>
       <c r="AE25">
-        <v>0.3066429000599038</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>5901.80664290006</v>
+        <v>1098.1</v>
       </c>
       <c r="AG25">
-        <v>-40.59335709993957</v>
+        <v>97.09999999999991</v>
       </c>
       <c r="AH25">
-        <v>0.9082627632621763</v>
+        <v>0.8970672330691937</v>
       </c>
       <c r="AI25">
-        <v>0.7330975433831868</v>
+        <v>0.6937705332322466</v>
       </c>
       <c r="AJ25">
-        <v>-0.07307447645993785</v>
+        <v>0.4352308381891526</v>
       </c>
       <c r="AK25">
-        <v>-0.01925583662318738</v>
+        <v>0.1668958404950153</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>37830.1282051282</v>
-      </c>
-      <c r="AP25">
-        <v>-260.2138275637152</v>
       </c>
     </row>
     <row r="26">
@@ -3531,7 +3504,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kyushu Financial Group,Inc. (TSE:7180)</t>
+          <t>Hirogin Holdings, Inc. (TSE:7337)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3540,10 +3513,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.0382</v>
+        <v>0.036</v>
       </c>
       <c r="E26">
-        <v>0.0234</v>
+        <v>-0.035</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3558,85 +3531,85 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>154.2</v>
+        <v>127.6</v>
       </c>
       <c r="L26">
-        <v>0.1175125743026978</v>
+        <v>0.1362811064829649</v>
       </c>
       <c r="M26">
-        <v>53.70580000000001</v>
+        <v>91.38329999999999</v>
       </c>
       <c r="N26">
-        <v>0.0360611025313906</v>
+        <v>0.04613454159935379</v>
       </c>
       <c r="O26">
-        <v>0.3482866407263295</v>
+        <v>0.7161700626959248</v>
       </c>
       <c r="P26">
-        <v>35.90580000000001</v>
+        <v>55.9833</v>
       </c>
       <c r="Q26">
-        <v>0.02410917880883637</v>
+        <v>0.02826297455573506</v>
       </c>
       <c r="R26">
-        <v>0.2328521400778211</v>
+        <v>0.4387405956112853</v>
       </c>
       <c r="S26">
-        <v>17.8</v>
+        <v>35.39999999999999</v>
       </c>
       <c r="T26">
-        <v>0.3314353384550645</v>
+        <v>0.3873793132880953</v>
       </c>
       <c r="U26">
-        <v>12922.6</v>
+        <v>17951.4</v>
       </c>
       <c r="V26">
-        <v>8.676962331296583</v>
+        <v>9.062701938610664</v>
       </c>
       <c r="W26">
-        <v>0.0246763430363744</v>
+        <v>0.0392712052197464</v>
       </c>
       <c r="X26">
-        <v>0.2369684499228159</v>
+        <v>0.1489043808115999</v>
       </c>
       <c r="Y26">
-        <v>-0.2122921068864415</v>
+        <v>-0.1096331755918535</v>
       </c>
       <c r="Z26">
-        <v>0.3977689532874598</v>
+        <v>0.5845663982019101</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.06295326001005078</v>
+        <v>0.04880707867266276</v>
       </c>
       <c r="AC26">
-        <v>-0.06295326001005078</v>
+        <v>-0.04880707867266276</v>
       </c>
       <c r="AD26">
-        <v>12957.9</v>
+        <v>16217.3</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>12957.9</v>
+        <v>16217.3</v>
       </c>
       <c r="AG26">
-        <v>35.29999999999927</v>
+        <v>-1734.100000000002</v>
       </c>
       <c r="AH26">
-        <v>0.8969142809679385</v>
+        <v>0.8911534720657651</v>
       </c>
       <c r="AI26">
-        <v>0.7433313064329229</v>
+        <v>0.8293469978470208</v>
       </c>
       <c r="AJ26">
-        <v>0.02315361406270451</v>
+        <v>-7.029185245237202</v>
       </c>
       <c r="AK26">
-        <v>0.007827745254567873</v>
+        <v>-1.081851643895442</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3653,7 +3626,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Shimizu Bank, Ltd. (TSE:8364)</t>
+          <t>The Yamanashi Chuo Bank,Ltd. (TSE:8360)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3662,10 +3635,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.00758</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="E27">
-        <v>-0.0609</v>
+        <v>-0.0174</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3680,85 +3653,85 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>11.1</v>
+        <v>32.3</v>
       </c>
       <c r="L27">
-        <v>0.06232453677709152</v>
+        <v>0.08314028314028313</v>
       </c>
       <c r="M27">
-        <v>2.3805</v>
+        <v>16.954</v>
       </c>
       <c r="N27">
-        <v>0.01758124076809453</v>
+        <v>0.04682132007732671</v>
       </c>
       <c r="O27">
-        <v>0.2144594594594595</v>
+        <v>0.5248916408668731</v>
       </c>
       <c r="P27">
-        <v>2.3805</v>
+        <v>10.184</v>
       </c>
       <c r="Q27">
-        <v>0.01758124076809453</v>
+        <v>0.02812482739574703</v>
       </c>
       <c r="R27">
-        <v>0.2144594594594595</v>
+        <v>0.3152941176470588</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>6.770000000000001</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>0.3993157956824349</v>
       </c>
       <c r="U27">
-        <v>1080.1</v>
+        <v>5641.5</v>
       </c>
       <c r="V27">
-        <v>7.977104874446085</v>
+        <v>15.57995028997514</v>
       </c>
       <c r="W27">
-        <v>0.0140506329113924</v>
+        <v>0.02479085117814107</v>
       </c>
       <c r="X27">
-        <v>0.2210681173483456</v>
+        <v>0.1482284923831038</v>
       </c>
       <c r="Y27">
-        <v>-0.2070174844369531</v>
+        <v>-0.1234376412049627</v>
       </c>
       <c r="Z27">
-        <v>0.4294670846394986</v>
+        <v>8.427331887201669</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.06297029085292845</v>
+        <v>0.04881219951969602</v>
       </c>
       <c r="AC27">
-        <v>-0.06297029085292845</v>
+        <v>-0.04881219951969602</v>
       </c>
       <c r="AD27">
-        <v>1069.4</v>
+        <v>2943.2</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>1069.4</v>
+        <v>2943.2</v>
       </c>
       <c r="AG27">
-        <v>-10.69999999999982</v>
+        <v>-2698.3</v>
       </c>
       <c r="AH27">
-        <v>0.8876162018592297</v>
+        <v>0.8904486733428131</v>
       </c>
       <c r="AI27">
-        <v>0.6719869297473923</v>
+        <v>0.6887256049047596</v>
       </c>
       <c r="AJ27">
-        <v>-0.08580593424217965</v>
+        <v>1.154995291499015</v>
       </c>
       <c r="AK27">
-        <v>-0.02092704869939334</v>
+        <v>1.972297346685184</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3775,7 +3748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Ogaki Kyoritsu Bank, Ltd. (TSE:8361)</t>
+          <t>The Shiga Bank, Ltd. (TSE:8366)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3784,103 +3757,103 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0191</v>
+        <v>0.0233</v>
       </c>
       <c r="E28">
-        <v>0.0479</v>
+        <v>0.021</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.05183893468611288</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>9.765721011646884e-05</v>
+        <v>6.588872919925769e-05</v>
       </c>
       <c r="J28">
-        <v>6.807254722268578e-05</v>
+        <v>4.679185851101129e-05</v>
       </c>
       <c r="K28">
-        <v>68.8</v>
+        <v>103.4</v>
       </c>
       <c r="L28">
-        <v>0.08756522845869924</v>
+        <v>0.1639188332276474</v>
       </c>
       <c r="M28">
-        <v>22.7644</v>
+        <v>32.18</v>
       </c>
       <c r="N28">
-        <v>0.03838206036081605</v>
+        <v>0.0273732562095951</v>
       </c>
       <c r="O28">
-        <v>0.3308779069767442</v>
+        <v>0.3112185686653772</v>
       </c>
       <c r="P28">
-        <v>20.1344</v>
+        <v>25.46</v>
       </c>
       <c r="Q28">
-        <v>0.03394773225425729</v>
+        <v>0.02165702619938755</v>
       </c>
       <c r="R28">
-        <v>0.2926511627906977</v>
+        <v>0.2462282398452611</v>
       </c>
       <c r="S28">
-        <v>2.629999999999999</v>
+        <v>6.719999999999999</v>
       </c>
       <c r="T28">
-        <v>0.1155312681203985</v>
+        <v>0.2088253573648228</v>
       </c>
       <c r="U28">
-        <v>3862.9</v>
+        <v>9308</v>
       </c>
       <c r="V28">
-        <v>6.513066936435677</v>
+        <v>7.917659067710106</v>
       </c>
       <c r="W28">
-        <v>0.02349486049926578</v>
+        <v>0.03513660459426397</v>
       </c>
       <c r="X28">
-        <v>0.2029716419526754</v>
+        <v>0.1445043738597867</v>
       </c>
       <c r="Y28">
-        <v>-0.1794767814534097</v>
+        <v>-0.1093677692655227</v>
       </c>
       <c r="Z28">
-        <v>0.323894303117936</v>
+        <v>0.4963871908803827</v>
       </c>
       <c r="AA28">
-        <v>2.20483102441546e-05</v>
+        <v>2.322687920235322e-05</v>
       </c>
       <c r="AB28">
-        <v>0.06299383971687425</v>
+        <v>0.04884164856480473</v>
       </c>
       <c r="AC28">
-        <v>-0.06297179140663009</v>
+        <v>-0.04881842168560238</v>
       </c>
       <c r="AD28">
-        <v>4142.4</v>
+        <v>9172.299999999999</v>
       </c>
       <c r="AE28">
-        <v>0.1913536500574521</v>
+        <v>0.2821869481055413</v>
       </c>
       <c r="AF28">
-        <v>4142.591353650057</v>
+        <v>9172.582186948104</v>
       </c>
       <c r="AG28">
-        <v>279.6913536500574</v>
+        <v>-135.4178130518958</v>
       </c>
       <c r="AH28">
-        <v>0.8747595745354338</v>
+        <v>0.8863955061128751</v>
       </c>
       <c r="AI28">
-        <v>0.6757135720400708</v>
+        <v>0.7491685954349725</v>
       </c>
       <c r="AJ28">
-        <v>0.3204561462259841</v>
+        <v>-0.1301866295645879</v>
       </c>
       <c r="AK28">
-        <v>0.1233320486912909</v>
+        <v>-0.0461282265682425</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3889,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="AN28">
-        <v>36020.86956521738</v>
+        <v>93594.89795918367</v>
       </c>
       <c r="AP28">
-        <v>2432.098727391804</v>
+        <v>-1381.814418896896</v>
       </c>
     </row>
     <row r="29">
@@ -3903,7 +3876,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The San-in Godo Bank, Ltd. (TSE:8381)</t>
+          <t>Chugin Financial Group,Inc. (TSE:5832)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3912,10 +3885,10 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.0284</v>
+        <v>0.0155</v>
       </c>
       <c r="E29">
-        <v>0.0229</v>
+        <v>-0.0305</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3924,97 +3897,100 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>0.0002321747139841577</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>0.0001624372541061323</v>
       </c>
       <c r="K29">
-        <v>103.8</v>
+        <v>133.7</v>
       </c>
       <c r="L29">
-        <v>0.1503694046066927</v>
+        <v>0.1501740986184432</v>
       </c>
       <c r="M29">
-        <v>41.028</v>
+        <v>-0</v>
       </c>
       <c r="N29">
-        <v>0.04464417845484222</v>
+        <v>-0</v>
       </c>
       <c r="O29">
-        <v>0.3952601156069364</v>
+        <v>-0</v>
       </c>
       <c r="P29">
-        <v>41.028</v>
+        <v>-0</v>
       </c>
       <c r="Q29">
-        <v>0.04464417845484222</v>
+        <v>-0</v>
       </c>
       <c r="R29">
-        <v>0.3952601156069364</v>
+        <v>-0</v>
       </c>
       <c r="S29">
         <v>0</v>
       </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
       <c r="U29">
-        <v>5082.6</v>
+        <v>10655.8</v>
       </c>
       <c r="V29">
-        <v>5.530576713819369</v>
+        <v>8.220799259373553</v>
       </c>
       <c r="W29">
-        <v>0.02978650137741047</v>
+        <v>0.02939042887604141</v>
       </c>
       <c r="X29">
-        <v>0.2075141162606699</v>
+        <v>0.1366105829951597</v>
       </c>
       <c r="Y29">
-        <v>-0.1777276148832594</v>
+        <v>-0.1072201541191183</v>
       </c>
       <c r="Z29">
-        <v>0.1041129360662413</v>
+        <v>0.250380965884611</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>4.06711965787374e-05</v>
       </c>
       <c r="AB29">
-        <v>0.06298743626961821</v>
+        <v>0.04891188770766328</v>
       </c>
       <c r="AC29">
-        <v>-0.06298743626961821</v>
+        <v>-0.04887121651108454</v>
       </c>
       <c r="AD29">
-        <v>6629.6</v>
+        <v>9215.6</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>3.181474260699522</v>
       </c>
       <c r="AF29">
-        <v>6629.6</v>
+        <v>9218.781474260701</v>
       </c>
       <c r="AG29">
-        <v>1547</v>
+        <v>-1437.018525739299</v>
       </c>
       <c r="AH29">
-        <v>0.8782555705693771</v>
+        <v>0.8767282659343786</v>
       </c>
       <c r="AI29">
-        <v>0.7577378503177433</v>
+        <v>0.718965770075035</v>
       </c>
       <c r="AJ29">
-        <v>0.6273317112733171</v>
+        <v>10.20475479483213</v>
       </c>
       <c r="AK29">
-        <v>0.4219167621229477</v>
+        <v>-0.6632960137495164</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>10931.90984578885</v>
+      </c>
+      <c r="AP29">
+        <v>-1704.648310485526</v>
       </c>
     </row>
     <row r="30">
@@ -4025,7 +4001,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chugin Financial Group,Inc. (TSE:5832)</t>
+          <t>The Ogaki Kyoritsu Bank, Ltd. (TSE:8361)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4034,10 +4010,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0255</v>
+        <v>0.0101</v>
       </c>
       <c r="E30">
-        <v>0.0389</v>
+        <v>-0.223</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4046,91 +4022,91 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0.0002423591866120811</v>
+        <v>8.152687118144069e-05</v>
       </c>
       <c r="J30">
-        <v>0.000175406601474212</v>
+        <v>4.114679078436348e-05</v>
       </c>
       <c r="K30">
-        <v>153</v>
+        <v>16.1</v>
       </c>
       <c r="L30">
-        <v>0.1545454545454545</v>
+        <v>0.0211814234969083</v>
       </c>
       <c r="M30">
-        <v>38.76069999999999</v>
+        <v>19.5304</v>
       </c>
       <c r="N30">
-        <v>0.02910618007058646</v>
+        <v>0.03506985096067517</v>
       </c>
       <c r="O30">
-        <v>0.253337908496732</v>
+        <v>1.213068322981366</v>
       </c>
       <c r="P30">
-        <v>38.76069999999999</v>
+        <v>19.5104</v>
       </c>
       <c r="Q30">
-        <v>0.02910618007058646</v>
+        <v>0.03503393787035375</v>
       </c>
       <c r="R30">
-        <v>0.253337908496732</v>
+        <v>1.211826086956522</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>0.001024044566419509</v>
       </c>
       <c r="U30">
-        <v>7519.6</v>
+        <v>3507.8</v>
       </c>
       <c r="V30">
-        <v>5.646617105954794</v>
+        <v>6.298796911474233</v>
       </c>
       <c r="W30">
-        <v>0.02958694306930693</v>
+        <v>0.008507715070809555</v>
       </c>
       <c r="X30">
-        <v>0.1621368619038135</v>
+        <v>0.1192765031211451</v>
       </c>
       <c r="Y30">
-        <v>-0.1325499188345066</v>
+        <v>-0.1107687880503355</v>
       </c>
       <c r="Z30">
-        <v>0.2856252331224818</v>
+        <v>0.349941044996104</v>
       </c>
       <c r="AA30">
-        <v>5.010055143729406e-05</v>
+        <v>1.439895096531621e-05</v>
       </c>
       <c r="AB30">
-        <v>0.06307366244069006</v>
+        <v>0.049117712833118</v>
       </c>
       <c r="AC30">
-        <v>-0.06302356188925276</v>
+        <v>-0.04910331388215268</v>
       </c>
       <c r="AD30">
-        <v>6556.3</v>
+        <v>3116.4</v>
       </c>
       <c r="AE30">
-        <v>0.2803220262701983</v>
+        <v>0.1801571260749347</v>
       </c>
       <c r="AF30">
-        <v>6556.580322026271</v>
+        <v>3116.580157126075</v>
       </c>
       <c r="AG30">
-        <v>-963.0196779737298</v>
+        <v>-391.2198428739252</v>
       </c>
       <c r="AH30">
-        <v>0.8311799345819997</v>
+        <v>0.8483998888847443</v>
       </c>
       <c r="AI30">
-        <v>0.6424064512392876</v>
+        <v>0.6066477585473323</v>
       </c>
       <c r="AJ30">
-        <v>-2.612072357648397</v>
+        <v>-2.361295701670693</v>
       </c>
       <c r="AK30">
-        <v>-0.3584422270407776</v>
+        <v>-0.2400740099608724</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -4139,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>22149.66216216216</v>
+        <v>31800</v>
       </c>
       <c r="AP30">
-        <v>-3253.444858019358</v>
+        <v>-3992.039212999237</v>
       </c>
     </row>
     <row r="31">
@@ -4153,7 +4129,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Shiga Bank, Ltd. (TSE:8366)</t>
+          <t>Kyushu Financial Group,Inc. (TSE:7180)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4162,115 +4138,109 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.0338</v>
+        <v>0.0442</v>
       </c>
       <c r="E31">
-        <v>0.0447</v>
+        <v>0.0432</v>
       </c>
       <c r="G31">
-        <v>0.07830366189028803</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>3.054350923816543e-05</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>2.34186005791062e-05</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>122.6</v>
+        <v>155.3</v>
       </c>
       <c r="L31">
-        <v>0.1774497032855696</v>
+        <v>0.1201547388781431</v>
       </c>
       <c r="M31">
-        <v>43.0575</v>
+        <v>46.91</v>
       </c>
       <c r="N31">
-        <v>0.04521421820854774</v>
+        <v>0.01875949772054707</v>
       </c>
       <c r="O31">
-        <v>0.3512030995106036</v>
+        <v>0.3020605280103026</v>
       </c>
       <c r="P31">
-        <v>18.8575</v>
+        <v>43.26000000000001</v>
       </c>
       <c r="Q31">
-        <v>0.01980205817494487</v>
+        <v>0.01729984803647125</v>
       </c>
       <c r="R31">
-        <v>0.1538132137030995</v>
+        <v>0.2785576303927882</v>
       </c>
       <c r="S31">
-        <v>24.2</v>
+        <v>3.649999999999999</v>
       </c>
       <c r="T31">
-        <v>0.5620391337165418</v>
+        <v>0.07780856960136427</v>
       </c>
       <c r="U31">
-        <v>6192.9</v>
+        <v>14704.9</v>
       </c>
       <c r="V31">
-        <v>6.503097763309881</v>
+        <v>5.880548668319603</v>
       </c>
       <c r="W31">
-        <v>0.02711789427117894</v>
+        <v>0.03474117489150374</v>
       </c>
       <c r="X31">
-        <v>0.158644379105504</v>
+        <v>0.1150835016349074</v>
       </c>
       <c r="Y31">
-        <v>-0.1315264848343251</v>
+        <v>-0.08034232674340369</v>
       </c>
       <c r="Z31">
-        <v>1.471755185651076</v>
+        <v>0.286871601376096</v>
       </c>
       <c r="AA31">
-        <v>3.446644684299084e-05</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.06308314730815659</v>
+        <v>0.04918254599606336</v>
       </c>
       <c r="AC31">
-        <v>-0.0630486808613136</v>
+        <v>-0.04918254599606336</v>
       </c>
       <c r="AD31">
-        <v>4520.6</v>
+        <v>13077.2</v>
       </c>
       <c r="AE31">
-        <v>0.1394874473367576</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>4520.739487447338</v>
+        <v>13077.2</v>
       </c>
       <c r="AG31">
-        <v>-1672.160512552662</v>
+        <v>-1627.699999999999</v>
       </c>
       <c r="AH31">
-        <v>0.8260016208207263</v>
+        <v>0.8394766911887429</v>
       </c>
       <c r="AI31">
-        <v>0.6057098639393024</v>
+        <v>0.7412874407636669</v>
       </c>
       <c r="AJ31">
-        <v>2.322895176765698</v>
+        <v>-1.864703860694234</v>
       </c>
       <c r="AK31">
-        <v>-1.315999171340065</v>
+        <v>-0.5543370908967061</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
         <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>92257.14285714286</v>
-      </c>
-      <c r="AP31">
-        <v>-34125.72474597269</v>
       </c>
     </row>
     <row r="32">
@@ -4281,7 +4251,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Iyogin Holdings,Inc. (TSE:5830)</t>
+          <t>The San-in Godo Bank,Ltd. (TSE:8381)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4290,10 +4260,10 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.0488</v>
+        <v>0.0374</v>
       </c>
       <c r="E32">
-        <v>0.0561</v>
+        <v>0.00261</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4302,103 +4272,97 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0.0004478674120367205</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>0.0003153032194224143</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>217.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="L32">
-        <v>0.2238482943419561</v>
+        <v>0.127230857800806</v>
       </c>
       <c r="M32">
-        <v>34.6764</v>
+        <v>49.319</v>
       </c>
       <c r="N32">
-        <v>0.02047375568282458</v>
+        <v>0.04556869629492747</v>
       </c>
       <c r="O32">
-        <v>0.1596519337016575</v>
+        <v>0.5579072398190045</v>
       </c>
       <c r="P32">
-        <v>34.6764</v>
+        <v>35.919</v>
       </c>
       <c r="Q32">
-        <v>0.02047375568282458</v>
+        <v>0.03318765591795252</v>
       </c>
       <c r="R32">
-        <v>0.1596519337016575</v>
+        <v>0.4063235294117648</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>0.2717005616496684</v>
       </c>
       <c r="U32">
-        <v>7741.4</v>
+        <v>4684</v>
       </c>
       <c r="V32">
-        <v>4.570703194190234</v>
+        <v>4.32782038251871</v>
       </c>
       <c r="W32">
-        <v>0.03247267779987142</v>
+        <v>0.04176904176904177</v>
       </c>
       <c r="X32">
-        <v>0.1155125426663798</v>
+        <v>0.1088928691034614</v>
       </c>
       <c r="Y32">
-        <v>-0.08303986486650838</v>
+        <v>-0.0671238273344196</v>
       </c>
       <c r="Z32">
-        <v>0.6097502842505915</v>
+        <v>0.1896598788011137</v>
       </c>
       <c r="AA32">
-        <v>0.0001922562276679438</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.06327750225955413</v>
+        <v>0.0492935474144137</v>
       </c>
       <c r="AC32">
-        <v>-0.06308524603188619</v>
+        <v>-0.0492935474144137</v>
       </c>
       <c r="AD32">
-        <v>4350.8</v>
+        <v>5074.1</v>
       </c>
       <c r="AE32">
-        <v>2.107171250503851</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>4352.907171250504</v>
+        <v>5074.1</v>
       </c>
       <c r="AG32">
-        <v>-3388.492828749496</v>
+        <v>390.1000000000004</v>
       </c>
       <c r="AH32">
-        <v>0.7198925030134339</v>
+        <v>0.8241992073289585</v>
       </c>
       <c r="AI32">
-        <v>0.4641513129070789</v>
+        <v>0.7127846376445137</v>
       </c>
       <c r="AJ32">
-        <v>1.999355184462102</v>
+        <v>0.2649415919587071</v>
       </c>
       <c r="AK32">
-        <v>-2.070184495929793</v>
+        <v>0.1602250790651827</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
         <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>5082.710280373832</v>
-      </c>
-      <c r="AP32">
-        <v>-3958.519659754084</v>
       </c>
     </row>
     <row r="33">
@@ -4409,7 +4373,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Ehime Bank, Ltd. (TSE:8541)</t>
+          <t>Shizuoka Financial Group,Inc. (TSE:5831)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4418,10 +4382,13 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.00478</v>
+        <v>0.0248</v>
       </c>
       <c r="E33">
-        <v>0.0127</v>
+        <v>0.00363</v>
+      </c>
+      <c r="F33">
+        <v>0.0842</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4430,91 +4397,91 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0.001042890683063048</v>
+        <v>0.001227466350152914</v>
       </c>
       <c r="J33">
-        <v>0.0006806233931569367</v>
+        <v>0.0008638575284602505</v>
       </c>
       <c r="K33">
-        <v>43.2</v>
+        <v>376.5</v>
       </c>
       <c r="L33">
-        <v>0.1528121683763707</v>
+        <v>0.22918188458729</v>
       </c>
       <c r="M33">
-        <v>8.1007</v>
+        <v>114.8436</v>
       </c>
       <c r="N33">
-        <v>0.02984782608695652</v>
+        <v>0.02441922177333616</v>
       </c>
       <c r="O33">
-        <v>0.1875162037037037</v>
+        <v>0.3050294820717131</v>
       </c>
       <c r="P33">
-        <v>8.0937</v>
+        <v>114.8436</v>
       </c>
       <c r="Q33">
-        <v>0.02982203389830509</v>
+        <v>0.02441922177333616</v>
       </c>
       <c r="R33">
-        <v>0.1873541666666667</v>
+        <v>0.3050294820717131</v>
       </c>
       <c r="S33">
-        <v>0.006999999999999673</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>0.0008641228535805145</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>973.8</v>
+        <v>12170.7</v>
       </c>
       <c r="V33">
-        <v>3.588061901252764</v>
+        <v>2.587858813523283</v>
       </c>
       <c r="W33">
-        <v>0.03142503819015058</v>
+        <v>0.04206609908158476</v>
       </c>
       <c r="X33">
-        <v>0.09923472086364327</v>
+        <v>0.09922306737347006</v>
       </c>
       <c r="Y33">
-        <v>-0.06780968267349269</v>
+        <v>-0.0571569682918853</v>
       </c>
       <c r="Z33">
-        <v>0.3615455340727396</v>
+        <v>0.2500982858479819</v>
       </c>
       <c r="AA33">
-        <v>0.0002460763481813249</v>
+        <v>0.0002160492870847828</v>
       </c>
       <c r="AB33">
-        <v>0.06343088123388169</v>
+        <v>0.04951659171659624</v>
       </c>
       <c r="AC33">
-        <v>-0.06318480488570036</v>
+        <v>-0.04930054242951146</v>
       </c>
       <c r="AD33">
-        <v>472.7</v>
+        <v>18065.9</v>
       </c>
       <c r="AE33">
-        <v>1.820874019490382</v>
+        <v>6.017591399843962</v>
       </c>
       <c r="AF33">
-        <v>474.5208740194903</v>
+        <v>18071.91759139984</v>
       </c>
       <c r="AG33">
-        <v>-499.2791259805096</v>
+        <v>5901.217591399844</v>
       </c>
       <c r="AH33">
-        <v>0.6361544374840641</v>
+        <v>0.7935008993500848</v>
       </c>
       <c r="AI33">
-        <v>0.3636117118632414</v>
+        <v>0.7043023465852792</v>
       </c>
       <c r="AJ33">
-        <v>2.190982275503429</v>
+        <v>0.5564972182564234</v>
       </c>
       <c r="AK33">
-        <v>-1.507390279850327</v>
+        <v>0.4374961000571607</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -4523,10 +4490,10 @@
         <v>0</v>
       </c>
       <c r="AN33">
-        <v>717.298937784522</v>
+        <v>5610.527950310559</v>
       </c>
       <c r="AP33">
-        <v>-757.6314506532771</v>
+        <v>1832.676270621069</v>
       </c>
     </row>
     <row r="34">
@@ -4537,7 +4504,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Tottori Bank, Ltd. (TSE:8383)</t>
+          <t>The Yamagata Bank, Ltd. (TSE:8344)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4546,10 +4513,10 @@
         </is>
       </c>
       <c r="D34">
-        <v>-0.0391</v>
+        <v>0.0117</v>
       </c>
       <c r="E34">
-        <v>-0.08019999999999999</v>
+        <v>-0.206</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4564,85 +4531,85 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>5.85</v>
+        <v>10.3</v>
       </c>
       <c r="L34">
-        <v>0.07267080745341614</v>
+        <v>0.03656372026979056</v>
       </c>
       <c r="M34">
-        <v>3.23856</v>
+        <v>7.495</v>
       </c>
       <c r="N34">
-        <v>0.03983468634686346</v>
+        <v>0.03091996699669967</v>
       </c>
       <c r="O34">
-        <v>0.5536</v>
+        <v>0.7276699029126213</v>
       </c>
       <c r="P34">
-        <v>3.23856</v>
+        <v>7.488</v>
       </c>
       <c r="Q34">
-        <v>0.03983468634686346</v>
+        <v>0.03089108910891089</v>
       </c>
       <c r="R34">
-        <v>0.5536</v>
+        <v>0.7269902912621359</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>0.006999999999999673</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>0.0009339559706470545</v>
       </c>
       <c r="U34">
-        <v>539.5</v>
+        <v>976.8</v>
       </c>
       <c r="V34">
-        <v>6.635916359163592</v>
+        <v>4.02970297029703</v>
       </c>
       <c r="W34">
-        <v>0.01319350473612991</v>
+        <v>0.01115080653891956</v>
       </c>
       <c r="X34">
-        <v>0.1069725100793055</v>
+        <v>0.1032916531717242</v>
       </c>
       <c r="Y34">
-        <v>-0.09377900534317563</v>
+        <v>-0.09214084663280463</v>
       </c>
       <c r="Z34">
-        <v>0.6011949215832711</v>
+        <v>1.688848920863308</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.06334795888850557</v>
+        <v>0.04941390274186241</v>
       </c>
       <c r="AC34">
-        <v>-0.06334795888850557</v>
+        <v>-0.04941390274186241</v>
       </c>
       <c r="AD34">
-        <v>173.9</v>
+        <v>1017.7</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>173.9</v>
+        <v>1017.7</v>
       </c>
       <c r="AG34">
-        <v>-365.6</v>
+        <v>40.90000000000009</v>
       </c>
       <c r="AH34">
-        <v>0.6814263322884013</v>
+        <v>0.8076343147369256</v>
       </c>
       <c r="AI34">
-        <v>0.3435401027261952</v>
+        <v>0.5363090219224284</v>
       </c>
       <c r="AJ34">
-        <v>1.285965529370383</v>
+        <v>0.1443699258736325</v>
       </c>
       <c r="AK34">
-        <v>10.97897897897898</v>
+        <v>0.04441789748045188</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -4659,7 +4626,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The First Bank Of Toyama, Ltd. (TSE:7184)</t>
+          <t>The Daito Bank, Ltd. (TSE:8563)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4668,10 +4635,10 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.0198</v>
+        <v>-0.0003</v>
       </c>
       <c r="E35">
-        <v>-0.0202</v>
+        <v>0.117</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4686,85 +4653,85 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>29.1</v>
+        <v>8.59</v>
       </c>
       <c r="L35">
-        <v>0.1428571428571429</v>
+        <v>0.1004678362573099</v>
       </c>
       <c r="M35">
-        <v>13.5556</v>
+        <v>2.5527</v>
       </c>
       <c r="N35">
-        <v>0.04783203952011292</v>
+        <v>0.03832882882882883</v>
       </c>
       <c r="O35">
-        <v>0.465828178694158</v>
+        <v>0.2971711292200233</v>
       </c>
       <c r="P35">
-        <v>6.6456</v>
+        <v>2.5527</v>
       </c>
       <c r="Q35">
-        <v>0.02344954128440367</v>
+        <v>0.03832882882882883</v>
       </c>
       <c r="R35">
-        <v>0.2283711340206185</v>
+        <v>0.2971711292200233</v>
       </c>
       <c r="S35">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>0.5097524270412228</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>615.3</v>
+        <v>628.2</v>
       </c>
       <c r="V35">
-        <v>2.171136203246295</v>
+        <v>9.432432432432433</v>
       </c>
       <c r="W35">
-        <v>0.02811051004636785</v>
+        <v>0.03564315352697096</v>
       </c>
       <c r="X35">
-        <v>0.09892001039297164</v>
+        <v>0.1015204754607527</v>
       </c>
       <c r="Y35">
-        <v>-0.0708095003466038</v>
+        <v>-0.06587732193378179</v>
       </c>
       <c r="Z35">
-        <v>0.2990311215502056</v>
+        <v>1.158536585365854</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.06343475550938672</v>
+        <v>0.04945682559061871</v>
       </c>
       <c r="AC35">
-        <v>-0.06343475550938672</v>
+        <v>-0.04945682559061871</v>
       </c>
       <c r="AD35">
-        <v>491</v>
+        <v>269.3</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>491</v>
+        <v>269.3</v>
       </c>
       <c r="AG35">
-        <v>-124.3</v>
+        <v>-358.9</v>
       </c>
       <c r="AH35">
-        <v>0.6340392561983471</v>
+        <v>0.8017267043763026</v>
       </c>
       <c r="AI35">
-        <v>0.3680659670164917</v>
+        <v>0.5364541832669323</v>
       </c>
       <c r="AJ35">
-        <v>-0.7812696417347577</v>
+        <v>1.227848101265823</v>
       </c>
       <c r="AK35">
-        <v>-0.1729511618199526</v>
+        <v>2.843898573692551</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -4781,7 +4748,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Yamagata Bank, Ltd. (TSE:8344)</t>
+          <t>Iyogin Holdings,Inc. (TSE:5830)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4790,10 +4757,10 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.0298</v>
+        <v>0.0414</v>
       </c>
       <c r="E36">
-        <v>-0.0238</v>
+        <v>0.0171</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4802,97 +4769,103 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>0.0005750011293708312</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>0.0004023404955414379</v>
       </c>
       <c r="K36">
-        <v>33.4</v>
+        <v>173.2</v>
       </c>
       <c r="L36">
-        <v>0.1040174400498287</v>
+        <v>0.183455142463722</v>
       </c>
       <c r="M36">
-        <v>11.638</v>
+        <v>34.1214</v>
       </c>
       <c r="N36">
-        <v>0.03880626875625209</v>
+        <v>0.01651808103790483</v>
       </c>
       <c r="O36">
-        <v>0.3484431137724551</v>
+        <v>0.1970057736720554</v>
       </c>
       <c r="P36">
-        <v>8.288</v>
+        <v>34.1214</v>
       </c>
       <c r="Q36">
-        <v>0.02763587862620874</v>
+        <v>0.01651808103790483</v>
       </c>
       <c r="R36">
-        <v>0.2481437125748503</v>
+        <v>0.1970057736720554</v>
       </c>
       <c r="S36">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>0.2878501460732084</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>1087.6</v>
+        <v>5480.5</v>
       </c>
       <c r="V36">
-        <v>3.626542180726909</v>
+        <v>2.653095802875539</v>
       </c>
       <c r="W36">
-        <v>0.02232471091504579</v>
+        <v>0.02902290664745212</v>
       </c>
       <c r="X36">
-        <v>0.08644214397856061</v>
+        <v>0.08878421630853264</v>
       </c>
       <c r="Y36">
-        <v>-0.06411743306351482</v>
+        <v>-0.05976130966108052</v>
       </c>
       <c r="Z36">
-        <v>0.3831285049516765</v>
+        <v>0.6283482676665757</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>0.0002528099533855741</v>
       </c>
       <c r="AB36">
-        <v>0.06363553763925961</v>
+        <v>0.04986512087351926</v>
       </c>
       <c r="AC36">
-        <v>-0.06363553763925961</v>
+        <v>-0.04961231092013368</v>
       </c>
       <c r="AD36">
-        <v>330.7</v>
+        <v>6050.4</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.610707168804991</v>
       </c>
       <c r="AF36">
-        <v>330.7</v>
+        <v>6052.010707168804</v>
       </c>
       <c r="AG36">
-        <v>-756.8999999999999</v>
+        <v>571.5107071688044</v>
       </c>
       <c r="AH36">
-        <v>0.5244211861718998</v>
+        <v>0.7455317053642024</v>
       </c>
       <c r="AI36">
-        <v>0.2633800573431029</v>
+        <v>0.5353861442585796</v>
       </c>
       <c r="AJ36">
-        <v>1.656236323851204</v>
+        <v>0.2167102938021792</v>
       </c>
       <c r="AK36">
-        <v>-4.505357142857139</v>
+        <v>0.0981385174522421</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
         <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>6994.682080924855</v>
+      </c>
+      <c r="AP36">
+        <v>660.7060198483288</v>
       </c>
     </row>
     <row r="37">
@@ -4903,7 +4876,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Bank of Kyoto, Ltd. (TSE:8369)</t>
+          <t>The Bank Of Kochi, Ltd. (TSE:8416)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4912,13 +4885,10 @@
         </is>
       </c>
       <c r="D37">
-        <v>0.0309</v>
+        <v>3e-05</v>
       </c>
       <c r="E37">
-        <v>0.0339</v>
-      </c>
-      <c r="F37">
-        <v>0.153</v>
+        <v>0.0487</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4927,103 +4897,97 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>-0.0005411781417218346</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>-0.0003941026889074222</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>157.7</v>
+        <v>10.4</v>
       </c>
       <c r="L37">
-        <v>0.1876934063318257</v>
+        <v>0.07113543091655268</v>
       </c>
       <c r="M37">
-        <v>64.8</v>
+        <v>117.3867</v>
       </c>
       <c r="N37">
-        <v>0.01945011405931084</v>
+        <v>1.752040298507463</v>
       </c>
       <c r="O37">
-        <v>0.4109067850348764</v>
+        <v>11.28718269230769</v>
       </c>
       <c r="P37">
-        <v>64.8</v>
+        <v>1.6867</v>
       </c>
       <c r="Q37">
-        <v>0.01945011405931084</v>
+        <v>0.02517462686567164</v>
       </c>
       <c r="R37">
-        <v>0.4109067850348764</v>
+        <v>0.1621826923076923</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>115.7</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>0.9856312512405579</v>
       </c>
       <c r="U37">
-        <v>5853.8</v>
+        <v>370.1</v>
       </c>
       <c r="V37">
-        <v>1.757053667907312</v>
+        <v>5.523880597014926</v>
       </c>
       <c r="W37">
-        <v>0.01503838268249654</v>
+        <v>0.02237521514629948</v>
       </c>
       <c r="X37">
-        <v>0.08428037960825194</v>
+        <v>0.08689074249615555</v>
       </c>
       <c r="Y37">
-        <v>-0.06924199692575539</v>
+        <v>-0.06451552734985608</v>
       </c>
       <c r="Z37">
-        <v>0.1729011685928087</v>
+        <v>0.4026438997521343</v>
       </c>
       <c r="AA37">
-        <v>-6.814081545766143e-05</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>0.06663049993337336</v>
+        <v>0.04994645209096341</v>
       </c>
       <c r="AC37">
-        <v>-0.06669864074883103</v>
+        <v>-0.04994645209096341</v>
       </c>
       <c r="AD37">
-        <v>3301.6</v>
+        <v>185.2</v>
       </c>
       <c r="AE37">
-        <v>8.623489373373427</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>3310.223489373373</v>
+        <v>185.2</v>
       </c>
       <c r="AG37">
-        <v>-2543.576510626627</v>
+        <v>-184.9</v>
       </c>
       <c r="AH37">
-        <v>0.4983907649261661</v>
+        <v>0.7343378271213322</v>
       </c>
       <c r="AI37">
-        <v>0.3203786186756333</v>
+        <v>0.3210818307905687</v>
       </c>
       <c r="AJ37">
-        <v>-3.227792756088081</v>
+        <v>1.568278201865988</v>
       </c>
       <c r="AK37">
-        <v>-0.5679624798016873</v>
+        <v>-0.8945331398161589</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
         <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>2599.685039370079</v>
-      </c>
-      <c r="AP37">
-        <v>-2002.816150099706</v>
       </c>
     </row>
     <row r="38">
@@ -5034,7 +4998,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Bank of Toyama, Ltd. (TSE:8365)</t>
+          <t>Tokyo Kiraboshi Financial Group, Inc. (TSE:7173)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5043,10 +5007,10 @@
         </is>
       </c>
       <c r="D38">
-        <v>-0.0396</v>
+        <v>0.116</v>
       </c>
       <c r="E38">
-        <v>-0.18</v>
+        <v>0.5820000000000001</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5055,97 +5019,103 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>8.322663555665729e-05</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>6.01196561086743e-05</v>
       </c>
       <c r="K38">
-        <v>3.45</v>
+        <v>174.1</v>
       </c>
       <c r="L38">
-        <v>0.06609195402298851</v>
+        <v>0.204751264259673</v>
       </c>
       <c r="M38">
-        <v>2.34186</v>
+        <v>26.1172</v>
       </c>
       <c r="N38">
-        <v>0.03261643454038997</v>
+        <v>0.03060370283571596</v>
       </c>
       <c r="O38">
-        <v>0.6787999999999998</v>
+        <v>0.150012636415853</v>
       </c>
       <c r="P38">
-        <v>1.87186</v>
+        <v>25.8762</v>
       </c>
       <c r="Q38">
-        <v>0.02607047353760445</v>
+        <v>0.03032130302320131</v>
       </c>
       <c r="R38">
-        <v>0.5425681159420289</v>
+        <v>0.1486283744974153</v>
       </c>
       <c r="S38">
-        <v>0.4699999999999998</v>
+        <v>0.2409999999999997</v>
       </c>
       <c r="T38">
-        <v>0.2006951739215836</v>
+        <v>0.0092276354279938</v>
       </c>
       <c r="U38">
-        <v>384.9</v>
+        <v>4973.3</v>
       </c>
       <c r="V38">
-        <v>5.360724233983287</v>
+        <v>5.827630653855168</v>
       </c>
       <c r="W38">
-        <v>0.01142005958291956</v>
+        <v>0.08104459547528163</v>
       </c>
       <c r="X38">
-        <v>0.1298523099234094</v>
+        <v>0.08309493390553246</v>
       </c>
       <c r="Y38">
-        <v>-0.1184322503404898</v>
+        <v>-0.002050338430250834</v>
       </c>
       <c r="Z38">
-        <v>0.5359342915811089</v>
+        <v>0.4034693405767087</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.425643800586531e-05</v>
       </c>
       <c r="AB38">
-        <v>0.06772739777241239</v>
+        <v>0.0501331293049814</v>
       </c>
       <c r="AC38">
-        <v>-0.06772739777241239</v>
+        <v>-0.05010887286697553</v>
       </c>
       <c r="AD38">
-        <v>236.5</v>
+        <v>2075.5</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>0.1711619589308715</v>
       </c>
       <c r="AF38">
-        <v>236.5</v>
+        <v>2075.671161958931</v>
       </c>
       <c r="AG38">
-        <v>-148.4</v>
+        <v>-2897.628838041069</v>
       </c>
       <c r="AH38">
-        <v>0.7671099578332793</v>
+        <v>0.7086448389907826</v>
       </c>
       <c r="AI38">
-        <v>0.5350678733031674</v>
+        <v>0.4804715209871034</v>
       </c>
       <c r="AJ38">
-        <v>1.93733681462141</v>
+        <v>1.417467939067815</v>
       </c>
       <c r="AK38">
-        <v>-2.59894921190893</v>
+        <v>4.435855659297902</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
         <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>19766.66666666667</v>
+      </c>
+      <c r="AP38">
+        <v>-27596.46512420066</v>
       </c>
     </row>
     <row r="39">
@@ -5156,7 +5126,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Gunma Bank, Ltd. (TSE:8334)</t>
+          <t>The Ehime Bank, Ltd. (TSE:8541)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5165,10 +5135,10 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.0141</v>
+        <v>0.0188</v>
       </c>
       <c r="E39">
-        <v>-0.0298</v>
+        <v>-0.0626</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5177,91 +5147,91 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0.0002184922173080352</v>
+        <v>0.0007399132107450256</v>
       </c>
       <c r="J39">
-        <v>0.000147667045371835</v>
+        <v>0.0004879523572059523</v>
       </c>
       <c r="K39">
-        <v>171.8</v>
+        <v>27.4</v>
       </c>
       <c r="L39">
-        <v>0.163821874702012</v>
+        <v>0.09124209124209123</v>
       </c>
       <c r="M39">
-        <v>66.9336</v>
+        <v>7.8661</v>
       </c>
       <c r="N39">
-        <v>0.04262200713194091</v>
+        <v>0.02814347048300537</v>
       </c>
       <c r="O39">
-        <v>0.3896018626309662</v>
+        <v>0.2870839416058394</v>
       </c>
       <c r="P39">
-        <v>42.7336</v>
+        <v>7.859100000000001</v>
       </c>
       <c r="Q39">
-        <v>0.02721192052980132</v>
+        <v>0.02811842576028623</v>
       </c>
       <c r="R39">
-        <v>0.2487403958090803</v>
+        <v>0.2868284671532847</v>
       </c>
       <c r="S39">
-        <v>24.2</v>
+        <v>0.006999999999999673</v>
       </c>
       <c r="T39">
-        <v>0.3615523444129705</v>
+        <v>0.0008898946110524494</v>
       </c>
       <c r="U39">
-        <v>10756.2</v>
+        <v>997.4</v>
       </c>
       <c r="V39">
-        <v>6.849337748344371</v>
+        <v>3.568515205724508</v>
       </c>
       <c r="W39">
-        <v>0.03402047565298323</v>
+        <v>0.0330518697225573</v>
       </c>
       <c r="X39">
-        <v>0.1756176415581084</v>
+        <v>0.07542616770675101</v>
       </c>
       <c r="Y39">
-        <v>-0.1415971659051252</v>
+        <v>-0.04237429798419371</v>
       </c>
       <c r="Z39">
-        <v>0.3398691423558507</v>
+        <v>0.9120202068010075</v>
       </c>
       <c r="AA39">
-        <v>5.018747206474804e-05</v>
+        <v>0.0004450224097280116</v>
       </c>
       <c r="AB39">
-        <v>0.06805993318539577</v>
+        <v>0.05064719779586194</v>
       </c>
       <c r="AC39">
-        <v>-0.06800974571333103</v>
+        <v>-0.05020217538613393</v>
       </c>
       <c r="AD39">
-        <v>8797.799999999999</v>
+        <v>491</v>
       </c>
       <c r="AE39">
-        <v>2.599336058545318</v>
+        <v>1.369020314066344</v>
       </c>
       <c r="AF39">
-        <v>8800.399336058545</v>
+        <v>492.3690203140663</v>
       </c>
       <c r="AG39">
-        <v>-1955.800663941456</v>
+        <v>-505.0309796859336</v>
       </c>
       <c r="AH39">
-        <v>0.848574835062151</v>
+        <v>0.6378919316048285</v>
       </c>
       <c r="AI39">
-        <v>0.7188870674299705</v>
+        <v>0.3671740456753799</v>
       </c>
       <c r="AJ39">
-        <v>5.074720536128994</v>
+        <v>2.239297591795246</v>
       </c>
       <c r="AK39">
-        <v>-1.316594774879372</v>
+        <v>-1.469954943039597</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -5270,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="AN39">
-        <v>11746.06141522029</v>
+        <v>989.9193548387096</v>
       </c>
       <c r="AP39">
-        <v>-2611.215839708219</v>
+        <v>-1018.207620334544</v>
       </c>
     </row>
     <row r="40">
@@ -5284,7 +5254,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Hachijuni Bank, Ltd. (TSE:8359)</t>
+          <t>The Bank of Toyama, Ltd. (TSE:8365)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5293,10 +5263,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.0286</v>
-      </c>
-      <c r="E40">
-        <v>-0.0171</v>
+        <v>-0.0541</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5311,85 +5278,85 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>168.3</v>
+        <v>-0.221</v>
       </c>
       <c r="L40">
-        <v>0.1490831783151741</v>
+        <v>-0.004732334047109208</v>
       </c>
       <c r="M40">
-        <v>54.04770000000001</v>
+        <v>1.8157</v>
       </c>
       <c r="N40">
-        <v>0.02686400914558378</v>
+        <v>0.02784815950920246</v>
       </c>
       <c r="O40">
-        <v>0.3211390374331551</v>
+        <v>-8.215837104072399</v>
       </c>
       <c r="P40">
-        <v>33.3477</v>
+        <v>1.8157</v>
       </c>
       <c r="Q40">
-        <v>0.01657522739698792</v>
+        <v>0.02784815950920246</v>
       </c>
       <c r="R40">
-        <v>0.198144385026738</v>
+        <v>-8.215837104072399</v>
       </c>
       <c r="S40">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>0.3829950210647262</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>19562.1</v>
+        <v>332.7</v>
       </c>
       <c r="V40">
-        <v>9.723196977981011</v>
+        <v>5.102760736196319</v>
       </c>
       <c r="W40">
-        <v>0.02029446876243534</v>
+        <v>-0.001106659989984978</v>
       </c>
       <c r="X40">
-        <v>0.2294189917364916</v>
+        <v>0.0814319498305222</v>
       </c>
       <c r="Y40">
-        <v>-0.2091245229740563</v>
+        <v>-0.08253860982050717</v>
       </c>
       <c r="Z40">
-        <v>0.1036011232861627</v>
+        <v>0.9103313840155944</v>
       </c>
       <c r="AA40">
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0.06824004671854551</v>
+        <v>0.05022679289527817</v>
       </c>
       <c r="AC40">
-        <v>-0.06824004671854551</v>
+        <v>-0.05022679289527817</v>
       </c>
       <c r="AD40">
-        <v>16738.2</v>
+        <v>149.1</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>16738.2</v>
+        <v>149.1</v>
       </c>
       <c r="AG40">
-        <v>-2823.899999999998</v>
+        <v>-183.6</v>
       </c>
       <c r="AH40">
-        <v>0.8926992389373922</v>
+        <v>0.6957536164255715</v>
       </c>
       <c r="AI40">
-        <v>0.7398459151605161</v>
+        <v>0.4274655963302753</v>
       </c>
       <c r="AJ40">
-        <v>3.477709359605918</v>
+        <v>1.550675675675676</v>
       </c>
       <c r="AK40">
-        <v>-0.9223006074857913</v>
+        <v>-11.40372670807454</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -5406,7 +5373,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shinsei Bank, Limited (TSE:8303)</t>
+          <t>The Bank of Saga Ltd. (TSE:8395)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5415,13 +5382,10 @@
         </is>
       </c>
       <c r="D41">
-        <v>0.00814</v>
+        <v>0.0026</v>
       </c>
       <c r="E41">
-        <v>-0.154</v>
-      </c>
-      <c r="F41">
-        <v>0.424</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -5430,103 +5394,97 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0.009236943532744287</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>0.006421472414754495</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>152.4</v>
+        <v>30.3</v>
       </c>
       <c r="L41">
-        <v>0.06592836130818482</v>
+        <v>0.1000330141961043</v>
       </c>
       <c r="M41">
-        <v>86.0403</v>
+        <v>7.9462</v>
       </c>
       <c r="N41">
-        <v>0.02587911691280417</v>
+        <v>0.03603718820861678</v>
       </c>
       <c r="O41">
-        <v>0.5645688976377953</v>
+        <v>0.2622508250825082</v>
       </c>
       <c r="P41">
-        <v>16.9403</v>
+        <v>7.8792</v>
       </c>
       <c r="Q41">
-        <v>0.005095286792793335</v>
+        <v>0.03573333333333333</v>
       </c>
       <c r="R41">
-        <v>0.1111568241469816</v>
+        <v>0.260039603960396</v>
       </c>
       <c r="S41">
-        <v>69.09999999999999</v>
+        <v>0.06700000000000017</v>
       </c>
       <c r="T41">
-        <v>0.8031120300603322</v>
+        <v>0.00843170320404724</v>
       </c>
       <c r="U41">
-        <v>17414.9</v>
+        <v>880.5</v>
       </c>
       <c r="V41">
-        <v>5.238036514572745</v>
+        <v>3.993197278911565</v>
       </c>
       <c r="W41">
-        <v>0.01823140970427792</v>
+        <v>0.0407258064516129</v>
       </c>
       <c r="X41">
-        <v>0.1228864315555498</v>
+        <v>0.08078672878769591</v>
       </c>
       <c r="Y41">
-        <v>-0.1046550218512719</v>
+        <v>-0.04006092233608301</v>
       </c>
       <c r="Z41">
-        <v>0.2287005676653088</v>
+        <v>0.2658883426966291</v>
       </c>
       <c r="AA41">
-        <v>0.001468594386501474</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>0.06982072432550424</v>
+        <v>0.05026540417245755</v>
       </c>
       <c r="AC41">
-        <v>-0.06835212993900276</v>
+        <v>-0.05026540417245755</v>
       </c>
       <c r="AD41">
-        <v>9722.9</v>
+        <v>491.8</v>
       </c>
       <c r="AE41">
-        <v>59.23940664854155</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>9782.139406648541</v>
+        <v>491.8</v>
       </c>
       <c r="AG41">
-        <v>-7632.760593351461</v>
+        <v>-388.7</v>
       </c>
       <c r="AH41">
-        <v>0.7463385415164603</v>
+        <v>0.6904394215920259</v>
       </c>
       <c r="AI41">
-        <v>0.5978557540127714</v>
+        <v>0.4020930422696428</v>
       </c>
       <c r="AJ41">
-        <v>1.771739377373415</v>
+        <v>2.310939357907253</v>
       </c>
       <c r="AK41">
-        <v>7.249545325896273</v>
+        <v>-1.134559252772913</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
         <v>0</v>
-      </c>
-      <c r="AN41">
-        <v>292.8584337349397</v>
-      </c>
-      <c r="AP41">
-        <v>-229.9024275105861</v>
       </c>
     </row>
     <row r="42">
@@ -5537,7 +5495,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Keiyo Bank, Ltd. (TSE:8544)</t>
+          <t>The Hachijuni Bank, Ltd. (TSE:8359)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5546,10 +5504,10 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.0116</v>
+        <v>0.014</v>
       </c>
       <c r="E42">
-        <v>0.00206</v>
+        <v>0.1</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -5558,94 +5516,97 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>-0.000512406406964551</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>-0.0003601664665955915</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>78.40000000000001</v>
+        <v>251.1</v>
       </c>
       <c r="L42">
-        <v>0.1740674955595027</v>
+        <v>0.2202052091554854</v>
       </c>
       <c r="M42">
-        <v>23.134</v>
+        <v>162.2287</v>
       </c>
       <c r="N42">
-        <v>0.04087279151943463</v>
+        <v>0.05956406961374652</v>
       </c>
       <c r="O42">
-        <v>0.2950765306122449</v>
+        <v>0.6460720828355238</v>
       </c>
       <c r="P42">
-        <v>18.444</v>
+        <v>98.2287</v>
       </c>
       <c r="Q42">
-        <v>0.03258657243816254</v>
+        <v>0.03606575855485387</v>
       </c>
       <c r="R42">
-        <v>0.2352551020408163</v>
+        <v>0.3911935483870968</v>
       </c>
       <c r="S42">
-        <v>4.690000000000001</v>
+        <v>64</v>
       </c>
       <c r="T42">
-        <v>0.2027319097432351</v>
+        <v>0.3945047947742908</v>
       </c>
       <c r="U42">
-        <v>7868.7</v>
+        <v>26016</v>
       </c>
       <c r="V42">
-        <v>13.90229681978798</v>
+        <v>9.55206344543986</v>
       </c>
       <c r="W42">
-        <v>0.02910170749814403</v>
+        <v>0.04283886377207199</v>
       </c>
       <c r="X42">
-        <v>0.2313742737507471</v>
+        <v>0.1660118242083015</v>
       </c>
       <c r="Y42">
-        <v>-0.202272566252603</v>
+        <v>-0.1231729604362295</v>
+      </c>
+      <c r="Z42">
+        <v>0.3753950487226755</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>0.06824463650326283</v>
+        <v>0.0523512517737805</v>
+      </c>
+      <c r="AC42">
+        <v>-0.0523512517737805</v>
       </c>
       <c r="AD42">
-        <v>4753.7</v>
+        <v>26373.4</v>
       </c>
       <c r="AE42">
-        <v>11.05393922848417</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>4764.753939228484</v>
+        <v>26373.4</v>
       </c>
       <c r="AG42">
-        <v>-3103.946060771515</v>
+        <v>357.4000000000015</v>
       </c>
       <c r="AH42">
-        <v>0.8938236492525264</v>
+        <v>0.9063958483692477</v>
       </c>
       <c r="AI42">
-        <v>0.7052465029789704</v>
+        <v>0.8024182016222762</v>
       </c>
       <c r="AJ42">
-        <v>1.223014983946483</v>
+        <v>0.1160012982797797</v>
       </c>
       <c r="AK42">
-        <v>2.789948362784214</v>
+        <v>0.05216452111977134</v>
       </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
         <v>0</v>
-      </c>
-      <c r="AN42">
-        <v>2400.858585858586</v>
-      </c>
-      <c r="AP42">
-        <v>-1567.649525642179</v>
       </c>
     </row>
     <row r="43">
@@ -5656,7 +5617,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TOMONY Holdings, Inc. (TSE:8600)</t>
+          <t>The Gunma Bank, Ltd. (TSE:8334)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5665,7 +5626,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.0101</v>
+        <v>0.0315</v>
       </c>
       <c r="E43">
         <v>0.0249</v>
@@ -5677,82 +5638,91 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>-0.0002596917924292194</v>
+        <v>0.0002742945215211107</v>
       </c>
       <c r="J43">
-        <v>-0.0001819421220514744</v>
+        <v>0.0002045354077112854</v>
       </c>
       <c r="K43">
-        <v>90.59999999999999</v>
+        <v>194.1</v>
       </c>
       <c r="L43">
-        <v>0.1879668049792531</v>
+        <v>0.1792243767313019</v>
       </c>
       <c r="M43">
-        <v>11.7622</v>
+        <v>96.4554</v>
       </c>
       <c r="N43">
-        <v>0.02593077601410934</v>
+        <v>0.05050549795790135</v>
       </c>
       <c r="O43">
-        <v>0.1298256070640177</v>
+        <v>0.4969366306027821</v>
       </c>
       <c r="P43">
-        <v>10.6722</v>
+        <v>49.5554</v>
       </c>
       <c r="Q43">
-        <v>0.02352777777777778</v>
+        <v>0.02594795266520054</v>
       </c>
       <c r="R43">
-        <v>0.117794701986755</v>
+        <v>0.2553086038124678</v>
       </c>
       <c r="S43">
-        <v>1.09</v>
+        <v>46.9</v>
       </c>
       <c r="T43">
-        <v>0.09266973865433337</v>
+        <v>0.4862350889633966</v>
       </c>
       <c r="U43">
-        <v>3252.6</v>
+        <v>11892.6</v>
       </c>
       <c r="V43">
-        <v>7.17063492063492</v>
+        <v>6.227144203581527</v>
       </c>
       <c r="W43">
-        <v>0.04074657072183494</v>
+        <v>0.05640310347833667</v>
       </c>
       <c r="X43">
-        <v>0.1314978257622283</v>
+        <v>0.1195653973992738</v>
       </c>
       <c r="Y43">
-        <v>-0.09075125504039341</v>
+        <v>-0.06316229392093715</v>
+      </c>
+      <c r="Z43">
+        <v>0.7292611584702517</v>
+      </c>
+      <c r="AA43">
+        <v>0.0001491597283757172</v>
       </c>
       <c r="AB43">
-        <v>0.06318292143449489</v>
+        <v>0.052536901175001</v>
+      </c>
+      <c r="AC43">
+        <v>-0.05238774144662528</v>
       </c>
       <c r="AD43">
-        <v>1526</v>
+        <v>10733.9</v>
       </c>
       <c r="AE43">
-        <v>5.775857219754418</v>
+        <v>2.164695165963185</v>
       </c>
       <c r="AF43">
-        <v>1531.775857219754</v>
+        <v>10736.06469516596</v>
       </c>
       <c r="AG43">
-        <v>-1720.824142780245</v>
+        <v>-1156.535304834037</v>
       </c>
       <c r="AH43">
-        <v>0.7715294067113295</v>
+        <v>0.848978298753264</v>
       </c>
       <c r="AI43">
-        <v>0.4814973381649573</v>
+        <v>0.754277998877693</v>
       </c>
       <c r="AJ43">
-        <v>1.357947725810224</v>
+        <v>-1.535363746975056</v>
       </c>
       <c r="AK43">
-        <v>24.12681142319821</v>
+        <v>-0.4940421815084416</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -5761,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="AN43">
-        <v>1481.553398058252</v>
+        <v>14703.97260273973</v>
       </c>
       <c r="AP43">
-        <v>-1670.703051242957</v>
+        <v>-1584.294938128817</v>
       </c>
     </row>
     <row r="44">
@@ -5775,7 +5745,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Kita-Nippon Bank, Ltd. (TSE:8551)</t>
+          <t>Kyoto Financial Group,Inc. (TSE:5844)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5784,10 +5754,13 @@
         </is>
       </c>
       <c r="D44">
-        <v>-0.009260000000000001</v>
+        <v>0.0134</v>
       </c>
       <c r="E44">
-        <v>-0.0143</v>
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="F44">
+        <v>0.148</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5796,88 +5769,103 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>-6.801811295766846e-06</v>
+        <v>-0.0005144557703029717</v>
       </c>
       <c r="J44">
-        <v>-5.422642185104444e-06</v>
+        <v>-0.0003725306708304812</v>
       </c>
       <c r="K44">
-        <v>17.3</v>
+        <v>204</v>
       </c>
       <c r="L44">
-        <v>0.110613810741688</v>
+        <v>0.267892317793828</v>
       </c>
       <c r="M44">
-        <v>4.9316</v>
+        <v>79.7032</v>
       </c>
       <c r="N44">
-        <v>0.03639557195571956</v>
+        <v>0.01719742804125491</v>
       </c>
       <c r="O44">
-        <v>0.2850635838150289</v>
+        <v>0.3907019607843137</v>
       </c>
       <c r="P44">
-        <v>3.7716</v>
+        <v>79.7032</v>
       </c>
       <c r="Q44">
-        <v>0.02783468634686347</v>
+        <v>0.01719742804125491</v>
       </c>
       <c r="R44">
-        <v>0.2180115606936416</v>
+        <v>0.3907019607843137</v>
       </c>
       <c r="S44">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>0.2352177792197259</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>1318.1</v>
+        <v>7651</v>
       </c>
       <c r="V44">
-        <v>9.727675276752766</v>
+        <v>1.650843654252794</v>
       </c>
       <c r="W44">
-        <v>0.02517462165308498</v>
+        <v>0.02912746119908049</v>
       </c>
       <c r="X44">
-        <v>0.1273354112641099</v>
+        <v>0.06973305857439908</v>
       </c>
       <c r="Y44">
-        <v>-0.1021607896110249</v>
+        <v>-0.0406055973753186</v>
+      </c>
+      <c r="Z44">
+        <v>0.1707759497696619</v>
+      </c>
+      <c r="AA44">
+        <v>-6.361927912940468e-05</v>
       </c>
       <c r="AB44">
-        <v>0.06320402217463507</v>
+        <v>0.0534769050461961</v>
+      </c>
+      <c r="AC44">
+        <v>-0.05354052432532551</v>
       </c>
       <c r="AD44">
-        <v>429.1</v>
+        <v>5849.4</v>
       </c>
       <c r="AE44">
-        <v>0.005319016433289673</v>
+        <v>7.558790345428565</v>
       </c>
       <c r="AF44">
-        <v>429.1053190164333</v>
+        <v>5856.958790345428</v>
       </c>
       <c r="AG44">
-        <v>-888.9946809835666</v>
+        <v>-1794.041209654572</v>
       </c>
       <c r="AH44">
-        <v>0.7600093455795868</v>
+        <v>0.5582543935926028</v>
       </c>
       <c r="AI44">
-        <v>0.4564924371549557</v>
+        <v>0.4548578833442069</v>
       </c>
       <c r="AJ44">
-        <v>1.179828741223663</v>
+        <v>-0.6315803833218342</v>
       </c>
       <c r="AK44">
-        <v>2.351248842408882</v>
+        <v>-0.3433270228767753</v>
       </c>
       <c r="AL44">
         <v>0</v>
       </c>
       <c r="AM44">
         <v>0</v>
+      </c>
+      <c r="AN44">
+        <v>5222.678571428571</v>
+      </c>
+      <c r="AP44">
+        <v>-1601.822508620153</v>
       </c>
     </row>
     <row r="45">
@@ -5888,115 +5876,472 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>The First Bank Of Toyama, Ltd. (TSE:7184)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>0.0312</v>
+      </c>
+      <c r="E45">
+        <v>-0.04269999999999999</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>29.2</v>
+      </c>
+      <c r="L45">
+        <v>0.1340064249655805</v>
+      </c>
+      <c r="M45">
+        <v>11.7457</v>
+      </c>
+      <c r="N45">
+        <v>0.03376171313595861</v>
+      </c>
+      <c r="O45">
+        <v>0.4022500000000001</v>
+      </c>
+      <c r="P45">
+        <v>10.2557</v>
+      </c>
+      <c r="Q45">
+        <v>0.02947887323943663</v>
+      </c>
+      <c r="R45">
+        <v>0.3512226027397261</v>
+      </c>
+      <c r="S45">
+        <v>1.49</v>
+      </c>
+      <c r="T45">
+        <v>0.126854934146113</v>
+      </c>
+      <c r="U45">
+        <v>479.8</v>
+      </c>
+      <c r="V45">
+        <v>1.379131934463927</v>
+      </c>
+      <c r="W45">
+        <v>0.03684077718899823</v>
+      </c>
+      <c r="X45">
+        <v>0.06191490360160581</v>
+      </c>
+      <c r="Y45">
+        <v>-0.02507412641260758</v>
+      </c>
+      <c r="Z45">
+        <v>0.3260511746221757</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0.05409493849417231</v>
+      </c>
+      <c r="AC45">
+        <v>-0.05409493849417231</v>
+      </c>
+      <c r="AD45">
+        <v>201.8</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>201.8</v>
+      </c>
+      <c r="AG45">
+        <v>-278</v>
+      </c>
+      <c r="AH45">
+        <v>0.3671093323631072</v>
+      </c>
+      <c r="AI45">
+        <v>0.1766456582633053</v>
+      </c>
+      <c r="AJ45">
+        <v>-3.977110157367669</v>
+      </c>
+      <c r="AK45">
+        <v>-0.4195593118019921</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Aichi Financial Group, Inc. (TSE:7389)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>-0.001840998015112174</v>
+      </c>
+      <c r="J46">
+        <v>-0.001831668231756053</v>
+      </c>
+      <c r="K46">
+        <v>615.4</v>
+      </c>
+      <c r="L46">
+        <v>1.221516474791584</v>
+      </c>
+      <c r="M46">
+        <v>22.324</v>
+      </c>
+      <c r="N46">
+        <v>0.0278840869347989</v>
+      </c>
+      <c r="O46">
+        <v>0.03627559311017224</v>
+      </c>
+      <c r="P46">
+        <v>18.424</v>
+      </c>
+      <c r="Q46">
+        <v>0.0230127404446665</v>
+      </c>
+      <c r="R46">
+        <v>0.02993825154371141</v>
+      </c>
+      <c r="S46">
+        <v>3.899999999999999</v>
+      </c>
+      <c r="T46">
+        <v>0.174699874574449</v>
+      </c>
+      <c r="U46">
+        <v>3770.5</v>
+      </c>
+      <c r="V46">
+        <v>4.709592805395953</v>
+      </c>
+      <c r="X46">
+        <v>0.1101977043006056</v>
+      </c>
+      <c r="Z46">
+        <v>59.46315090444448</v>
+      </c>
+      <c r="AA46">
+        <v>-0.1089167644717872</v>
+      </c>
+      <c r="AB46">
+        <v>0.05413845622543613</v>
+      </c>
+      <c r="AC46">
+        <v>-0.1630552206972233</v>
+      </c>
+      <c r="AD46">
+        <v>3836.3</v>
+      </c>
+      <c r="AE46">
+        <v>8.472474000067566</v>
+      </c>
+      <c r="AF46">
+        <v>3844.772474000068</v>
+      </c>
+      <c r="AG46">
+        <v>74.27247400006763</v>
+      </c>
+      <c r="AH46">
+        <v>0.8276564463924215</v>
+      </c>
+      <c r="AI46">
+        <v>0.6258101307110834</v>
+      </c>
+      <c r="AJ46">
+        <v>0.08489520039472849</v>
+      </c>
+      <c r="AK46">
+        <v>0.03129670296355608</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>0</v>
+      </c>
+      <c r="AN46">
+        <v>5001.694915254237</v>
+      </c>
+      <c r="AP46">
+        <v>96.83503780973615</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Tomato Bank, Ltd. (TSE:8542)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D45">
-        <v>0.0421</v>
-      </c>
-      <c r="E45">
-        <v>-0.0285</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>-0.0003232419855682374</v>
-      </c>
-      <c r="J45">
-        <v>-0.0002248111553764058</v>
-      </c>
-      <c r="K45">
-        <v>9.24</v>
-      </c>
-      <c r="L45">
-        <v>0.06277173913043479</v>
-      </c>
-      <c r="M45">
-        <v>52.579</v>
-      </c>
-      <c r="N45">
-        <v>0.5803421633554084</v>
-      </c>
-      <c r="O45">
-        <v>5.690367965367965</v>
-      </c>
-      <c r="P45">
-        <v>3.979</v>
-      </c>
-      <c r="Q45">
-        <v>0.04391832229580574</v>
-      </c>
-      <c r="R45">
-        <v>0.4306277056277056</v>
-      </c>
-      <c r="S45">
-        <v>48.6</v>
-      </c>
-      <c r="T45">
-        <v>0.9243233990756766</v>
-      </c>
-      <c r="U45">
-        <v>688.4</v>
-      </c>
-      <c r="V45">
-        <v>7.598233995584989</v>
-      </c>
-      <c r="W45">
-        <v>0.01951013513513513</v>
-      </c>
-      <c r="X45">
-        <v>0.130279395399328</v>
-      </c>
-      <c r="Y45">
-        <v>-0.1107692602641929</v>
-      </c>
-      <c r="AB45">
-        <v>0.06318888539457376</v>
-      </c>
-      <c r="AD45">
-        <v>299.4</v>
-      </c>
-      <c r="AE45">
-        <v>0.9779061013782226</v>
-      </c>
-      <c r="AF45">
-        <v>300.3779061013782</v>
-      </c>
-      <c r="AG45">
-        <v>-388.0220938986218</v>
-      </c>
-      <c r="AH45">
-        <v>0.768273351035575</v>
-      </c>
-      <c r="AI45">
-        <v>0.44687262609324</v>
-      </c>
-      <c r="AJ45">
-        <v>1.30461758510409</v>
-      </c>
-      <c r="AK45">
-        <v>23.91935938255098</v>
-      </c>
-      <c r="AL45">
-        <v>0</v>
-      </c>
-      <c r="AM45">
-        <v>0</v>
-      </c>
-      <c r="AN45">
-        <v>2022.972972972973</v>
-      </c>
-      <c r="AP45">
-        <v>-2621.770904720418</v>
+      <c r="D47">
+        <v>0.0616</v>
+      </c>
+      <c r="E47">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>-0.0006647865091046765</v>
+      </c>
+      <c r="J47">
+        <v>-0.0004625130529807535</v>
+      </c>
+      <c r="K47">
+        <v>11.4</v>
+      </c>
+      <c r="L47">
+        <v>0.07707910750507099</v>
+      </c>
+      <c r="M47">
+        <v>3.8595</v>
+      </c>
+      <c r="N47">
+        <v>0.04101487778958555</v>
+      </c>
+      <c r="O47">
+        <v>0.3385526315789474</v>
+      </c>
+      <c r="P47">
+        <v>3.8525</v>
+      </c>
+      <c r="Q47">
+        <v>0.04094048884165782</v>
+      </c>
+      <c r="R47">
+        <v>0.337938596491228</v>
+      </c>
+      <c r="S47">
+        <v>0.007000000000000117</v>
+      </c>
+      <c r="T47">
+        <v>0.001813706438657888</v>
+      </c>
+      <c r="U47">
+        <v>542.8</v>
+      </c>
+      <c r="V47">
+        <v>5.768331562167907</v>
+      </c>
+      <c r="W47">
+        <v>0.03066164604626143</v>
+      </c>
+      <c r="X47">
+        <v>0.08743544432886957</v>
+      </c>
+      <c r="Y47">
+        <v>-0.05677379828260815</v>
+      </c>
+      <c r="AB47">
+        <v>0.04992233130066781</v>
+      </c>
+      <c r="AD47">
+        <v>263.8</v>
+      </c>
+      <c r="AE47">
+        <v>0.7916096234829083</v>
+      </c>
+      <c r="AF47">
+        <v>264.5916096234829</v>
+      </c>
+      <c r="AG47">
+        <v>-278.2083903765171</v>
+      </c>
+      <c r="AH47">
+        <v>0.7376576494254315</v>
+      </c>
+      <c r="AI47">
+        <v>0.4173424468197923</v>
+      </c>
+      <c r="AJ47">
+        <v>1.51111195859981</v>
+      </c>
+      <c r="AK47">
+        <v>-3.05081127008504</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>0</v>
+      </c>
+      <c r="AN47">
+        <v>4396.666666666667</v>
+      </c>
+      <c r="AP47">
+        <v>-4636.806506275285</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>The Keiyo Bank, Ltd. (TSE:8544)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>0.0126</v>
+      </c>
+      <c r="E48">
+        <v>-0.0259</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>-0.000148847035380458</v>
+      </c>
+      <c r="J48">
+        <v>-0.0001040529432283452</v>
+      </c>
+      <c r="K48">
+        <v>65.7</v>
+      </c>
+      <c r="L48">
+        <v>0.1476404494382023</v>
+      </c>
+      <c r="M48">
+        <v>25.1632</v>
+      </c>
+      <c r="N48">
+        <v>0.0414823606989779</v>
+      </c>
+      <c r="O48">
+        <v>0.3830015220700151</v>
+      </c>
+      <c r="P48">
+        <v>18.4632</v>
+      </c>
+      <c r="Q48">
+        <v>0.0304371909000989</v>
+      </c>
+      <c r="R48">
+        <v>0.2810228310502282</v>
+      </c>
+      <c r="S48">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="T48">
+        <v>0.2662618426909137</v>
+      </c>
+      <c r="U48">
+        <v>8014.7</v>
+      </c>
+      <c r="V48">
+        <v>13.21249587866799</v>
+      </c>
+      <c r="W48">
+        <v>0.03360441921129354</v>
+      </c>
+      <c r="X48">
+        <v>0.1606420396336463</v>
+      </c>
+      <c r="Y48">
+        <v>-0.1270376204223528</v>
+      </c>
+      <c r="AB48">
+        <v>0.04872760057174844</v>
+      </c>
+      <c r="AD48">
+        <v>5579.2</v>
+      </c>
+      <c r="AE48">
+        <v>9.831184653721518</v>
+      </c>
+      <c r="AF48">
+        <v>5589.031184653722</v>
+      </c>
+      <c r="AG48">
+        <v>-2425.668815346278</v>
+      </c>
+      <c r="AH48">
+        <v>0.9020922998931055</v>
+      </c>
+      <c r="AI48">
+        <v>0.7349316571197777</v>
+      </c>
+      <c r="AJ48">
+        <v>1.333467318488733</v>
+      </c>
+      <c r="AK48">
+        <v>5.918158992644874</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>0</v>
+      </c>
+      <c r="AN48">
+        <v>2936.421052631579</v>
+      </c>
+      <c r="AP48">
+        <v>-1276.667797550673</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0394</v>
+        <v>0.0335</v>
       </c>
       <c r="E2">
-        <v>0.0592</v>
+        <v>0.0408</v>
       </c>
       <c r="F2">
-        <v>0.159</v>
+        <v>0.147</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.000132364352990408</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>9.375675571358346E-05</v>
       </c>
       <c r="K2">
-        <v>940.3</v>
+        <v>4538</v>
       </c>
       <c r="L2">
-        <v>0.2301441613432215</v>
+        <v>0.1886855213591345</v>
       </c>
       <c r="M2">
-        <v>580.5872000000001</v>
+        <v>2124.87491</v>
       </c>
       <c r="N2">
-        <v>0.0521965279463459</v>
+        <v>0.04478861501234131</v>
       </c>
       <c r="O2">
-        <v>0.6174488992874615</v>
+        <v>0.4682403944468929</v>
       </c>
       <c r="P2">
-        <v>346.3872</v>
+        <v>1405.65991</v>
       </c>
       <c r="Q2">
-        <v>0.03114124659492408</v>
+        <v>0.02962883144366947</v>
       </c>
       <c r="R2">
-        <v>0.3683794533659471</v>
+        <v>0.3097531754076686</v>
       </c>
       <c r="S2">
-        <v>234.2</v>
+        <v>719.215</v>
       </c>
       <c r="T2">
-        <v>0.4033847112027272</v>
+        <v>0.3384740422202077</v>
       </c>
       <c r="U2">
-        <v>64864.6</v>
+        <v>262211.1</v>
       </c>
       <c r="V2">
-        <v>5.831521787990757</v>
+        <v>5.526947470927842</v>
       </c>
       <c r="W2">
-        <v>0.06147116225856383</v>
+        <v>0.04518654313035723</v>
       </c>
       <c r="X2">
-        <v>0.1159189339723065</v>
+        <v>0.1075507646826663</v>
       </c>
       <c r="Y2">
-        <v>-0.05444777171374268</v>
+        <v>-0.06236422155230902</v>
       </c>
       <c r="Z2">
-        <v>0.4252747939045715</v>
+        <v>0.3127318294837019</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05511989512398434</v>
+        <v>0.05483463616884646</v>
       </c>
       <c r="AC2">
-        <v>-0.05511989512398434</v>
+        <v>-0.05483463616884646</v>
       </c>
       <c r="AD2">
-        <v>58519.7</v>
+        <v>265551.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>39.36778945984447</v>
       </c>
       <c r="AF2">
-        <v>58519.7</v>
+        <v>265590.5677894598</v>
       </c>
       <c r="AG2">
-        <v>-6344.900000000001</v>
+        <v>3379.467789459857</v>
       </c>
       <c r="AH2">
-        <v>0.8402835612583066</v>
+        <v>0.8484430713777034</v>
       </c>
       <c r="AI2">
-        <v>0.7481376365530775</v>
+        <v>0.7245094210738222</v>
       </c>
       <c r="AJ2">
-        <v>-1.327884977606631</v>
+        <v>0.06649646276493237</v>
       </c>
       <c r="AK2">
-        <v>-0.4750634551022396</v>
+        <v>0.03238006791722559</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>24016.56868951795</v>
+      </c>
+      <c r="AP2">
+        <v>305.640570630357</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Hachijuni Bank, Ltd. (TSE:8359)</t>
+          <t>The Hyakugo Bank, Ltd. (TSE:8368)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0394</v>
+        <v>0.0495</v>
       </c>
       <c r="E3">
-        <v>0.0408</v>
+        <v>0.066</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,97 +731,103 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.001608789220734364</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.00115758353050798</v>
       </c>
       <c r="K3">
-        <v>210.1</v>
+        <v>105.7</v>
       </c>
       <c r="L3">
-        <v>0.1670908223317958</v>
+        <v>0.1492094861660079</v>
       </c>
       <c r="M3">
-        <v>176.4132</v>
+        <v>59.8408</v>
       </c>
       <c r="N3">
-        <v>0.05904649061150719</v>
+        <v>0.06053085170948817</v>
       </c>
       <c r="O3">
-        <v>0.8396630176106616</v>
+        <v>0.5661381267738884</v>
       </c>
       <c r="P3">
-        <v>87.2132</v>
+        <v>27.5408</v>
       </c>
       <c r="Q3">
-        <v>0.02919074873648626</v>
+        <v>0.02785838559579203</v>
       </c>
       <c r="R3">
-        <v>0.4151032841504046</v>
+        <v>0.2605562913907285</v>
       </c>
       <c r="S3">
-        <v>89.20000000000002</v>
+        <v>32.3</v>
       </c>
       <c r="T3">
-        <v>0.5056310978997037</v>
+        <v>0.5397655111562679</v>
       </c>
       <c r="U3">
-        <v>20836.7</v>
+        <v>6639.2</v>
       </c>
       <c r="V3">
-        <v>6.974160725641799</v>
+        <v>6.715759660125429</v>
       </c>
       <c r="W3">
-        <v>0.0324870113805047</v>
+        <v>0.03715028820469563</v>
       </c>
       <c r="X3">
-        <v>0.1322498957614037</v>
+        <v>0.1257077751592466</v>
       </c>
       <c r="Y3">
-        <v>-0.099762884380899</v>
+        <v>-0.08855748695455101</v>
       </c>
       <c r="Z3">
-        <v>0.1842452304896991</v>
+        <v>0.387675451831901</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.0004487667182228483</v>
       </c>
       <c r="AB3">
-        <v>0.05488054633147165</v>
+        <v>0.05287587097204942</v>
       </c>
       <c r="AC3">
-        <v>-0.05488054633147165</v>
+        <v>-0.05242710425382657</v>
       </c>
       <c r="AD3">
-        <v>19811.6</v>
+        <v>5949.9</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>4.901668580158884</v>
       </c>
       <c r="AF3">
-        <v>19811.6</v>
+        <v>5954.801668580159</v>
       </c>
       <c r="AG3">
-        <v>-1025.100000000002</v>
+        <v>-684.3983314198413</v>
       </c>
       <c r="AH3">
-        <v>0.8689565030505322</v>
+        <v>0.8576202202915106</v>
       </c>
       <c r="AI3">
-        <v>0.7238436244062842</v>
+        <v>0.6501441811252595</v>
       </c>
       <c r="AJ3">
-        <v>-0.5223173341485802</v>
+        <v>-2.249817808739266</v>
       </c>
       <c r="AK3">
-        <v>-0.1569038617543971</v>
+        <v>-0.2715864596254219</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>2806.556603773585</v>
+      </c>
+      <c r="AP3">
+        <v>-322.8294016131326</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Chiba Bank, Ltd. (TSE:8331)</t>
+          <t>The Shimizu Bank, Ltd. (TSE:8364)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +847,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0297</v>
-      </c>
-      <c r="E4">
-        <v>0.0592</v>
-      </c>
-      <c r="F4">
-        <v>0.159</v>
+        <v>0.00468</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +862,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>456.7</v>
+        <v>-15.6</v>
       </c>
       <c r="L4">
-        <v>0.2663595007581943</v>
+        <v>-0.08112324492979718</v>
       </c>
       <c r="M4">
-        <v>243.7988</v>
+        <v>7.0692</v>
       </c>
       <c r="N4">
-        <v>0.04398715381145692</v>
+        <v>0.06836750483558994</v>
       </c>
       <c r="O4">
-        <v>0.5338270199255529</v>
+        <v>-0.4531538461538462</v>
       </c>
       <c r="P4">
-        <v>173.8988</v>
+        <v>4.3392</v>
       </c>
       <c r="Q4">
-        <v>0.03137551646368967</v>
+        <v>0.04196518375241779</v>
       </c>
       <c r="R4">
-        <v>0.3807724983577841</v>
+        <v>-0.2781538461538461</v>
       </c>
       <c r="S4">
-        <v>69.90000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="T4">
-        <v>0.2867118295906297</v>
+        <v>0.3861823120013581</v>
       </c>
       <c r="U4">
-        <v>33013.6</v>
+        <v>1475.1</v>
       </c>
       <c r="V4">
-        <v>5.956445647271087</v>
+        <v>14.26595744680851</v>
       </c>
       <c r="W4">
-        <v>0.06147116225856383</v>
+        <v>-0.03286286075416052</v>
       </c>
       <c r="X4">
-        <v>0.1159189339723065</v>
+        <v>0.1469071582142011</v>
       </c>
       <c r="Y4">
-        <v>-0.05444777171374268</v>
+        <v>-0.1797700189683616</v>
       </c>
       <c r="Z4">
-        <v>3.863452005407816</v>
+        <v>0.3363064008394544</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05511989512398434</v>
+        <v>0.05257085460832239</v>
       </c>
       <c r="AC4">
-        <v>-0.05511989512398434</v>
+        <v>-0.05257085460832239</v>
       </c>
       <c r="AD4">
-        <v>28300.7</v>
+        <v>827.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>28300.7</v>
+        <v>827.6</v>
       </c>
       <c r="AG4">
-        <v>-4712.899999999998</v>
+        <v>-647.4999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.8362300255295009</v>
+        <v>0.888936627282492</v>
       </c>
       <c r="AI4">
-        <v>0.775807999122783</v>
+        <v>0.6031190788514794</v>
       </c>
       <c r="AJ4">
-        <v>-5.680930568948874</v>
+        <v>1.190038595846352</v>
       </c>
       <c r="AK4">
-        <v>-1.359987303053037</v>
+        <v>6.292517006802728</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,117 +957,3843 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Juroku Financial Group,Inc. (TSE:7380)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0413</v>
+      </c>
+      <c r="E5">
+        <v>0.116</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.0005730361422764969</v>
+      </c>
+      <c r="J5">
+        <v>0.0003976793014537667</v>
+      </c>
+      <c r="K5">
+        <v>141</v>
+      </c>
+      <c r="L5">
+        <v>0.1684185379837554</v>
+      </c>
+      <c r="M5">
+        <v>41.7452</v>
+      </c>
+      <c r="N5">
+        <v>0.04272356974721113</v>
+      </c>
+      <c r="O5">
+        <v>0.2960652482269504</v>
+      </c>
+      <c r="P5">
+        <v>22.5452</v>
+      </c>
+      <c r="Q5">
+        <v>0.02307358509876164</v>
+      </c>
+      <c r="R5">
+        <v>0.1598950354609929</v>
+      </c>
+      <c r="S5">
+        <v>19.2</v>
+      </c>
+      <c r="T5">
+        <v>0.4599331180590823</v>
+      </c>
+      <c r="U5">
+        <v>7180.5</v>
+      </c>
+      <c r="V5">
+        <v>7.348787227509979</v>
+      </c>
+      <c r="W5">
+        <v>0.05137922238822286</v>
+      </c>
+      <c r="X5">
+        <v>0.1088250445870477</v>
+      </c>
+      <c r="Y5">
+        <v>-0.05744582219882484</v>
+      </c>
+      <c r="Z5">
+        <v>1.737285313170587</v>
+      </c>
+      <c r="AA5">
+        <v>0.0006908824097675674</v>
+      </c>
+      <c r="AB5">
+        <v>0.05327744760221748</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05258656519244991</v>
+      </c>
+      <c r="AD5">
+        <v>4338.4</v>
+      </c>
+      <c r="AE5">
+        <v>6.101270708430584</v>
+      </c>
+      <c r="AF5">
+        <v>4344.501270708431</v>
+      </c>
+      <c r="AG5">
+        <v>-2835.998729291569</v>
+      </c>
+      <c r="AH5">
+        <v>0.8163898514196789</v>
+      </c>
+      <c r="AI5">
+        <v>0.5917003321570372</v>
+      </c>
+      <c r="AJ5">
+        <v>1.525633798443864</v>
+      </c>
+      <c r="AK5">
+        <v>-17.51684046012796</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>2552</v>
+      </c>
+      <c r="AP5">
+        <v>-1668.2345466421</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hirogin Holdings, Inc. (TSE:7337)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0489</v>
+      </c>
+      <c r="E6">
+        <v>0.0172</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>205.7</v>
+      </c>
+      <c r="L6">
+        <v>0.2091297275315169</v>
+      </c>
+      <c r="M6">
+        <v>111.9722</v>
+      </c>
+      <c r="N6">
+        <v>0.04999428494887709</v>
+      </c>
+      <c r="O6">
+        <v>0.5443471074380166</v>
+      </c>
+      <c r="P6">
+        <v>89.87220000000001</v>
+      </c>
+      <c r="Q6">
+        <v>0.04012689199446355</v>
+      </c>
+      <c r="R6">
+        <v>0.436909090909091</v>
+      </c>
+      <c r="S6">
+        <v>22.10000000000001</v>
+      </c>
+      <c r="T6">
+        <v>0.1973704187289345</v>
+      </c>
+      <c r="U6">
+        <v>11847.1</v>
+      </c>
+      <c r="V6">
+        <v>5.289592356119123</v>
+      </c>
+      <c r="W6">
+        <v>0.06165512693702604</v>
+      </c>
+      <c r="X6">
+        <v>0.1388758916117872</v>
+      </c>
+      <c r="Y6">
+        <v>-0.07722076467476113</v>
+      </c>
+      <c r="Z6">
+        <v>0.6139058794158044</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.0526691859447755</v>
+      </c>
+      <c r="AC6">
+        <v>-0.0526691859447755</v>
+      </c>
+      <c r="AD6">
+        <v>16245.9</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>16245.9</v>
+      </c>
+      <c r="AG6">
+        <v>4398.799999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.8788408274548839</v>
+      </c>
+      <c r="AI6">
+        <v>0.8122462652240865</v>
+      </c>
+      <c r="AJ6">
+        <v>0.6626195676734202</v>
+      </c>
+      <c r="AK6">
+        <v>0.5394586772298597</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chugin Financial Group,Inc. (TSE:5832)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0321</v>
+      </c>
+      <c r="E7">
+        <v>0.111</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.0003878286628235026</v>
+      </c>
+      <c r="J7">
+        <v>0.0002689487813286527</v>
+      </c>
+      <c r="K7">
+        <v>178.5</v>
+      </c>
+      <c r="L7">
+        <v>0.2120708090768682</v>
+      </c>
+      <c r="M7">
+        <v>97.81200000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.05240958045330334</v>
+      </c>
+      <c r="O7">
+        <v>0.5479663865546219</v>
+      </c>
+      <c r="P7">
+        <v>58.712</v>
+      </c>
+      <c r="Q7">
+        <v>0.03145903659647431</v>
+      </c>
+      <c r="R7">
+        <v>0.3289187675070028</v>
+      </c>
+      <c r="S7">
+        <v>39.10000000000001</v>
+      </c>
+      <c r="T7">
+        <v>0.3997464523780314</v>
+      </c>
+      <c r="U7">
+        <v>9165</v>
+      </c>
+      <c r="V7">
+        <v>4.910786047259283</v>
+      </c>
+      <c r="W7">
+        <v>0.04953517413625642</v>
+      </c>
+      <c r="X7">
+        <v>0.1314238197870213</v>
+      </c>
+      <c r="Y7">
+        <v>-0.08188864565076492</v>
+      </c>
+      <c r="Z7">
+        <v>0.3886740424531224</v>
+      </c>
+      <c r="AA7">
+        <v>0.0001045334100518483</v>
+      </c>
+      <c r="AB7">
+        <v>0.05277788826773108</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05267335485767923</v>
+      </c>
+      <c r="AD7">
+        <v>12235.9</v>
+      </c>
+      <c r="AE7">
+        <v>2.267823072507289</v>
+      </c>
+      <c r="AF7">
+        <v>12238.16782307251</v>
+      </c>
+      <c r="AG7">
+        <v>3073.167823072507</v>
+      </c>
+      <c r="AH7">
+        <v>0.8676802256270137</v>
+      </c>
+      <c r="AI7">
+        <v>0.7543682832705254</v>
+      </c>
+      <c r="AJ7">
+        <v>0.6221657743608699</v>
+      </c>
+      <c r="AK7">
+        <v>0.4354120561191633</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>15687.05128205128</v>
+      </c>
+      <c r="AP7">
+        <v>3939.958747528854</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>San ju San Financial Group,Inc. (TSE:7322)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0111</v>
+      </c>
+      <c r="E8">
+        <v>0.08</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>54.4</v>
+      </c>
+      <c r="L8">
+        <v>0.1154009333899024</v>
+      </c>
+      <c r="M8">
+        <v>14.718</v>
+      </c>
+      <c r="N8">
+        <v>0.03897775423728813</v>
+      </c>
+      <c r="O8">
+        <v>0.2705514705882353</v>
+      </c>
+      <c r="P8">
+        <v>14.69</v>
+      </c>
+      <c r="Q8">
+        <v>0.03890360169491525</v>
+      </c>
+      <c r="R8">
+        <v>0.2700367647058823</v>
+      </c>
+      <c r="S8">
+        <v>0.02800000000000047</v>
+      </c>
+      <c r="T8">
+        <v>0.001902432395705971</v>
+      </c>
+      <c r="U8">
+        <v>3446.2</v>
+      </c>
+      <c r="V8">
+        <v>9.126588983050846</v>
+      </c>
+      <c r="W8">
+        <v>0.04111866969009826</v>
+      </c>
+      <c r="X8">
+        <v>0.1341568694537804</v>
+      </c>
+      <c r="Y8">
+        <v>-0.09303819976368211</v>
+      </c>
+      <c r="Z8">
+        <v>0.7725335955424447</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.05273577215627168</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05273577215627168</v>
+      </c>
+      <c r="AD8">
+        <v>2572.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>2572.5</v>
+      </c>
+      <c r="AG8">
+        <v>-873.6999999999998</v>
+      </c>
+      <c r="AH8">
+        <v>0.8720043388359717</v>
+      </c>
+      <c r="AI8">
+        <v>0.6349813640066151</v>
+      </c>
+      <c r="AJ8">
+        <v>1.761136867567023</v>
+      </c>
+      <c r="AK8">
+        <v>-1.443893571310527</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The Ogaki Kyoritsu Bank, Ltd. (TSE:8361)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0254</v>
+      </c>
+      <c r="E9">
+        <v>0.09119999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="L9">
+        <v>0.08287545787545789</v>
+      </c>
+      <c r="M9">
+        <v>20.3704</v>
+      </c>
+      <c r="N9">
+        <v>0.03973161692997854</v>
+      </c>
+      <c r="O9">
+        <v>0.2813591160220995</v>
+      </c>
+      <c r="P9">
+        <v>20.3424</v>
+      </c>
+      <c r="Q9">
+        <v>0.03967700409596255</v>
+      </c>
+      <c r="R9">
+        <v>0.2809723756906077</v>
+      </c>
+      <c r="S9">
+        <v>0.02799999999999869</v>
+      </c>
+      <c r="T9">
+        <v>0.001374543455209455</v>
+      </c>
+      <c r="U9">
+        <v>5852.8</v>
+      </c>
+      <c r="V9">
+        <v>11.41564267602887</v>
+      </c>
+      <c r="W9">
+        <v>0.03582739509105305</v>
+      </c>
+      <c r="X9">
+        <v>0.1262269771453726</v>
+      </c>
+      <c r="Y9">
+        <v>-0.09039958205431957</v>
+      </c>
+      <c r="Z9">
+        <v>0.5361482754388119</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.05286636000061742</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05286636000061742</v>
+      </c>
+      <c r="AD9">
+        <v>3113.1</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>3113.1</v>
+      </c>
+      <c r="AG9">
+        <v>-2739.7</v>
+      </c>
+      <c r="AH9">
+        <v>0.8585967234817143</v>
+      </c>
+      <c r="AI9">
+        <v>0.5762652252785903</v>
+      </c>
+      <c r="AJ9">
+        <v>1.230220026942075</v>
+      </c>
+      <c r="AK9">
+        <v>6.080115401686636</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The Yamagata Bank, Ltd. (TSE:8344)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0308</v>
+      </c>
+      <c r="E10">
+        <v>-0.0659</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>18.2</v>
+      </c>
+      <c r="L10">
+        <v>0.05341943058409158</v>
+      </c>
+      <c r="M10">
+        <v>7.989</v>
+      </c>
+      <c r="N10">
+        <v>0.03920019627085378</v>
+      </c>
+      <c r="O10">
+        <v>0.438956043956044</v>
+      </c>
+      <c r="P10">
+        <v>7.808</v>
+      </c>
+      <c r="Q10">
+        <v>0.03831207065750736</v>
+      </c>
+      <c r="R10">
+        <v>0.429010989010989</v>
+      </c>
+      <c r="S10">
+        <v>0.181</v>
+      </c>
+      <c r="T10">
+        <v>0.02265615220928778</v>
+      </c>
+      <c r="U10">
+        <v>1434.4</v>
+      </c>
+      <c r="V10">
+        <v>7.038272816486752</v>
+      </c>
+      <c r="W10">
+        <v>0.02071241606919312</v>
+      </c>
+      <c r="X10">
+        <v>0.1075507646826663</v>
+      </c>
+      <c r="Y10">
+        <v>-0.08683834861347313</v>
+      </c>
+      <c r="Z10">
+        <v>0.3704871683340582</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.05331740862550632</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05331740862550632</v>
+      </c>
+      <c r="AD10">
+        <v>881.9</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>881.9</v>
+      </c>
+      <c r="AG10">
+        <v>-552.5000000000001</v>
+      </c>
+      <c r="AH10">
+        <v>0.8122870037763654</v>
+      </c>
+      <c r="AI10">
+        <v>0.4699957365167342</v>
+      </c>
+      <c r="AJ10">
+        <v>1.584456552910811</v>
+      </c>
+      <c r="AK10">
+        <v>-1.250000000000001</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The Tottori Bank, Ltd. (TSE:8383)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.009140000000000001</v>
+      </c>
+      <c r="E11">
+        <v>0.00991</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>7.11</v>
+      </c>
+      <c r="L11">
+        <v>0.07563829787234043</v>
+      </c>
+      <c r="M11">
+        <v>3.26664</v>
+      </c>
+      <c r="N11">
+        <v>0.04402479784366577</v>
+      </c>
+      <c r="O11">
+        <v>0.4594430379746835</v>
+      </c>
+      <c r="P11">
+        <v>3.26664</v>
+      </c>
+      <c r="Q11">
+        <v>0.04402479784366577</v>
+      </c>
+      <c r="R11">
+        <v>0.4594430379746835</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>783.4</v>
+      </c>
+      <c r="V11">
+        <v>10.55795148247978</v>
+      </c>
+      <c r="W11">
+        <v>0.02192414431082331</v>
+      </c>
+      <c r="X11">
+        <v>0.1035712647284817</v>
+      </c>
+      <c r="Y11">
+        <v>-0.0816471204176584</v>
+      </c>
+      <c r="Z11">
+        <v>1.718464351005483</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.0534545643264239</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0534545643264239</v>
+      </c>
+      <c r="AD11">
+        <v>293.5</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>293.5</v>
+      </c>
+      <c r="AG11">
+        <v>-489.9</v>
+      </c>
+      <c r="AH11">
+        <v>0.7982050584715801</v>
+      </c>
+      <c r="AI11">
+        <v>0.4609706298099576</v>
+      </c>
+      <c r="AJ11">
+        <v>1.178494106326678</v>
+      </c>
+      <c r="AK11">
+        <v>3.339468302658487</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The San-in Godo Bank,Ltd. (TSE:8381)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0573</v>
+      </c>
+      <c r="E12">
+        <v>0.07519999999999999</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>129.3</v>
+      </c>
+      <c r="L12">
+        <v>0.1737903225806452</v>
+      </c>
+      <c r="M12">
+        <v>61.7594</v>
+      </c>
+      <c r="N12">
+        <v>0.0504487828786146</v>
+      </c>
+      <c r="O12">
+        <v>0.4776442382057231</v>
+      </c>
+      <c r="P12">
+        <v>47.7594</v>
+      </c>
+      <c r="Q12">
+        <v>0.03901274301584708</v>
+      </c>
+      <c r="R12">
+        <v>0.369368909512761</v>
+      </c>
+      <c r="S12">
+        <v>14</v>
+      </c>
+      <c r="T12">
+        <v>0.2266861400855578</v>
+      </c>
+      <c r="U12">
+        <v>5267.6</v>
+      </c>
+      <c r="V12">
+        <v>4.3028916843653</v>
+      </c>
+      <c r="W12">
+        <v>0.06333578251285819</v>
+      </c>
+      <c r="X12">
+        <v>0.101920765649744</v>
+      </c>
+      <c r="Y12">
+        <v>-0.03858498313688578</v>
+      </c>
+      <c r="Z12">
+        <v>0.3059713768711959</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.05351768096695389</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05351768096695389</v>
+      </c>
+      <c r="AD12">
+        <v>4653.6</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>4653.6</v>
+      </c>
+      <c r="AG12">
+        <v>-614</v>
+      </c>
+      <c r="AH12">
+        <v>0.7917247949913233</v>
+      </c>
+      <c r="AI12">
+        <v>0.6732931116801945</v>
+      </c>
+      <c r="AJ12">
+        <v>-1.006227466404457</v>
+      </c>
+      <c r="AK12">
+        <v>-0.3734566023964479</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Tohoku Bank, Ltd. (TSE:8349)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.00231</v>
+      </c>
+      <c r="E13">
+        <v>0.0815</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>9.41</v>
+      </c>
+      <c r="L13">
+        <v>0.1050223214285714</v>
+      </c>
+      <c r="M13">
+        <v>3.3155</v>
+      </c>
+      <c r="N13">
+        <v>0.04729671897289586</v>
+      </c>
+      <c r="O13">
+        <v>0.3523379383634431</v>
+      </c>
+      <c r="P13">
+        <v>3.3155</v>
+      </c>
+      <c r="Q13">
+        <v>0.04729671897289586</v>
+      </c>
+      <c r="R13">
+        <v>0.3523379383634431</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>673.8</v>
+      </c>
+      <c r="V13">
+        <v>9.611982881597717</v>
+      </c>
+      <c r="W13">
+        <v>0.03740063593004769</v>
+      </c>
+      <c r="X13">
+        <v>0.1011612262124453</v>
+      </c>
+      <c r="Y13">
+        <v>-0.06376059028239765</v>
+      </c>
+      <c r="Z13">
+        <v>4.691099476439785</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.05354810887799069</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05354810887799069</v>
+      </c>
+      <c r="AD13">
+        <v>261.5</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>261.5</v>
+      </c>
+      <c r="AG13">
+        <v>-412.3</v>
+      </c>
+      <c r="AH13">
+        <v>0.7886007237635705</v>
+      </c>
+      <c r="AI13">
+        <v>0.4905271056087038</v>
+      </c>
+      <c r="AJ13">
+        <v>1.204850964348334</v>
+      </c>
+      <c r="AK13">
+        <v>2.930348258706469</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Shizuoka Financial Group,Inc. (TSE:5831)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0493</v>
+      </c>
+      <c r="E14">
+        <v>0.109</v>
+      </c>
+      <c r="F14">
+        <v>0.135</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>473.4</v>
+      </c>
+      <c r="L14">
+        <v>0.2759706190975865</v>
+      </c>
+      <c r="M14">
+        <v>236.0032</v>
+      </c>
+      <c r="N14">
+        <v>0.0525701557035618</v>
+      </c>
+      <c r="O14">
+        <v>0.4985280946345585</v>
+      </c>
+      <c r="P14">
+        <v>180.2032</v>
+      </c>
+      <c r="Q14">
+        <v>0.0401406009845633</v>
+      </c>
+      <c r="R14">
+        <v>0.3806573722010985</v>
+      </c>
+      <c r="S14">
+        <v>55.79999999999998</v>
+      </c>
+      <c r="T14">
+        <v>0.2364374720342774</v>
+      </c>
+      <c r="U14">
+        <v>7476.7</v>
+      </c>
+      <c r="V14">
+        <v>1.665448956407458</v>
+      </c>
+      <c r="W14">
+        <v>0.06239455925769717</v>
+      </c>
+      <c r="X14">
+        <v>0.1002801213946765</v>
+      </c>
+      <c r="Y14">
+        <v>-0.03788556213697929</v>
+      </c>
+      <c r="Z14">
+        <v>0.1272325402005578</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05358457073234733</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05358457073234733</v>
+      </c>
+      <c r="AD14">
+        <v>16377.3</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>16377.3</v>
+      </c>
+      <c r="AG14">
+        <v>8900.599999999999</v>
+      </c>
+      <c r="AH14">
+        <v>0.7848571401186586</v>
+      </c>
+      <c r="AI14">
+        <v>0.6606920256090624</v>
+      </c>
+      <c r="AJ14">
+        <v>0.6647249045922673</v>
+      </c>
+      <c r="AK14">
+        <v>0.5141467472301489</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Bank of Nagoya, Ltd. (TSE:8522)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.0785</v>
+      </c>
+      <c r="E15">
+        <v>0.153</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.002190321904229671</v>
+      </c>
+      <c r="J15">
+        <v>0.001552330944586449</v>
+      </c>
+      <c r="K15">
+        <v>91</v>
+      </c>
+      <c r="L15">
+        <v>0.1410196807686347</v>
+      </c>
+      <c r="M15">
+        <v>51.108</v>
+      </c>
+      <c r="N15">
+        <v>0.07622371364653244</v>
+      </c>
+      <c r="O15">
+        <v>0.5616263736263736</v>
+      </c>
+      <c r="P15">
+        <v>24.108</v>
+      </c>
+      <c r="Q15">
+        <v>0.03595525727069351</v>
+      </c>
+      <c r="R15">
+        <v>0.2649230769230769</v>
+      </c>
+      <c r="S15">
+        <v>27</v>
+      </c>
+      <c r="T15">
+        <v>0.5282930265320498</v>
+      </c>
+      <c r="U15">
+        <v>5477.8</v>
+      </c>
+      <c r="V15">
+        <v>8.16972408650261</v>
+      </c>
+      <c r="W15">
+        <v>0.05202378230048022</v>
+      </c>
+      <c r="X15">
+        <v>0.1047200017975234</v>
+      </c>
+      <c r="Y15">
+        <v>-0.05269621949704314</v>
+      </c>
+      <c r="Z15">
+        <v>1.030282734349831</v>
+      </c>
+      <c r="AA15">
+        <v>0.001599339770204382</v>
+      </c>
+      <c r="AB15">
+        <v>0.05536157231662329</v>
+      </c>
+      <c r="AC15">
+        <v>-0.0537622325464189</v>
+      </c>
+      <c r="AD15">
+        <v>2721.8</v>
+      </c>
+      <c r="AE15">
+        <v>2.332926376002967</v>
+      </c>
+      <c r="AF15">
+        <v>2724.132926376003</v>
+      </c>
+      <c r="AG15">
+        <v>-2753.667073623997</v>
+      </c>
+      <c r="AH15">
+        <v>0.8024823259120969</v>
+      </c>
+      <c r="AI15">
+        <v>0.5833844560745365</v>
+      </c>
+      <c r="AJ15">
+        <v>1.321865686381822</v>
+      </c>
+      <c r="AK15">
+        <v>3.406877706000669</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>1447.765957446809</v>
+      </c>
+      <c r="AP15">
+        <v>-1464.716528523403</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fukuoka Financial Group, Inc. (TSE:8354)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0556</v>
+      </c>
+      <c r="E16">
+        <v>-0.152</v>
+      </c>
+      <c r="F16">
+        <v>0.173</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>489.1</v>
+      </c>
+      <c r="L16">
+        <v>0.2331045658183205</v>
+      </c>
+      <c r="M16">
+        <v>161.8065</v>
+      </c>
+      <c r="N16">
+        <v>0.03410329637904144</v>
+      </c>
+      <c r="O16">
+        <v>0.3308249846657125</v>
+      </c>
+      <c r="P16">
+        <v>161.6805</v>
+      </c>
+      <c r="Q16">
+        <v>0.03407673987269738</v>
+      </c>
+      <c r="R16">
+        <v>0.3305673686362707</v>
+      </c>
+      <c r="S16">
+        <v>0.1260000000000048</v>
+      </c>
+      <c r="T16">
+        <v>0.0007787079011041261</v>
+      </c>
+      <c r="U16">
+        <v>52670.1</v>
+      </c>
+      <c r="V16">
+        <v>11.10106226025376</v>
+      </c>
+      <c r="W16">
+        <v>0.08150851581508516</v>
+      </c>
+      <c r="X16">
+        <v>0.2171545387498949</v>
+      </c>
+      <c r="Y16">
+        <v>-0.1356460229348098</v>
+      </c>
+      <c r="Z16">
+        <v>0.1584180842148179</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05438712124536875</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05438712124536875</v>
+      </c>
+      <c r="AD16">
+        <v>69110.89999999999</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>69110.89999999999</v>
+      </c>
+      <c r="AG16">
+        <v>16440.8</v>
+      </c>
+      <c r="AH16">
+        <v>0.9357583389185639</v>
+      </c>
+      <c r="AI16">
+        <v>0.9076520996815182</v>
+      </c>
+      <c r="AJ16">
+        <v>0.77604387927535</v>
+      </c>
+      <c r="AK16">
+        <v>0.7004311446635197</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Taiko Bank,Ltd. (TSE:8537)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>-0.0169</v>
+      </c>
+      <c r="E17">
+        <v>0.0248</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0.000224181234707398</v>
+      </c>
+      <c r="J17">
+        <v>0.0001457621071516481</v>
+      </c>
+      <c r="K17">
+        <v>16.2</v>
+      </c>
+      <c r="L17">
+        <v>0.1232876712328767</v>
+      </c>
+      <c r="M17">
+        <v>3.65952</v>
+      </c>
+      <c r="N17">
+        <v>0.04149115646258503</v>
+      </c>
+      <c r="O17">
+        <v>0.2258962962962963</v>
+      </c>
+      <c r="P17">
+        <v>3.65952</v>
+      </c>
+      <c r="Q17">
+        <v>0.04149115646258503</v>
+      </c>
+      <c r="R17">
+        <v>0.2258962962962963</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>1037.3</v>
+      </c>
+      <c r="V17">
+        <v>11.76077097505669</v>
+      </c>
+      <c r="W17">
+        <v>0.03335392217418159</v>
+      </c>
+      <c r="X17">
+        <v>0.1549406470759105</v>
+      </c>
+      <c r="Y17">
+        <v>-0.1215867249017289</v>
+      </c>
+      <c r="Z17">
+        <v>0.8246894036048964</v>
+      </c>
+      <c r="AA17">
+        <v>0.0001202084652150857</v>
+      </c>
+      <c r="AB17">
+        <v>0.05466698319551147</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05454677473029639</v>
+      </c>
+      <c r="AD17">
+        <v>770</v>
+      </c>
+      <c r="AE17">
+        <v>2.13271292879724</v>
+      </c>
+      <c r="AF17">
+        <v>772.1327129287972</v>
+      </c>
+      <c r="AG17">
+        <v>-265.1672870712027</v>
+      </c>
+      <c r="AH17">
+        <v>0.8974815223522721</v>
+      </c>
+      <c r="AI17">
+        <v>0.5865786858786083</v>
+      </c>
+      <c r="AJ17">
+        <v>1.498397197921177</v>
+      </c>
+      <c r="AK17">
+        <v>-0.9503089594332521</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>1688.59649122807</v>
+      </c>
+      <c r="AP17">
+        <v>-581.5072084894797</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nishi-Nippon Financial Holdings, Inc. (TSE:7189)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0408</v>
+      </c>
+      <c r="E18">
+        <v>0.0288</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>171.6</v>
+      </c>
+      <c r="L18">
+        <v>0.1561561561561561</v>
+      </c>
+      <c r="M18">
+        <v>72.5343</v>
+      </c>
+      <c r="N18">
+        <v>0.04025881112282844</v>
+      </c>
+      <c r="O18">
+        <v>0.422694055944056</v>
+      </c>
+      <c r="P18">
+        <v>58.53429999999999</v>
+      </c>
+      <c r="Q18">
+        <v>0.03248837209302325</v>
+      </c>
+      <c r="R18">
+        <v>0.3411089743589744</v>
+      </c>
+      <c r="S18">
+        <v>14.00000000000001</v>
+      </c>
+      <c r="T18">
+        <v>0.1930121335699111</v>
+      </c>
+      <c r="U18">
+        <v>13827.4</v>
+      </c>
+      <c r="V18">
+        <v>7.674640617194871</v>
+      </c>
+      <c r="W18">
+        <v>0.04869742891197003</v>
+      </c>
+      <c r="X18">
+        <v>0.1558687345551515</v>
+      </c>
+      <c r="Y18">
+        <v>-0.1071713056431815</v>
+      </c>
+      <c r="Z18">
+        <v>0.2153945666235447</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.05466037949018912</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05466037949018912</v>
+      </c>
+      <c r="AD18">
+        <v>15928.9</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>15928.9</v>
+      </c>
+      <c r="AG18">
+        <v>2101.5</v>
+      </c>
+      <c r="AH18">
+        <v>0.8983847134332736</v>
+      </c>
+      <c r="AI18">
+        <v>0.7957685966928111</v>
+      </c>
+      <c r="AJ18">
+        <v>0.5384043861447018</v>
+      </c>
+      <c r="AK18">
+        <v>0.3395211322217914</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kyushu Financial Group, Inc. (TSE:7180)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.0335</v>
+      </c>
+      <c r="E19">
+        <v>0.0353</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>176.5</v>
+      </c>
+      <c r="L19">
+        <v>0.1370022510284871</v>
+      </c>
+      <c r="M19">
+        <v>54.5076</v>
+      </c>
+      <c r="N19">
+        <v>0.02725107489251075</v>
+      </c>
+      <c r="O19">
+        <v>0.3088249291784703</v>
+      </c>
+      <c r="P19">
+        <v>54.5076</v>
+      </c>
+      <c r="Q19">
+        <v>0.02725107489251075</v>
+      </c>
+      <c r="R19">
+        <v>0.3088249291784703</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>15054.8</v>
+      </c>
+      <c r="V19">
+        <v>7.526647335266473</v>
+      </c>
+      <c r="W19">
+        <v>0.03870953592420388</v>
+      </c>
+      <c r="X19">
+        <v>0.1358550261971355</v>
+      </c>
+      <c r="Y19">
+        <v>-0.09714549027293165</v>
+      </c>
+      <c r="Z19">
+        <v>0.4394078924929222</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05483463616884646</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05483463616884646</v>
+      </c>
+      <c r="AD19">
+        <v>13944.2</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>13944.2</v>
+      </c>
+      <c r="AG19">
+        <v>-1110.599999999999</v>
+      </c>
+      <c r="AH19">
+        <v>0.8745515666942625</v>
+      </c>
+      <c r="AI19">
+        <v>0.7384017411288741</v>
+      </c>
+      <c r="AJ19">
+        <v>-1.248426258992802</v>
+      </c>
+      <c r="AK19">
+        <v>-0.2900117508813156</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Shiga Bank, Ltd. (TSE:8366)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.0271</v>
+      </c>
+      <c r="E20">
+        <v>-0.0359</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="L20">
+        <v>0.1259830835435525</v>
+      </c>
+      <c r="M20">
+        <v>41.8117</v>
+      </c>
+      <c r="N20">
+        <v>0.03563598397681753</v>
+      </c>
+      <c r="O20">
+        <v>0.4924817432273262</v>
+      </c>
+      <c r="P20">
+        <v>27.8117</v>
+      </c>
+      <c r="Q20">
+        <v>0.02370382681326174</v>
+      </c>
+      <c r="R20">
+        <v>0.3275818610129564</v>
+      </c>
+      <c r="S20">
+        <v>14</v>
+      </c>
+      <c r="T20">
+        <v>0.3348345080443991</v>
+      </c>
+      <c r="U20">
+        <v>6887.9</v>
+      </c>
+      <c r="V20">
+        <v>5.87053609477542</v>
+      </c>
+      <c r="W20">
+        <v>0.02764481781772004</v>
+      </c>
+      <c r="X20">
+        <v>0.1337333842535289</v>
+      </c>
+      <c r="Y20">
+        <v>-0.1060885664358089</v>
+      </c>
+      <c r="Z20">
+        <v>0.2295768890100157</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.05485802318728553</v>
+      </c>
+      <c r="AC20">
+        <v>-0.05485802318728553</v>
+      </c>
+      <c r="AD20">
+        <v>7947</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>7947</v>
+      </c>
+      <c r="AG20">
+        <v>1059.1</v>
+      </c>
+      <c r="AH20">
+        <v>0.8713529160224993</v>
+      </c>
+      <c r="AI20">
+        <v>0.7060799104406003</v>
+      </c>
+      <c r="AJ20">
+        <v>0.4744221465687153</v>
+      </c>
+      <c r="AK20">
+        <v>0.2425123649019967</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Bank Of Kochi, Ltd. (TSE:8416)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.0117</v>
+      </c>
+      <c r="E21">
+        <v>-0.0236</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>10.1</v>
+      </c>
+      <c r="L21">
+        <v>0.06300686213349968</v>
+      </c>
+      <c r="M21">
+        <v>1.0605</v>
+      </c>
+      <c r="N21">
+        <v>0.01974860335195531</v>
+      </c>
+      <c r="O21">
+        <v>0.105</v>
+      </c>
+      <c r="P21">
+        <v>1.0605</v>
+      </c>
+      <c r="Q21">
+        <v>0.01974860335195531</v>
+      </c>
+      <c r="R21">
+        <v>0.105</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>533.7</v>
+      </c>
+      <c r="V21">
+        <v>9.938547486033519</v>
+      </c>
+      <c r="W21">
+        <v>0.02730467693971344</v>
+      </c>
+      <c r="X21">
+        <v>0.1333903101343114</v>
+      </c>
+      <c r="Y21">
+        <v>-0.106085633194598</v>
+      </c>
+      <c r="Z21">
+        <v>0.8664864864864871</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.05486191740064071</v>
+      </c>
+      <c r="AC21">
+        <v>-0.05486191740064071</v>
+      </c>
+      <c r="AD21">
+        <v>362</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>362</v>
+      </c>
+      <c r="AG21">
+        <v>-171.7</v>
+      </c>
+      <c r="AH21">
+        <v>0.8708203031031995</v>
+      </c>
+      <c r="AI21">
+        <v>0.4599161478846398</v>
+      </c>
+      <c r="AJ21">
+        <v>1.455084745762712</v>
+      </c>
+      <c r="AK21">
+        <v>-0.6775848460931336</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Hachijuni Bank, Ltd. (TSE:8359)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.0394</v>
+      </c>
+      <c r="E22">
+        <v>0.0408</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>210.1</v>
+      </c>
+      <c r="L22">
+        <v>0.1670908223317958</v>
+      </c>
+      <c r="M22">
+        <v>176.4132</v>
+      </c>
+      <c r="N22">
+        <v>0.05904649061150719</v>
+      </c>
+      <c r="O22">
+        <v>0.8396630176106616</v>
+      </c>
+      <c r="P22">
+        <v>87.2132</v>
+      </c>
+      <c r="Q22">
+        <v>0.02919074873648626</v>
+      </c>
+      <c r="R22">
+        <v>0.4151032841504046</v>
+      </c>
+      <c r="S22">
+        <v>89.20000000000002</v>
+      </c>
+      <c r="T22">
+        <v>0.5056310978997037</v>
+      </c>
+      <c r="U22">
+        <v>20836.7</v>
+      </c>
+      <c r="V22">
+        <v>6.974160725641799</v>
+      </c>
+      <c r="W22">
+        <v>0.0324870113805047</v>
+      </c>
+      <c r="X22">
+        <v>0.1322117274593794</v>
+      </c>
+      <c r="Y22">
+        <v>-0.09972471607887473</v>
+      </c>
+      <c r="Z22">
+        <v>0.1842452304896991</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.05487554462370177</v>
+      </c>
+      <c r="AC22">
+        <v>-0.05487554462370177</v>
+      </c>
+      <c r="AD22">
+        <v>19811.6</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>19811.6</v>
+      </c>
+      <c r="AG22">
+        <v>-1025.100000000002</v>
+      </c>
+      <c r="AH22">
+        <v>0.8689565030505322</v>
+      </c>
+      <c r="AI22">
+        <v>0.7238436244062842</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.5223173341485802</v>
+      </c>
+      <c r="AK22">
+        <v>-0.1569038617543971</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tomato Bank, Ltd. (TSE:8542)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.0447</v>
+      </c>
+      <c r="E23">
+        <v>-0.0202</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>-0.0008474435738472881</v>
+      </c>
+      <c r="J23">
+        <v>-0.0005607774760273412</v>
+      </c>
+      <c r="K23">
+        <v>10.7</v>
+      </c>
+      <c r="L23">
+        <v>0.06441902468392534</v>
+      </c>
+      <c r="M23">
+        <v>4.369499999999999</v>
+      </c>
+      <c r="N23">
+        <v>0.04838870431893687</v>
+      </c>
+      <c r="O23">
+        <v>0.4083644859813084</v>
+      </c>
+      <c r="P23">
+        <v>4.0135</v>
+      </c>
+      <c r="Q23">
+        <v>0.04444629014396456</v>
+      </c>
+      <c r="R23">
+        <v>0.3750934579439252</v>
+      </c>
+      <c r="S23">
+        <v>0.3559999999999999</v>
+      </c>
+      <c r="T23">
+        <v>0.08147385284357476</v>
+      </c>
+      <c r="U23">
+        <v>913.6</v>
+      </c>
+      <c r="V23">
+        <v>10.11738648947951</v>
+      </c>
+      <c r="W23">
+        <v>0.02896589063345966</v>
+      </c>
+      <c r="X23">
+        <v>0.09424769269838262</v>
+      </c>
+      <c r="Y23">
+        <v>-0.06528180206492296</v>
+      </c>
+      <c r="Z23">
+        <v>1.812649880039587</v>
+      </c>
+      <c r="AA23">
+        <v>-0.001016493224649863</v>
+      </c>
+      <c r="AB23">
+        <v>0.05387367660407368</v>
+      </c>
+      <c r="AC23">
+        <v>-0.05489016982872354</v>
+      </c>
+      <c r="AD23">
+        <v>277.3</v>
+      </c>
+      <c r="AE23">
+        <v>1.233801888080173</v>
+      </c>
+      <c r="AF23">
+        <v>278.5338018880802</v>
+      </c>
+      <c r="AG23">
+        <v>-635.0661981119199</v>
+      </c>
+      <c r="AH23">
+        <v>0.7551742830029422</v>
+      </c>
+      <c r="AI23">
+        <v>0.4140942680939272</v>
+      </c>
+      <c r="AJ23">
+        <v>1.165759183137586</v>
+      </c>
+      <c r="AK23">
+        <v>2.635499099408769</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>2616.037735849057</v>
+      </c>
+      <c r="AP23">
+        <v>-5991.19054822566</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Bank of Toyama, Ltd. (TSE:8365)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.008289999999999999</v>
+      </c>
+      <c r="E24">
+        <v>-0.0211</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>9.68</v>
+      </c>
+      <c r="L24">
+        <v>0.1464447806354009</v>
+      </c>
+      <c r="M24">
+        <v>0.9292499999999999</v>
+      </c>
+      <c r="N24">
+        <v>0.01756616257088847</v>
+      </c>
+      <c r="O24">
+        <v>0.09599690082644627</v>
+      </c>
+      <c r="P24">
+        <v>0.9292499999999999</v>
+      </c>
+      <c r="Q24">
+        <v>0.01756616257088847</v>
+      </c>
+      <c r="R24">
+        <v>0.09599690082644627</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>278.5</v>
+      </c>
+      <c r="V24">
+        <v>5.264650283553875</v>
+      </c>
+      <c r="W24">
+        <v>0.04992264053635895</v>
+      </c>
+      <c r="X24">
+        <v>0.07984563963349177</v>
+      </c>
+      <c r="Y24">
+        <v>-0.02992299909713282</v>
+      </c>
+      <c r="Z24">
+        <v>6.417475728155332</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.05504492624562857</v>
+      </c>
+      <c r="AC24">
+        <v>-0.05504492624562857</v>
+      </c>
+      <c r="AD24">
+        <v>92</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>92</v>
+      </c>
+      <c r="AG24">
+        <v>-186.5</v>
+      </c>
+      <c r="AH24">
+        <v>0.6349206349206349</v>
+      </c>
+      <c r="AI24">
+        <v>0.301540478531629</v>
+      </c>
+      <c r="AJ24">
+        <v>1.395958083832335</v>
+      </c>
+      <c r="AK24">
+        <v>-7.011278195488723</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Chiba Bank, Ltd. (TSE:8331)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.0297</v>
+      </c>
+      <c r="E25">
+        <v>0.0592</v>
+      </c>
+      <c r="F25">
+        <v>0.159</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>456.7</v>
+      </c>
+      <c r="L25">
+        <v>0.2663595007581943</v>
+      </c>
+      <c r="M25">
+        <v>243.7988</v>
+      </c>
+      <c r="N25">
+        <v>0.04398715381145692</v>
+      </c>
+      <c r="O25">
+        <v>0.5338270199255529</v>
+      </c>
+      <c r="P25">
+        <v>173.8988</v>
+      </c>
+      <c r="Q25">
+        <v>0.03137551646368967</v>
+      </c>
+      <c r="R25">
+        <v>0.3807724983577841</v>
+      </c>
+      <c r="S25">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="T25">
+        <v>0.2867118295906297</v>
+      </c>
+      <c r="U25">
+        <v>33013.6</v>
+      </c>
+      <c r="V25">
+        <v>5.956445647271087</v>
+      </c>
+      <c r="W25">
+        <v>0.06147116225856383</v>
+      </c>
+      <c r="X25">
+        <v>0.1158879759170549</v>
+      </c>
+      <c r="Y25">
+        <v>-0.0544168136584911</v>
+      </c>
+      <c r="Z25">
+        <v>3.863452005407816</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.05511482512406613</v>
+      </c>
+      <c r="AC25">
+        <v>-0.05511482512406613</v>
+      </c>
+      <c r="AD25">
+        <v>28300.7</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>28300.7</v>
+      </c>
+      <c r="AG25">
+        <v>-4712.899999999998</v>
+      </c>
+      <c r="AH25">
+        <v>0.8362300255295009</v>
+      </c>
+      <c r="AI25">
+        <v>0.775807999122783</v>
+      </c>
+      <c r="AJ25">
+        <v>-5.680930568948874</v>
+      </c>
+      <c r="AK25">
+        <v>-1.359987303053037</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yamaguchi Financial Group, Inc. (TSE:8418)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.0335</v>
+      </c>
+      <c r="E26">
+        <v>0.0392</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>-3.595514197724977E-05</v>
+      </c>
+      <c r="J26">
+        <v>-2.375933291293407E-05</v>
+      </c>
+      <c r="K26">
+        <v>194.2</v>
+      </c>
+      <c r="L26">
+        <v>0.1678914152329904</v>
+      </c>
+      <c r="M26">
+        <v>104.0174</v>
+      </c>
+      <c r="N26">
+        <v>0.04677882712718116</v>
+      </c>
+      <c r="O26">
+        <v>0.5356199794026777</v>
+      </c>
+      <c r="P26">
+        <v>32.8174</v>
+      </c>
+      <c r="Q26">
+        <v>0.01475867961863645</v>
+      </c>
+      <c r="R26">
+        <v>0.1689876416065912</v>
+      </c>
+      <c r="S26">
+        <v>71.20000000000002</v>
+      </c>
+      <c r="T26">
+        <v>0.6845008623557214</v>
+      </c>
+      <c r="U26">
+        <v>12347</v>
+      </c>
+      <c r="V26">
+        <v>5.552707321460694</v>
+      </c>
+      <c r="W26">
+        <v>0.04700130693644416</v>
+      </c>
+      <c r="X26">
+        <v>0.1067357133913801</v>
+      </c>
+      <c r="Y26">
+        <v>-0.05973440645493593</v>
+      </c>
+      <c r="Z26">
+        <v>0.8686294972180216</v>
+      </c>
+      <c r="AA26">
+        <v>-2.063805740239752E-05</v>
+      </c>
+      <c r="AB26">
+        <v>0.05530978561829579</v>
+      </c>
+      <c r="AC26">
+        <v>-0.05533042367569819</v>
+      </c>
+      <c r="AD26">
+        <v>9448</v>
+      </c>
+      <c r="AE26">
+        <v>4.837946563625424</v>
+      </c>
+      <c r="AF26">
+        <v>9452.837946563626</v>
+      </c>
+      <c r="AG26">
+        <v>-2894.162053436374</v>
+      </c>
+      <c r="AH26">
+        <v>0.8095652107109939</v>
+      </c>
+      <c r="AI26">
+        <v>0.6776306637233889</v>
+      </c>
+      <c r="AJ26">
+        <v>4.316024204777024</v>
+      </c>
+      <c r="AK26">
+        <v>-1.805648574543208</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>10203.02375809935</v>
+      </c>
+      <c r="AP26">
+        <v>-3125.444982112715</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>The Gunma Bank, Ltd. (TSE:8334)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D27">
         <v>0.0521</v>
       </c>
-      <c r="E5">
+      <c r="E27">
         <v>0.152</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <v>273.5</v>
       </c>
-      <c r="L5">
+      <c r="L27">
         <v>0.2455778037173386</v>
       </c>
-      <c r="M5">
+      <c r="M27">
         <v>160.3752</v>
       </c>
-      <c r="N5">
+      <c r="N27">
         <v>0.06185167187319218</v>
       </c>
-      <c r="O5">
+      <c r="O27">
         <v>0.5863809872029251</v>
       </c>
-      <c r="P5">
+      <c r="P27">
         <v>85.2752</v>
       </c>
-      <c r="Q5">
+      <c r="Q27">
         <v>0.03288796328435342</v>
       </c>
-      <c r="R5">
+      <c r="R27">
         <v>0.3117923217550274</v>
       </c>
-      <c r="S5">
+      <c r="S27">
         <v>75.10000000000001</v>
       </c>
-      <c r="T5">
+      <c r="T27">
         <v>0.4682768906913289</v>
       </c>
-      <c r="U5">
+      <c r="U27">
         <v>11014.3</v>
       </c>
-      <c r="V5">
+      <c r="V27">
         <v>4.247869181225655</v>
       </c>
-      <c r="W5">
+      <c r="W27">
         <v>0.07819871336669049</v>
       </c>
-      <c r="X5">
-        <v>0.1042209363640767</v>
-      </c>
-      <c r="Y5">
-        <v>-0.02602222299738619</v>
-      </c>
-      <c r="Z5">
+      <c r="X27">
+        <v>0.1041951430658425</v>
+      </c>
+      <c r="Y27">
+        <v>-0.02599642969915206</v>
+      </c>
+      <c r="Z27">
         <v>0.4761843680519927</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05538083949080267</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05538083949080267</v>
-      </c>
-      <c r="AD5">
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.05537569503698304</v>
+      </c>
+      <c r="AC27">
+        <v>-0.05537569503698304</v>
+      </c>
+      <c r="AD27">
         <v>10407.4</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
         <v>10407.4</v>
       </c>
-      <c r="AG5">
+      <c r="AG27">
         <v>-606.8999999999996</v>
       </c>
-      <c r="AH5">
+      <c r="AH27">
         <v>0.8005507565210034</v>
       </c>
-      <c r="AI5">
+      <c r="AI27">
         <v>0.7241693629753331</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ27">
         <v>-0.3055891238670692</v>
       </c>
-      <c r="AK5">
+      <c r="AK27">
         <v>-0.1807756463719765</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aichi Financial Group, Inc. (TSE:7389)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>-0.001171107381294844</v>
+      </c>
+      <c r="J28">
+        <v>-0.0008079011159230833</v>
+      </c>
+      <c r="K28">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="L28">
+        <v>0.1148626282687852</v>
+      </c>
+      <c r="M28">
+        <v>17.1919</v>
+      </c>
+      <c r="N28">
+        <v>0.02191726160122387</v>
+      </c>
+      <c r="O28">
+        <v>0.2477219020172911</v>
+      </c>
+      <c r="P28">
+        <v>17.1359</v>
+      </c>
+      <c r="Q28">
+        <v>0.02184586945436002</v>
+      </c>
+      <c r="R28">
+        <v>0.2469149855907781</v>
+      </c>
+      <c r="S28">
+        <v>0.05600000000000094</v>
+      </c>
+      <c r="T28">
+        <v>0.003257347937109972</v>
+      </c>
+      <c r="U28">
+        <v>4904.6</v>
+      </c>
+      <c r="V28">
+        <v>6.252677205507394</v>
+      </c>
+      <c r="W28">
+        <v>0.03026734702778141</v>
+      </c>
+      <c r="X28">
+        <v>0.1112203136451448</v>
+      </c>
+      <c r="Y28">
+        <v>-0.08095296661736334</v>
+      </c>
+      <c r="Z28">
+        <v>0.2554742919440223</v>
+      </c>
+      <c r="AA28">
+        <v>-0.0002063979655512352</v>
+      </c>
+      <c r="AB28">
+        <v>0.05520690863844685</v>
+      </c>
+      <c r="AC28">
+        <v>-0.05541330660399808</v>
+      </c>
+      <c r="AD28">
+        <v>3656.9</v>
+      </c>
+      <c r="AE28">
+        <v>6.312915398891724</v>
+      </c>
+      <c r="AF28">
+        <v>3663.212915398892</v>
+      </c>
+      <c r="AG28">
+        <v>-1241.387084601109</v>
+      </c>
+      <c r="AH28">
+        <v>0.8236357311392398</v>
+      </c>
+      <c r="AI28">
+        <v>0.5885045327616396</v>
+      </c>
+      <c r="AJ28">
+        <v>2.716459887886506</v>
+      </c>
+      <c r="AK28">
+        <v>-0.9404355594702473</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>6589.009009009009</v>
+      </c>
+      <c r="AP28">
+        <v>-2236.733485767763</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kyoto Financial Group,Inc. (TSE:5844)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0.0121</v>
+      </c>
+      <c r="E29">
+        <v>0.00649</v>
+      </c>
+      <c r="F29">
+        <v>0.126</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>-0.000215142996283279</v>
+      </c>
+      <c r="J29">
+        <v>-0.0001543502964160772</v>
+      </c>
+      <c r="K29">
+        <v>234.5</v>
+      </c>
+      <c r="L29">
+        <v>0.2600354845863828</v>
+      </c>
+      <c r="M29">
+        <v>131.708</v>
+      </c>
+      <c r="N29">
+        <v>0.0305431102453504</v>
+      </c>
+      <c r="O29">
+        <v>0.5616545842217484</v>
+      </c>
+      <c r="P29">
+        <v>40.908</v>
+      </c>
+      <c r="Q29">
+        <v>0.009486572978989843</v>
+      </c>
+      <c r="R29">
+        <v>0.1744477611940299</v>
+      </c>
+      <c r="S29">
+        <v>90.8</v>
+      </c>
+      <c r="T29">
+        <v>0.6894038327208674</v>
+      </c>
+      <c r="U29">
+        <v>6920.5</v>
+      </c>
+      <c r="V29">
+        <v>1.604865265989518</v>
+      </c>
+      <c r="W29">
+        <v>0.03349952143540806</v>
+      </c>
+      <c r="X29">
+        <v>0.07683180086105589</v>
+      </c>
+      <c r="Y29">
+        <v>-0.04333227942564782</v>
+      </c>
+      <c r="Z29">
+        <v>0.1732766221967552</v>
+      </c>
+      <c r="AA29">
+        <v>-2.67452979980458E-05</v>
+      </c>
+      <c r="AB29">
+        <v>0.05545228740540131</v>
+      </c>
+      <c r="AC29">
+        <v>-0.05547903270339935</v>
+      </c>
+      <c r="AD29">
+        <v>6279.5</v>
+      </c>
+      <c r="AE29">
+        <v>5.895079770241305</v>
+      </c>
+      <c r="AF29">
+        <v>6285.395079770241</v>
+      </c>
+      <c r="AG29">
+        <v>-635.104920229759</v>
+      </c>
+      <c r="AH29">
+        <v>0.5930963612459998</v>
+      </c>
+      <c r="AI29">
+        <v>0.4543737351275863</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.1727191999260032</v>
+      </c>
+      <c r="AK29">
+        <v>-0.09187648240649857</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>6375.1269035533</v>
+      </c>
+      <c r="AP29">
+        <v>-644.7765687611767</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Ehime Bank, Ltd. (TSE:8541)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.0257</v>
+      </c>
+      <c r="E30">
+        <v>-0.0306</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0.0009397571827781711</v>
+      </c>
+      <c r="J30">
+        <v>0.0006709707004157704</v>
+      </c>
+      <c r="K30">
+        <v>33.7</v>
+      </c>
+      <c r="L30">
+        <v>0.1047234307022996</v>
+      </c>
+      <c r="M30">
+        <v>10.157</v>
+      </c>
+      <c r="N30">
+        <v>0.03657544112351459</v>
+      </c>
+      <c r="O30">
+        <v>0.3013946587537092</v>
+      </c>
+      <c r="P30">
+        <v>9.243</v>
+      </c>
+      <c r="Q30">
+        <v>0.03328411955347498</v>
+      </c>
+      <c r="R30">
+        <v>0.274272997032641</v>
+      </c>
+      <c r="S30">
+        <v>0.9139999999999997</v>
+      </c>
+      <c r="T30">
+        <v>0.08998720094516094</v>
+      </c>
+      <c r="U30">
+        <v>1580.9</v>
+      </c>
+      <c r="V30">
+        <v>5.692833993518185</v>
+      </c>
+      <c r="W30">
+        <v>0.0397874852420307</v>
+      </c>
+      <c r="X30">
+        <v>0.07284838524936274</v>
+      </c>
+      <c r="Y30">
+        <v>-0.03306090000733204</v>
+      </c>
+      <c r="Z30">
+        <v>0.9416710275697072</v>
+      </c>
+      <c r="AA30">
+        <v>0.0006318336689296847</v>
+      </c>
+      <c r="AB30">
+        <v>0.05615946021918811</v>
+      </c>
+      <c r="AC30">
+        <v>-0.05552762655025842</v>
+      </c>
+      <c r="AD30">
+        <v>300.3</v>
+      </c>
+      <c r="AE30">
+        <v>1.132930692909923</v>
+      </c>
+      <c r="AF30">
+        <v>301.4329306929099</v>
+      </c>
+      <c r="AG30">
+        <v>-1279.46706930709</v>
+      </c>
+      <c r="AH30">
+        <v>0.5204900545583847</v>
+      </c>
+      <c r="AI30">
+        <v>0.2353229614682888</v>
+      </c>
+      <c r="AJ30">
+        <v>1.277210150451523</v>
+      </c>
+      <c r="AK30">
+        <v>4.265358435052883</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>567.6748582230624</v>
+      </c>
+      <c r="AP30">
+        <v>-2418.652304928337</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The Awa Bank, Ltd. (TSE:8388)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.0267</v>
+      </c>
+      <c r="E31">
+        <v>0.0279</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>91.2</v>
+      </c>
+      <c r="L31">
+        <v>0.1937539834289356</v>
+      </c>
+      <c r="M31">
+        <v>25.1321</v>
+      </c>
+      <c r="N31">
+        <v>0.03634432393347795</v>
+      </c>
+      <c r="O31">
+        <v>0.2755712719298246</v>
+      </c>
+      <c r="P31">
+        <v>11.1321</v>
+      </c>
+      <c r="Q31">
+        <v>0.01609848156182213</v>
+      </c>
+      <c r="R31">
+        <v>0.1220625</v>
+      </c>
+      <c r="S31">
+        <v>14</v>
+      </c>
+      <c r="T31">
+        <v>0.5570565133832827</v>
+      </c>
+      <c r="U31">
+        <v>2673</v>
+      </c>
+      <c r="V31">
+        <v>3.865509761388287</v>
+      </c>
+      <c r="W31">
+        <v>0.04518654313035723</v>
+      </c>
+      <c r="X31">
+        <v>0.07632529363062523</v>
+      </c>
+      <c r="Y31">
+        <v>-0.031138750500268</v>
+      </c>
+      <c r="Z31">
+        <v>7.5312</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.05553008975532725</v>
+      </c>
+      <c r="AC31">
+        <v>-0.05553008975532725</v>
+      </c>
+      <c r="AD31">
+        <v>975.2</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>975.2</v>
+      </c>
+      <c r="AG31">
+        <v>-1697.8</v>
+      </c>
+      <c r="AH31">
+        <v>0.5851082978340433</v>
+      </c>
+      <c r="AI31">
+        <v>0.2881626381419538</v>
+      </c>
+      <c r="AJ31">
+        <v>1.687170823809997</v>
+      </c>
+      <c r="AK31">
+        <v>-2.387232845894263</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>The Bank of Saga Ltd. (TSE:8395)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0559</v>
+      </c>
+      <c r="E32">
+        <v>0.264</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>47.4</v>
+      </c>
+      <c r="L32">
+        <v>0.1339361401525855</v>
+      </c>
+      <c r="M32">
+        <v>10.0287</v>
+      </c>
+      <c r="N32">
+        <v>0.04227951096121416</v>
+      </c>
+      <c r="O32">
+        <v>0.2115759493670886</v>
+      </c>
+      <c r="P32">
+        <v>10.0217</v>
+      </c>
+      <c r="Q32">
+        <v>0.04225</v>
+      </c>
+      <c r="R32">
+        <v>0.2114282700421941</v>
+      </c>
+      <c r="S32">
+        <v>0.006999999999999673</v>
+      </c>
+      <c r="T32">
+        <v>0.000697996749329392</v>
+      </c>
+      <c r="U32">
+        <v>1996.5</v>
+      </c>
+      <c r="V32">
+        <v>8.416947723440135</v>
+      </c>
+      <c r="W32">
+        <v>0.0648160809517298</v>
+      </c>
+      <c r="X32">
+        <v>0.07457810338023668</v>
+      </c>
+      <c r="Y32">
+        <v>-0.009762022428506878</v>
+      </c>
+      <c r="Z32">
+        <v>1.032983070636311</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.05582361344967048</v>
+      </c>
+      <c r="AC32">
+        <v>-0.05582361344967048</v>
+      </c>
+      <c r="AD32">
+        <v>295.8</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>295.8</v>
+      </c>
+      <c r="AG32">
+        <v>-1700.7</v>
+      </c>
+      <c r="AH32">
+        <v>0.5549718574108818</v>
+      </c>
+      <c r="AI32">
+        <v>0.2576879519121875</v>
+      </c>
+      <c r="AJ32">
+        <v>1.162077212162624</v>
+      </c>
+      <c r="AK32">
+        <v>2.004124440254537</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Iyogin Holdings,Inc. (TSE:5830)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.0861</v>
+      </c>
+      <c r="E33">
+        <v>0.201</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0.0005306236684716472</v>
+      </c>
+      <c r="J33">
+        <v>0.0003731003777636193</v>
+      </c>
+      <c r="K33">
+        <v>311.9</v>
+      </c>
+      <c r="L33">
+        <v>0.2872007366482505</v>
+      </c>
+      <c r="M33">
+        <v>148.6884</v>
+      </c>
+      <c r="N33">
+        <v>0.05081974160913254</v>
+      </c>
+      <c r="O33">
+        <v>0.4767181789034948</v>
+      </c>
+      <c r="P33">
+        <v>83.58840000000001</v>
+      </c>
+      <c r="Q33">
+        <v>0.02856941691161392</v>
+      </c>
+      <c r="R33">
+        <v>0.2679974350753447</v>
+      </c>
+      <c r="S33">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="T33">
+        <v>0.4378283712784588</v>
+      </c>
+      <c r="U33">
+        <v>7053.1</v>
+      </c>
+      <c r="V33">
+        <v>2.410656914348213</v>
+      </c>
+      <c r="W33">
+        <v>0.05941065544105602</v>
+      </c>
+      <c r="X33">
+        <v>0.08500319101552578</v>
+      </c>
+      <c r="Y33">
+        <v>-0.02559253557446976</v>
+      </c>
+      <c r="Z33">
+        <v>0.1865332376011597</v>
+      </c>
+      <c r="AA33">
+        <v>6.959562141446366E-05</v>
+      </c>
+      <c r="AB33">
+        <v>0.05618741613262754</v>
+      </c>
+      <c r="AC33">
+        <v>-0.05611782051121308</v>
+      </c>
+      <c r="AD33">
+        <v>6495.8</v>
+      </c>
+      <c r="AE33">
+        <v>2.218713480198955</v>
+      </c>
+      <c r="AF33">
+        <v>6498.018713480199</v>
+      </c>
+      <c r="AG33">
+        <v>-555.0812865198013</v>
+      </c>
+      <c r="AH33">
+        <v>0.6895313790560486</v>
+      </c>
+      <c r="AI33">
+        <v>0.5179140813378467</v>
+      </c>
+      <c r="AJ33">
+        <v>-0.2341405091053362</v>
+      </c>
+      <c r="AK33">
+        <v>-0.1010447802126748</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>6368.43137254902</v>
+      </c>
+      <c r="AP33">
+        <v>-544.1973397252954</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Musashino Bank, Ltd. (TSE:8336)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.0499</v>
+      </c>
+      <c r="E34">
+        <v>0.167</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>85.5</v>
+      </c>
+      <c r="L34">
+        <v>0.162054586808188</v>
+      </c>
+      <c r="M34">
+        <v>26.6283</v>
+      </c>
+      <c r="N34">
+        <v>0.04218010454617457</v>
+      </c>
+      <c r="O34">
+        <v>0.3114421052631579</v>
+      </c>
+      <c r="P34">
+        <v>26.5793</v>
+      </c>
+      <c r="Q34">
+        <v>0.04210248693172819</v>
+      </c>
+      <c r="R34">
+        <v>0.3108690058479532</v>
+      </c>
+      <c r="S34">
+        <v>0.04899999999999949</v>
+      </c>
+      <c r="T34">
+        <v>0.001840147512233206</v>
+      </c>
+      <c r="U34">
+        <v>1509.2</v>
+      </c>
+      <c r="V34">
+        <v>2.390622524948519</v>
+      </c>
+      <c r="W34">
+        <v>0.04975269130055281</v>
+      </c>
+      <c r="X34">
+        <v>0.06951046825100662</v>
+      </c>
+      <c r="Y34">
+        <v>-0.01975777695045382</v>
+      </c>
+      <c r="Z34">
+        <v>3.952059925093633</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0.05698054500715535</v>
+      </c>
+      <c r="AC34">
+        <v>-0.05698054500715535</v>
+      </c>
+      <c r="AD34">
+        <v>488.4</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>488.4</v>
+      </c>
+      <c r="AG34">
+        <v>-1020.8</v>
+      </c>
+      <c r="AH34">
+        <v>0.4361882647137627</v>
+      </c>
+      <c r="AI34">
+        <v>0.2030684794811027</v>
+      </c>
+      <c r="AJ34">
+        <v>2.620795892169447</v>
+      </c>
+      <c r="AK34">
+        <v>-1.139412880901886</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>The First Bank Of Toyama, Ltd. (TSE:7184)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.149</v>
+      </c>
+      <c r="E35">
+        <v>0.411</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="L35">
+        <v>0.2815413300186451</v>
+      </c>
+      <c r="M35">
+        <v>13.0875</v>
+      </c>
+      <c r="N35">
+        <v>0.03021819441237589</v>
+      </c>
+      <c r="O35">
+        <v>0.144453642384106</v>
+      </c>
+      <c r="P35">
+        <v>11.1475</v>
+      </c>
+      <c r="Q35">
+        <v>0.02573885938582313</v>
+      </c>
+      <c r="R35">
+        <v>0.1230408388520971</v>
+      </c>
+      <c r="S35">
+        <v>1.94</v>
+      </c>
+      <c r="T35">
+        <v>0.148233046800382</v>
+      </c>
+      <c r="U35">
+        <v>438.8</v>
+      </c>
+      <c r="V35">
+        <v>1.013160932809975</v>
+      </c>
+      <c r="W35">
+        <v>0.1017863161442534</v>
+      </c>
+      <c r="X35">
+        <v>0.06583604880069141</v>
+      </c>
+      <c r="Y35">
+        <v>0.03595026734356203</v>
+      </c>
+      <c r="Z35">
+        <v>0.5257310896912268</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0.05902899378023154</v>
+      </c>
+      <c r="AC35">
+        <v>-0.05902899378023154</v>
+      </c>
+      <c r="AD35">
+        <v>186.4</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>186.4</v>
+      </c>
+      <c r="AG35">
+        <v>-252.4</v>
+      </c>
+      <c r="AH35">
+        <v>0.3008878127522195</v>
+      </c>
+      <c r="AI35">
+        <v>0.1503225806451613</v>
+      </c>
+      <c r="AJ35">
+        <v>-1.396790260099612</v>
+      </c>
+      <c r="AK35">
+        <v>-0.3150274588117823</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
         <v>0</v>
       </c>
     </row>
